--- a/SMAF_lookup.xlsx
+++ b/SMAF_lookup.xlsx
@@ -5,26 +5,28 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uflorida-my.sharepoint.com/personal/moges_biru_ufl_edu/Documents/UFL/Research_Work/ETH SHAPE/Rerun for App/SMAF/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uflorida-my.sharepoint.com/personal/mohkam_singh_ufl_edu/Documents/Mohkam Singh - WORDLY/Research Projects/PhD Research/gSHAPE/SMAF for gSHAPE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_95635A838F67E66DF7088085E56DEBB51F12BD57" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7695E8D5-A9C0-46AC-A794-E28E05005812}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="11_95635A838F67E66DF7088085E56DEBB51F12BD57" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{947E2EBC-A47B-4A00-B013-04A1CB08819B}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28320" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="crop_factors" sheetId="1" r:id="rId1"/>
-    <sheet name="method_factors" sheetId="2" r:id="rId2"/>
-    <sheet name="weathering_classes" sheetId="3" r:id="rId3"/>
-    <sheet name="om_factors" sheetId="4" r:id="rId4"/>
-    <sheet name="texture_factors" sheetId="5" r:id="rId5"/>
-    <sheet name="slope_factors" sheetId="6" r:id="rId6"/>
-    <sheet name="constants" sheetId="7" r:id="rId7"/>
-    <sheet name="bd_texture_factors" sheetId="8" r:id="rId8"/>
-    <sheet name="bd_mineralogy_factors" sheetId="9" r:id="rId9"/>
-    <sheet name="bd_constants" sheetId="10" r:id="rId10"/>
-    <sheet name="exk_texture_params" sheetId="11" r:id="rId11"/>
-    <sheet name="exk_constants" sheetId="12" r:id="rId12"/>
+    <sheet name="ph_factors" sheetId="14" r:id="rId1"/>
+    <sheet name="crop_factors" sheetId="1" r:id="rId2"/>
+    <sheet name="method_factors" sheetId="2" r:id="rId3"/>
+    <sheet name="weathering_classes" sheetId="3" r:id="rId4"/>
+    <sheet name="om_factors" sheetId="4" r:id="rId5"/>
+    <sheet name="texture_factors" sheetId="5" r:id="rId6"/>
+    <sheet name="slope_factors" sheetId="6" r:id="rId7"/>
+    <sheet name="constants" sheetId="7" r:id="rId8"/>
+    <sheet name="bd_texture_factors" sheetId="8" r:id="rId9"/>
+    <sheet name="bd_mineralogy_factors" sheetId="9" r:id="rId10"/>
+    <sheet name="bd_constants" sheetId="10" r:id="rId11"/>
+    <sheet name="exk_texture_params" sheetId="11" r:id="rId12"/>
+    <sheet name="exk_constants" sheetId="12" r:id="rId13"/>
+    <sheet name="Sheet1" sheetId="13" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="194">
   <si>
     <t>crop_code</t>
   </si>
@@ -620,13 +622,22 @@
   </si>
   <si>
     <t>b</t>
+  </si>
+  <si>
+    <t>Clean crop name</t>
+  </si>
+  <si>
+    <t>pH_min</t>
+  </si>
+  <si>
+    <t>pH_max</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -673,6 +684,35 @@
       <color rgb="FF1E6B52"/>
       <name val="Arial"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -746,7 +786,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -777,11 +817,696 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="68">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -1040,8 +1765,1310 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF1CC01C-BF2E-442A-817B-F6A0C0A3903D}">
+  <dimension ref="A1:G108"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>5.5</v>
+      </c>
+      <c r="C2">
+        <v>7.5</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>7.5</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5">
+        <v>5.5</v>
+      </c>
+      <c r="C5">
+        <v>6.5</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="15">
+        <v>6</v>
+      </c>
+      <c r="C6" s="15">
+        <v>7</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7">
+        <v>4.3</v>
+      </c>
+      <c r="C7">
+        <v>5.5</v>
+      </c>
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="15">
+        <v>5.5</v>
+      </c>
+      <c r="C8" s="15">
+        <v>6.7</v>
+      </c>
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="15">
+        <v>5.5</v>
+      </c>
+      <c r="C9" s="15">
+        <v>7</v>
+      </c>
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+      <c r="E10" s="3"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="15">
+        <v>6.2</v>
+      </c>
+      <c r="C11" s="15">
+        <v>6.8</v>
+      </c>
+      <c r="E11" s="3"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12">
+        <v>5.5</v>
+      </c>
+      <c r="C12">
+        <v>7</v>
+      </c>
+      <c r="E12" s="3"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="15">
+        <v>6</v>
+      </c>
+      <c r="C13" s="15">
+        <v>6.8</v>
+      </c>
+      <c r="E13" s="3"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="15">
+        <v>5</v>
+      </c>
+      <c r="C14" s="15">
+        <v>6.5</v>
+      </c>
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15">
+        <v>5.8</v>
+      </c>
+      <c r="C15">
+        <v>6.2</v>
+      </c>
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16">
+        <v>5.8</v>
+      </c>
+      <c r="C16">
+        <v>6.2</v>
+      </c>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17">
+        <v>5.8</v>
+      </c>
+      <c r="C17">
+        <v>6.2</v>
+      </c>
+      <c r="E17" s="3"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="15">
+        <v>5.8</v>
+      </c>
+      <c r="C18" s="15">
+        <v>6.5</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19">
+        <v>5.5</v>
+      </c>
+      <c r="C19">
+        <v>7</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20">
+        <v>5.5</v>
+      </c>
+      <c r="C20">
+        <v>7</v>
+      </c>
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="15">
+        <v>6</v>
+      </c>
+      <c r="C21" s="15">
+        <v>7</v>
+      </c>
+      <c r="E21" s="3"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="15">
+        <v>6</v>
+      </c>
+      <c r="C22" s="15">
+        <v>7</v>
+      </c>
+      <c r="E22" s="3"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>7.5</v>
+      </c>
+      <c r="E23" s="3"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="15">
+        <v>5.5</v>
+      </c>
+      <c r="C24" s="15">
+        <v>6.5</v>
+      </c>
+      <c r="E24" s="3"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25" s="15">
+        <v>6</v>
+      </c>
+      <c r="C25" s="15">
+        <v>6.5</v>
+      </c>
+      <c r="E25" s="3"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26">
+        <v>5.5</v>
+      </c>
+      <c r="C26">
+        <v>6.8</v>
+      </c>
+      <c r="E26" s="3"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="15">
+        <v>6</v>
+      </c>
+      <c r="C27" s="15">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28">
+        <v>6</v>
+      </c>
+      <c r="C28">
+        <v>7</v>
+      </c>
+      <c r="E28" s="3"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" s="15">
+        <v>6</v>
+      </c>
+      <c r="C29" s="15">
+        <v>7</v>
+      </c>
+      <c r="E29" s="3"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" s="15">
+        <v>6</v>
+      </c>
+      <c r="C30" s="15">
+        <v>7</v>
+      </c>
+      <c r="E30" s="3"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31">
+        <v>5.8</v>
+      </c>
+      <c r="C31">
+        <v>7.2</v>
+      </c>
+      <c r="E31" s="3"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" s="15">
+        <v>6</v>
+      </c>
+      <c r="C32" s="15">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33">
+        <v>5.5</v>
+      </c>
+      <c r="C33">
+        <v>7</v>
+      </c>
+      <c r="E33" s="3"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>62</v>
+      </c>
+      <c r="B34">
+        <v>5.6</v>
+      </c>
+      <c r="C34">
+        <v>6.5</v>
+      </c>
+      <c r="E34" s="3"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>64</v>
+      </c>
+      <c r="B35">
+        <v>6</v>
+      </c>
+      <c r="C35">
+        <v>7</v>
+      </c>
+      <c r="E35" s="3"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>66</v>
+      </c>
+      <c r="B36">
+        <v>6</v>
+      </c>
+      <c r="C36">
+        <v>7.5</v>
+      </c>
+      <c r="E36" s="3"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>65</v>
+      </c>
+      <c r="B37">
+        <v>6</v>
+      </c>
+      <c r="C37">
+        <v>7</v>
+      </c>
+      <c r="E37" s="3"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38">
+        <v>5</v>
+      </c>
+      <c r="C38">
+        <v>6</v>
+      </c>
+      <c r="E38" s="3"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>77</v>
+      </c>
+      <c r="B39">
+        <v>5</v>
+      </c>
+      <c r="C39">
+        <v>5.5</v>
+      </c>
+      <c r="E39" s="3"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B40" s="15">
+        <v>6</v>
+      </c>
+      <c r="C40" s="15">
+        <v>6.8</v>
+      </c>
+      <c r="E40" s="3"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41">
+        <v>5.5</v>
+      </c>
+      <c r="C41">
+        <v>7.5</v>
+      </c>
+      <c r="E41" s="3"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B42" s="15">
+        <v>4</v>
+      </c>
+      <c r="C42" s="15">
+        <v>6</v>
+      </c>
+      <c r="E42" s="3"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>85</v>
+      </c>
+      <c r="B43">
+        <v>5.5</v>
+      </c>
+      <c r="C43">
+        <v>7</v>
+      </c>
+      <c r="E43" s="3"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>86</v>
+      </c>
+      <c r="B44">
+        <v>5.5</v>
+      </c>
+      <c r="C44">
+        <v>7</v>
+      </c>
+      <c r="E44" s="3"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>89</v>
+      </c>
+      <c r="B45">
+        <v>5</v>
+      </c>
+      <c r="C45">
+        <v>6.5</v>
+      </c>
+      <c r="E45" s="3"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>92</v>
+      </c>
+      <c r="B46">
+        <v>5</v>
+      </c>
+      <c r="C46">
+        <v>8</v>
+      </c>
+      <c r="E46" s="3"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="B47" s="15">
+        <v>6.5</v>
+      </c>
+      <c r="C47" s="15">
+        <v>7.5</v>
+      </c>
+      <c r="E47" s="3"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>94</v>
+      </c>
+      <c r="B48">
+        <v>5</v>
+      </c>
+      <c r="C48">
+        <v>6</v>
+      </c>
+      <c r="E48" s="3"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>96</v>
+      </c>
+      <c r="B49">
+        <v>5</v>
+      </c>
+      <c r="C49">
+        <v>6</v>
+      </c>
+      <c r="E49" s="3"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B50">
+        <v>5.5</v>
+      </c>
+      <c r="C50">
+        <v>7</v>
+      </c>
+      <c r="E50" s="3"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B51" s="15">
+        <v>6</v>
+      </c>
+      <c r="C51" s="15">
+        <v>7</v>
+      </c>
+      <c r="E51" s="3"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="B52" s="15">
+        <v>6</v>
+      </c>
+      <c r="C52" s="15">
+        <v>6.5</v>
+      </c>
+      <c r="E52" s="3"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B53" s="15">
+        <v>6</v>
+      </c>
+      <c r="C53" s="15">
+        <v>7</v>
+      </c>
+      <c r="E53" s="3"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B54">
+        <v>5.5</v>
+      </c>
+      <c r="C54">
+        <v>7</v>
+      </c>
+      <c r="E54" s="3"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="B55" s="15">
+        <v>6</v>
+      </c>
+      <c r="C55" s="15">
+        <v>6.8</v>
+      </c>
+      <c r="E55" s="3"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>104</v>
+      </c>
+      <c r="B56">
+        <v>5.5</v>
+      </c>
+      <c r="C56">
+        <v>7</v>
+      </c>
+      <c r="E56" s="3"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>105</v>
+      </c>
+      <c r="B57">
+        <v>5.5</v>
+      </c>
+      <c r="C57">
+        <v>7</v>
+      </c>
+      <c r="E57" s="3"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58">
+        <v>5.8</v>
+      </c>
+      <c r="C58">
+        <v>7</v>
+      </c>
+      <c r="E58" s="3"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59">
+        <v>5.8</v>
+      </c>
+      <c r="C59">
+        <v>7</v>
+      </c>
+      <c r="E59" s="3"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B60">
+        <v>5.8</v>
+      </c>
+      <c r="C60">
+        <v>7</v>
+      </c>
+      <c r="E60" s="3"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B61">
+        <v>5.8</v>
+      </c>
+      <c r="C61">
+        <v>7</v>
+      </c>
+      <c r="E61" s="3"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B62">
+        <v>5.8</v>
+      </c>
+      <c r="C62">
+        <v>7</v>
+      </c>
+      <c r="E62" s="3"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B63">
+        <v>5.8</v>
+      </c>
+      <c r="C63">
+        <v>7</v>
+      </c>
+      <c r="E63" s="3"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E64" s="3"/>
+    </row>
+    <row r="65" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E65" s="3"/>
+    </row>
+    <row r="66" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E66" s="3"/>
+    </row>
+    <row r="67" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E67" s="3"/>
+    </row>
+    <row r="68" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E68" s="3"/>
+    </row>
+    <row r="69" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E69" s="3"/>
+    </row>
+    <row r="70" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E70" s="3"/>
+    </row>
+    <row r="71" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E71" s="3"/>
+    </row>
+    <row r="72" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E72" s="3"/>
+    </row>
+    <row r="73" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E73" s="3"/>
+    </row>
+    <row r="74" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E74" s="3"/>
+    </row>
+    <row r="75" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E75" s="3"/>
+    </row>
+    <row r="76" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E76" s="3"/>
+    </row>
+    <row r="77" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E77" s="3"/>
+    </row>
+    <row r="78" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E78" s="3"/>
+    </row>
+    <row r="79" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E79" s="3"/>
+    </row>
+    <row r="80" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E80" s="3"/>
+    </row>
+    <row r="81" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E81" s="3"/>
+    </row>
+    <row r="82" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E82" s="3"/>
+    </row>
+    <row r="83" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E83" s="3"/>
+    </row>
+    <row r="84" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E84" s="3"/>
+    </row>
+    <row r="85" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E85" s="3"/>
+    </row>
+    <row r="86" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E86" s="3"/>
+    </row>
+    <row r="87" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E87" s="3"/>
+    </row>
+    <row r="88" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E88" s="3"/>
+    </row>
+    <row r="89" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E89" s="3"/>
+    </row>
+    <row r="90" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E90" s="3"/>
+    </row>
+    <row r="91" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E91" s="3"/>
+    </row>
+    <row r="92" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E92" s="3"/>
+    </row>
+    <row r="93" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E93" s="3"/>
+    </row>
+    <row r="94" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E94" s="3"/>
+    </row>
+    <row r="95" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E95" s="3"/>
+    </row>
+    <row r="96" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E96" s="3"/>
+    </row>
+    <row r="97" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E97" s="3"/>
+    </row>
+    <row r="98" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E98" s="3"/>
+    </row>
+    <row r="99" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E99" s="3"/>
+    </row>
+    <row r="100" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E100" s="3"/>
+    </row>
+    <row r="101" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E101" s="3"/>
+    </row>
+    <row r="102" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E102" s="3"/>
+    </row>
+    <row r="103" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E103" s="3"/>
+    </row>
+    <row r="104" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E104" s="3"/>
+    </row>
+    <row r="105" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E105" s="3"/>
+    </row>
+    <row r="106" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E106" s="3"/>
+    </row>
+    <row r="107" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E107" s="3"/>
+    </row>
+    <row r="108" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E108" s="3"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A15:A17">
+    <cfRule type="duplicateValues" dxfId="62" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F18:G19">
+    <cfRule type="duplicateValues" dxfId="61" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A51">
+    <cfRule type="duplicateValues" dxfId="60" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A51">
+    <cfRule type="duplicateValues" dxfId="59" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A58">
+    <cfRule type="duplicateValues" dxfId="58" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A58">
+    <cfRule type="duplicateValues" dxfId="57" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A58">
+    <cfRule type="duplicateValues" dxfId="56" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A59">
+    <cfRule type="duplicateValues" dxfId="55" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A59">
+    <cfRule type="duplicateValues" dxfId="54" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A59">
+    <cfRule type="duplicateValues" dxfId="53" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A60">
+    <cfRule type="duplicateValues" dxfId="52" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A60">
+    <cfRule type="duplicateValues" dxfId="51" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A60">
+    <cfRule type="duplicateValues" dxfId="50" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A61">
+    <cfRule type="duplicateValues" dxfId="49" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A61">
+    <cfRule type="duplicateValues" dxfId="48" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A61">
+    <cfRule type="duplicateValues" dxfId="47" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A62:A63">
+    <cfRule type="duplicateValues" dxfId="46" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A62:A63">
+    <cfRule type="duplicateValues" dxfId="45" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A62:A63">
+    <cfRule type="duplicateValues" dxfId="44" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="8">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3">
+        <v>-0.03</v>
+      </c>
+      <c r="C3" s="3">
+        <v>5.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3">
+        <v>-0.1</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+    </row>
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="58" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="B2" s="3">
+        <v>0.99399999999999999</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="B3" s="3">
+        <v>3.6950899999999999E-5</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="B4" s="3">
+        <v>11.628251000000001</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="B5" s="3">
+        <v>-1.1878</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="B6" s="3">
+        <v>-8.4931999999999999</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0.99399999999999999</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10"/>
+    </row>
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+    </row>
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+    </row>
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+    </row>
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+    </row>
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="12">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="12">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="12">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="12">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="12">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1.0541326</v>
+      </c>
+      <c r="C2" s="3">
+        <v>-9.8126979999999999E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1.0744899999999999</v>
+      </c>
+      <c r="C3" s="3">
+        <v>-1.3431848999999999E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="13"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BAE779D-EE07-4BAA-A5AD-49FE70D75EAE}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E110"/>
+  <dimension ref="A1:E172"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -2981,260 +5008,172 @@
     <row r="110" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="4"/>
     </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B115" s="15"/>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B117" s="15"/>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B118" s="15"/>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B120" s="15"/>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B122" s="15"/>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B123" s="15"/>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B124" s="3"/>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B125" s="3"/>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B126" s="3"/>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B127" s="15"/>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B130" s="15"/>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B131" s="15"/>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B133" s="15"/>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B134" s="15"/>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B136" s="15"/>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B138" s="15"/>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B139" s="15"/>
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B141" s="15"/>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B149" s="15"/>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B151" s="15"/>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B156" s="15"/>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B160" s="16"/>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B161" s="15"/>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B162" s="15"/>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B164" s="17"/>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B167" s="3"/>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B168" s="3"/>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B169" s="3"/>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B170" s="3"/>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B171" s="3"/>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B172" s="3"/>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="B173:B1048576 B1:B110 I12">
+    <cfRule type="duplicateValues" dxfId="43" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B173:B1048576 B1:B110 I12">
+    <cfRule type="duplicateValues" dxfId="42" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B110 B173:B1048576 I12">
+    <cfRule type="duplicateValues" dxfId="41" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B124:B126">
+    <cfRule type="duplicateValues" dxfId="40" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B160">
+    <cfRule type="duplicateValues" dxfId="39" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B160">
+    <cfRule type="duplicateValues" dxfId="38" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B167">
+    <cfRule type="duplicateValues" dxfId="37" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B167">
+    <cfRule type="duplicateValues" dxfId="36" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B167">
+    <cfRule type="duplicateValues" dxfId="35" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B168">
+    <cfRule type="duplicateValues" dxfId="34" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B168">
+    <cfRule type="duplicateValues" dxfId="33" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B168">
+    <cfRule type="duplicateValues" dxfId="32" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B169">
+    <cfRule type="duplicateValues" dxfId="31" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B169">
+    <cfRule type="duplicateValues" dxfId="30" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B169">
+    <cfRule type="duplicateValues" dxfId="29" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B170">
+    <cfRule type="duplicateValues" dxfId="28" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B170">
+    <cfRule type="duplicateValues" dxfId="27" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B170">
+    <cfRule type="duplicateValues" dxfId="26" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B171:B172">
+    <cfRule type="duplicateValues" dxfId="25" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B171:B172">
+    <cfRule type="duplicateValues" dxfId="24" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B171:B172">
+    <cfRule type="duplicateValues" dxfId="23" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="58" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="B2" s="3">
-        <v>0.99399999999999999</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="B3" s="3">
-        <v>3.6950899999999999E-5</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="B4" s="3">
-        <v>11.628251000000001</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="B5" s="3">
-        <v>-1.1878</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="B6" s="3">
-        <v>-8.4931999999999999</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="B7" s="3">
-        <v>0</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0.99399999999999999</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10"/>
-    </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-    </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-    </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-    </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-    </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="12">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="12">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="12">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="12">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="B2" s="3">
-        <v>1.0541326</v>
-      </c>
-      <c r="C2" s="3">
-        <v>-9.8126979999999999E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="B3" s="3">
-        <v>1.0744899999999999</v>
-      </c>
-      <c r="C3" s="3">
-        <v>-1.3431848999999999E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="13"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C22"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3465,7 +5404,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3528,7 +5467,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3619,7 +5558,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3722,7 +5661,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3828,7 +5767,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4000,7 +5939,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4144,81 +6083,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3">
-        <v>0</v>
-      </c>
-      <c r="C2" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3">
-        <v>-0.03</v>
-      </c>
-      <c r="C3" s="3">
-        <v>5.0000000000000001E-4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3">
-        <v>-0.1</v>
-      </c>
-      <c r="C4" s="3">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="C5" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-    </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
 </file>
--- a/SMAF_lookup.xlsx
+++ b/SMAF_lookup.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30317"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uflorida-my.sharepoint.com/personal/mohkam_singh_ufl_edu/Documents/Mohkam Singh - WORDLY/Research Projects/PhD Research/gSHAPE/SMAF for gSHAPE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="93" documentId="11_95635A838F67E66DF7088085E56DEBB51F12BD57" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{947E2EBC-A47B-4A00-B013-04A1CB08819B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A4D5D69C-A193-448A-9D17-6DCFDECF773D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ph_factors" sheetId="14" r:id="rId1"/>
@@ -28,8 +28,11 @@
     <sheet name="exk_constants" sheetId="12" r:id="rId13"/>
     <sheet name="Sheet1" sheetId="13" r:id="rId14"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -49,7 +52,343 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="201">
+  <si>
+    <t>Clean crop name</t>
+  </si>
+  <si>
+    <t>pH_min</t>
+  </si>
+  <si>
+    <t>pH_max</t>
+  </si>
+  <si>
+    <t>apples</t>
+  </si>
+  <si>
+    <t>avocado</t>
+  </si>
+  <si>
+    <t>banana</t>
+  </si>
+  <si>
+    <t>barley, malt barley</t>
+  </si>
+  <si>
+    <t>beans, dried</t>
+  </si>
+  <si>
+    <t>blueberries</t>
+  </si>
+  <si>
+    <t>fava or broad bean</t>
+  </si>
+  <si>
+    <t>buckwheat</t>
+  </si>
+  <si>
+    <t>cabbage</t>
+  </si>
+  <si>
+    <t>cantaloupe</t>
+  </si>
+  <si>
+    <t>carrot</t>
+  </si>
+  <si>
+    <t>pepper</t>
+  </si>
+  <si>
+    <t>coffee</t>
+  </si>
+  <si>
+    <t>corn, sweet</t>
+  </si>
+  <si>
+    <t>corn, pop</t>
+  </si>
+  <si>
+    <t>corn, grain</t>
+  </si>
+  <si>
+    <t>cotton</t>
+  </si>
+  <si>
+    <t>cowpea</t>
+  </si>
+  <si>
+    <t>cucumber</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>garlic</t>
+  </si>
+  <si>
+    <t>grape</t>
+  </si>
+  <si>
+    <t>grapefruit</t>
+  </si>
+  <si>
+    <t>peanut</t>
+  </si>
+  <si>
+    <t>guava</t>
+  </si>
+  <si>
+    <t>lentils</t>
+  </si>
+  <si>
+    <t>lettuce</t>
+  </si>
+  <si>
+    <t>flaxseed; flax</t>
+  </si>
+  <si>
+    <t>millet</t>
+  </si>
+  <si>
+    <t>oat</t>
+  </si>
+  <si>
+    <t>olive</t>
+  </si>
+  <si>
+    <t>onion</t>
+  </si>
+  <si>
+    <t>orange</t>
+  </si>
+  <si>
+    <t>papaya</t>
+  </si>
+  <si>
+    <t>peach</t>
+  </si>
+  <si>
+    <t>pea, field; peas</t>
+  </si>
+  <si>
+    <t>pineapple</t>
+  </si>
+  <si>
+    <t>potato</t>
+  </si>
+  <si>
+    <t>squash, scallop</t>
+  </si>
+  <si>
+    <t>rice, paddy</t>
+  </si>
+  <si>
+    <t>pine, slash</t>
+  </si>
+  <si>
+    <t>sorghum, grain sorghum</t>
+  </si>
+  <si>
+    <t>soybean</t>
+  </si>
+  <si>
+    <t>strawberry</t>
+  </si>
+  <si>
+    <t>sugarcane</t>
+  </si>
+  <si>
+    <t>sunflower</t>
+  </si>
+  <si>
+    <t>sweet potato</t>
+  </si>
+  <si>
+    <t>tobacco</t>
+  </si>
+  <si>
+    <t>tomato</t>
+  </si>
+  <si>
+    <t>triticale</t>
+  </si>
+  <si>
+    <t>walnut</t>
+  </si>
+  <si>
+    <t>watermelon</t>
+  </si>
+  <si>
+    <t>wheat, durum</t>
+  </si>
+  <si>
+    <t>zucchini</t>
+  </si>
+  <si>
+    <t>wheat, spring</t>
+  </si>
+  <si>
+    <t>winter wheat</t>
+  </si>
+  <si>
+    <t>bermuda grass, coastal</t>
+  </si>
+  <si>
+    <t>fescue, tall</t>
+  </si>
+  <si>
+    <t>orchard grass</t>
+  </si>
+  <si>
+    <t>timothy</t>
+  </si>
+  <si>
+    <t>ryegrass, annual</t>
+  </si>
+  <si>
+    <t>ryegrass, perennial</t>
+  </si>
+  <si>
+    <t>alfalfa</t>
+  </si>
+  <si>
+    <t>almond</t>
+  </si>
+  <si>
+    <t>apricot</t>
+  </si>
+  <si>
+    <t>asparagus</t>
+  </si>
+  <si>
+    <t>beet, red</t>
+  </si>
+  <si>
+    <t>blackberry</t>
+  </si>
+  <si>
+    <t>bluegrass</t>
+  </si>
+  <si>
+    <t>bluestem, big</t>
+  </si>
+  <si>
+    <t>bluestem, little</t>
+  </si>
+  <si>
+    <t>boysenberry</t>
+  </si>
+  <si>
+    <t>broccoli</t>
+  </si>
+  <si>
+    <t>cauliflower</t>
+  </si>
+  <si>
+    <t>celery</t>
+  </si>
+  <si>
+    <t>cherries</t>
+  </si>
+  <si>
+    <t>clover, berseem</t>
+  </si>
+  <si>
+    <t>clover, white</t>
+  </si>
+  <si>
+    <t>cranberries</t>
+  </si>
+  <si>
+    <t>foxtail, meadow</t>
+  </si>
+  <si>
+    <t>hops</t>
+  </si>
+  <si>
+    <t>indian grass</t>
+  </si>
+  <si>
+    <t>johnsongrass</t>
+  </si>
+  <si>
+    <t>macadamia orchards</t>
+  </si>
+  <si>
+    <t>melon</t>
+  </si>
+  <si>
+    <t>mulberry</t>
+  </si>
+  <si>
+    <t>pear</t>
+  </si>
+  <si>
+    <t>pecans</t>
+  </si>
+  <si>
+    <t>pine, lodgepole</t>
+  </si>
+  <si>
+    <t>pine, ponderosa</t>
+  </si>
+  <si>
+    <t>plum</t>
+  </si>
+  <si>
+    <t>poppy</t>
+  </si>
+  <si>
+    <t>radish</t>
+  </si>
+  <si>
+    <t>raspberry</t>
+  </si>
+  <si>
+    <t>safflower</t>
+  </si>
+  <si>
+    <t>sorghum</t>
+  </si>
+  <si>
+    <t>spinach</t>
+  </si>
+  <si>
+    <t>sudangrass</t>
+  </si>
+  <si>
+    <t>sugarbeet</t>
+  </si>
+  <si>
+    <t>turnip</t>
+  </si>
+  <si>
+    <t>vetch</t>
+  </si>
+  <si>
+    <t>pine, longleaf</t>
+  </si>
+  <si>
+    <t>oak, southern red</t>
+  </si>
+  <si>
+    <t>hickory</t>
+  </si>
+  <si>
+    <t>oak</t>
+  </si>
+  <si>
+    <t>cassava</t>
+  </si>
+  <si>
+    <t>tea</t>
+  </si>
+  <si>
+    <t>teff</t>
+  </si>
+  <si>
+    <t>eucalytus</t>
+  </si>
   <si>
     <t>crop_code</t>
   </si>
@@ -66,321 +405,15 @@
     <t>b1</t>
   </si>
   <si>
-    <t>alfalfa</t>
-  </si>
-  <si>
-    <t>almond</t>
-  </si>
-  <si>
-    <t>apples</t>
-  </si>
-  <si>
-    <t>apricot</t>
-  </si>
-  <si>
-    <t>asparagus</t>
-  </si>
-  <si>
-    <t>avocado</t>
-  </si>
-  <si>
-    <t>banana</t>
-  </si>
-  <si>
-    <t>barley, malt barley</t>
-  </si>
-  <si>
-    <t>beans, dried</t>
-  </si>
-  <si>
-    <t>beet, red</t>
-  </si>
-  <si>
-    <t>bermuda grass, coastal</t>
-  </si>
-  <si>
-    <t>blackberry</t>
-  </si>
-  <si>
-    <t>blueberries</t>
-  </si>
-  <si>
-    <t>bluegrass</t>
-  </si>
-  <si>
-    <t>bluestem, big</t>
-  </si>
-  <si>
-    <t>bluestem, little</t>
-  </si>
-  <si>
-    <t>boysenberry</t>
-  </si>
-  <si>
-    <t>broccoli</t>
-  </si>
-  <si>
-    <t>buckwheat</t>
-  </si>
-  <si>
-    <t>cabbage</t>
-  </si>
-  <si>
-    <t>cantaloupe</t>
-  </si>
-  <si>
-    <t>carrot</t>
-  </si>
-  <si>
-    <t>cauliflower</t>
-  </si>
-  <si>
-    <t>celery</t>
-  </si>
-  <si>
-    <t>cherries</t>
-  </si>
-  <si>
-    <t>clover, berseem</t>
-  </si>
-  <si>
     <t>clover, red, alsike, ladino, strawberry</t>
   </si>
   <si>
-    <t>clover, white</t>
-  </si>
-  <si>
-    <t>coffee</t>
-  </si>
-  <si>
-    <t>corn, sweet</t>
-  </si>
-  <si>
-    <t>corn, pop</t>
-  </si>
-  <si>
-    <t>corn, grain</t>
-  </si>
-  <si>
-    <t>cotton</t>
-  </si>
-  <si>
-    <t>cowpea</t>
-  </si>
-  <si>
-    <t>cranberries</t>
-  </si>
-  <si>
-    <t>cucumber</t>
-  </si>
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>fava or broad bean</t>
-  </si>
-  <si>
-    <t>fescue, tall</t>
-  </si>
-  <si>
-    <t>flaxseed; flax</t>
-  </si>
-  <si>
-    <t>foxtail, meadow</t>
-  </si>
-  <si>
-    <t>garlic</t>
-  </si>
-  <si>
-    <t>grape</t>
-  </si>
-  <si>
-    <t>grapefruit</t>
-  </si>
-  <si>
-    <t>guava</t>
-  </si>
-  <si>
-    <t>hops</t>
-  </si>
-  <si>
-    <t>indian grass</t>
-  </si>
-  <si>
-    <t>johnsongrass</t>
-  </si>
-  <si>
-    <t>lentils</t>
-  </si>
-  <si>
-    <t>lettuce</t>
-  </si>
-  <si>
-    <t>macadamia orchards</t>
-  </si>
-  <si>
-    <t>melon</t>
-  </si>
-  <si>
-    <t>millet</t>
-  </si>
-  <si>
-    <t>mulberry</t>
-  </si>
-  <si>
-    <t>oat</t>
-  </si>
-  <si>
-    <t>olive</t>
-  </si>
-  <si>
-    <t>onion</t>
-  </si>
-  <si>
-    <t>orange</t>
-  </si>
-  <si>
-    <t>orchard grass</t>
-  </si>
-  <si>
-    <t>papaya</t>
-  </si>
-  <si>
-    <t>pea, field; peas</t>
-  </si>
-  <si>
-    <t>peach</t>
-  </si>
-  <si>
-    <t>peanut</t>
-  </si>
-  <si>
-    <t>pear</t>
-  </si>
-  <si>
-    <t>pecans</t>
-  </si>
-  <si>
-    <t>pepper</t>
-  </si>
-  <si>
-    <t>pine, lodgepole</t>
-  </si>
-  <si>
-    <t>pine, ponderosa</t>
-  </si>
-  <si>
-    <t>pine, slash</t>
-  </si>
-  <si>
-    <t>pineapple</t>
-  </si>
-  <si>
-    <t>plum</t>
-  </si>
-  <si>
-    <t>poppy</t>
-  </si>
-  <si>
-    <t>potato</t>
-  </si>
-  <si>
-    <t>radish</t>
-  </si>
-  <si>
-    <t>raspberry</t>
-  </si>
-  <si>
-    <t>rice, paddy</t>
-  </si>
-  <si>
-    <t>ryegrass, annual</t>
-  </si>
-  <si>
-    <t>ryegrass, perennial</t>
-  </si>
-  <si>
-    <t>safflower</t>
-  </si>
-  <si>
     <t>sorghum x sudan grass</t>
   </si>
   <si>
-    <t>sorghum, grain sorghum</t>
-  </si>
-  <si>
-    <t>soybean</t>
-  </si>
-  <si>
-    <t>spinach</t>
-  </si>
-  <si>
-    <t>squash, scallop</t>
-  </si>
-  <si>
-    <t>strawberry</t>
-  </si>
-  <si>
-    <t>sudangrass</t>
-  </si>
-  <si>
-    <t>sugarbeet</t>
-  </si>
-  <si>
-    <t>sugarcane</t>
-  </si>
-  <si>
-    <t>sunflower</t>
-  </si>
-  <si>
-    <t>sweet potato</t>
-  </si>
-  <si>
-    <t>timothy</t>
-  </si>
-  <si>
-    <t>tobacco</t>
-  </si>
-  <si>
-    <t>tomato</t>
-  </si>
-  <si>
-    <t>triticale</t>
-  </si>
-  <si>
-    <t>turnip</t>
-  </si>
-  <si>
     <t>vetch, common or hairy</t>
   </si>
   <si>
-    <t>walnut</t>
-  </si>
-  <si>
-    <t>watermelon</t>
-  </si>
-  <si>
-    <t>wheat, durum</t>
-  </si>
-  <si>
-    <t>wheat, spring</t>
-  </si>
-  <si>
-    <t>winter wheat</t>
-  </si>
-  <si>
-    <t>zucchini</t>
-  </si>
-  <si>
-    <t>pine, longleaf</t>
-  </si>
-  <si>
-    <t>oak, southern red</t>
-  </si>
-  <si>
-    <t>hickory</t>
-  </si>
-  <si>
     <t>oak, white</t>
   </si>
   <si>
@@ -622,22 +655,13 @@
   </si>
   <si>
     <t>b</t>
-  </si>
-  <si>
-    <t>Clean crop name</t>
-  </si>
-  <si>
-    <t>pH_min</t>
-  </si>
-  <si>
-    <t>pH_max</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -714,8 +738,27 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -758,6 +801,24 @@
         <bgColor rgb="FFEAF1F3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDD9C4"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5D9F1"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -786,7 +847,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -821,281 +882,30 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="68">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="41">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1766,27 +1576,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF1CC01C-BF2E-442A-817B-F6A0C0A3903D}">
-  <dimension ref="A1:G108"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G110"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="31.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="15.75">
       <c r="A1" s="14" t="s">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>192</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>5.5</v>
@@ -1797,9 +1607,9 @@
       <c r="E2" s="3"/>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>6</v>
@@ -1810,9 +1620,9 @@
       <c r="E3" s="3"/>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>5</v>
@@ -1822,9 +1632,9 @@
       </c>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5">
         <v>5.5</v>
@@ -1835,9 +1645,9 @@
       <c r="E5" s="3"/>
       <c r="G5" s="3"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="15" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B6" s="15">
         <v>6</v>
@@ -1848,9 +1658,9 @@
       <c r="E6" s="3"/>
       <c r="G6" s="3"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>4.3</v>
@@ -1860,9 +1670,9 @@
       </c>
       <c r="G7" s="3"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="15" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="B8" s="15">
         <v>5.5</v>
@@ -1872,9 +1682,9 @@
       </c>
       <c r="E8" s="3"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="15" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B9" s="15">
         <v>5.5</v>
@@ -1884,9 +1694,9 @@
       </c>
       <c r="E9" s="3"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B10">
         <v>5.5</v>
@@ -1896,9 +1706,9 @@
       </c>
       <c r="E10" s="3"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="15" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B11" s="15">
         <v>6.2</v>
@@ -1908,9 +1718,9 @@
       </c>
       <c r="E11" s="3"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B12">
         <v>5.5</v>
@@ -1920,9 +1730,9 @@
       </c>
       <c r="E12" s="3"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="15" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="B13" s="15">
         <v>6</v>
@@ -1932,9 +1742,9 @@
       </c>
       <c r="E13" s="3"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="15" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B14" s="15">
         <v>5</v>
@@ -1944,9 +1754,9 @@
       </c>
       <c r="E14" s="3"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="A15" s="3" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="B15">
         <v>5.8</v>
@@ -1956,9 +1766,9 @@
       </c>
       <c r="E15" s="3"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="A16" s="3" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="B16">
         <v>5.8</v>
@@ -1968,9 +1778,9 @@
       </c>
       <c r="E16" s="3"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="3" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="B17">
         <v>5.8</v>
@@ -1980,9 +1790,9 @@
       </c>
       <c r="E17" s="3"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="15" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="B18" s="15">
         <v>5.8</v>
@@ -1994,9 +1804,9 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="B19">
         <v>5.5</v>
@@ -2008,9 +1818,9 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="B20">
         <v>5.5</v>
@@ -2020,9 +1830,9 @@
       </c>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7">
       <c r="A21" s="15" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="B21" s="15">
         <v>6</v>
@@ -2032,9 +1842,9 @@
       </c>
       <c r="E21" s="3"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7">
       <c r="A22" s="15" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="B22" s="15">
         <v>6</v>
@@ -2044,9 +1854,9 @@
       </c>
       <c r="E22" s="3"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="B23">
         <v>6</v>
@@ -2056,9 +1866,9 @@
       </c>
       <c r="E23" s="3"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7">
       <c r="A24" s="15" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="B24" s="15">
         <v>5.5</v>
@@ -2068,9 +1878,9 @@
       </c>
       <c r="E24" s="3"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7">
       <c r="A25" s="15" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="B25" s="15">
         <v>6</v>
@@ -2080,9 +1890,9 @@
       </c>
       <c r="E25" s="3"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="B26">
         <v>5.5</v>
@@ -2092,9 +1902,9 @@
       </c>
       <c r="E26" s="3"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7">
       <c r="A27" s="15" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="B27" s="15">
         <v>6</v>
@@ -2104,9 +1914,9 @@
       </c>
       <c r="E27" s="3"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="B28">
         <v>6</v>
@@ -2116,9 +1926,9 @@
       </c>
       <c r="E28" s="3"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7">
       <c r="A29" s="15" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="B29" s="15">
         <v>6</v>
@@ -2128,9 +1938,9 @@
       </c>
       <c r="E29" s="3"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7">
       <c r="A30" s="15" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="B30" s="15">
         <v>6</v>
@@ -2140,9 +1950,9 @@
       </c>
       <c r="E30" s="3"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="B31">
         <v>5.8</v>
@@ -2152,9 +1962,9 @@
       </c>
       <c r="E31" s="3"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7">
       <c r="A32" s="15" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="B32" s="15">
         <v>6</v>
@@ -2164,9 +1974,9 @@
       </c>
       <c r="E32" s="3"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="B33">
         <v>5.5</v>
@@ -2176,9 +1986,9 @@
       </c>
       <c r="E33" s="3"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="B34">
         <v>5.6</v>
@@ -2188,9 +1998,9 @@
       </c>
       <c r="E34" s="3"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="B35">
         <v>6</v>
@@ -2200,9 +2010,9 @@
       </c>
       <c r="E35" s="3"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="B36">
         <v>6</v>
@@ -2212,9 +2022,9 @@
       </c>
       <c r="E36" s="3"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="B37">
         <v>6</v>
@@ -2224,9 +2034,9 @@
       </c>
       <c r="E37" s="3"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="B38">
         <v>5</v>
@@ -2236,9 +2046,9 @@
       </c>
       <c r="E38" s="3"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="B39">
         <v>5</v>
@@ -2248,9 +2058,9 @@
       </c>
       <c r="E39" s="3"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5">
       <c r="A40" s="15" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="B40" s="15">
         <v>6</v>
@@ -2260,9 +2070,9 @@
       </c>
       <c r="E40" s="3"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="B41">
         <v>5.5</v>
@@ -2272,9 +2082,9 @@
       </c>
       <c r="E41" s="3"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5">
       <c r="A42" s="15" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="B42" s="15">
         <v>4</v>
@@ -2284,9 +2094,9 @@
       </c>
       <c r="E42" s="3"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="B43">
         <v>5.5</v>
@@ -2296,9 +2106,9 @@
       </c>
       <c r="E43" s="3"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="B44">
         <v>5.5</v>
@@ -2308,9 +2118,9 @@
       </c>
       <c r="E44" s="3"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="B45">
         <v>5</v>
@@ -2320,9 +2130,9 @@
       </c>
       <c r="E45" s="3"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="B46">
         <v>5</v>
@@ -2332,9 +2142,9 @@
       </c>
       <c r="E46" s="3"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5">
       <c r="A47" s="15" t="s">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="B47" s="15">
         <v>6.5</v>
@@ -2344,9 +2154,9 @@
       </c>
       <c r="E47" s="3"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>94</v>
+        <v>49</v>
       </c>
       <c r="B48">
         <v>5</v>
@@ -2356,9 +2166,9 @@
       </c>
       <c r="E48" s="3"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="B49">
         <v>5</v>
@@ -2368,9 +2178,9 @@
       </c>
       <c r="E49" s="3"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="B50">
         <v>5.5</v>
@@ -2380,9 +2190,9 @@
       </c>
       <c r="E50" s="3"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5">
       <c r="A51" s="16" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="B51" s="15">
         <v>6</v>
@@ -2392,9 +2202,9 @@
       </c>
       <c r="E51" s="3"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5">
       <c r="A52" s="15" t="s">
-        <v>101</v>
+        <v>53</v>
       </c>
       <c r="B52" s="15">
         <v>6</v>
@@ -2404,9 +2214,9 @@
       </c>
       <c r="E52" s="3"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5">
       <c r="A53" s="15" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="B53" s="15">
         <v>6</v>
@@ -2416,9 +2226,9 @@
       </c>
       <c r="E53" s="3"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="B54">
         <v>5.5</v>
@@ -2428,9 +2238,9 @@
       </c>
       <c r="E54" s="3"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5">
       <c r="A55" s="17" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="B55" s="15">
         <v>6</v>
@@ -2440,9 +2250,9 @@
       </c>
       <c r="E55" s="3"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="B56">
         <v>5.5</v>
@@ -2452,9 +2262,9 @@
       </c>
       <c r="E56" s="3"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>105</v>
+        <v>58</v>
       </c>
       <c r="B57">
         <v>5.5</v>
@@ -2464,9 +2274,9 @@
       </c>
       <c r="E57" s="3"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5">
       <c r="A58" s="3" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="B58">
         <v>5.8</v>
@@ -2476,9 +2286,9 @@
       </c>
       <c r="E58" s="3"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5">
       <c r="A59" s="3" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="B59">
         <v>5.8</v>
@@ -2488,9 +2298,9 @@
       </c>
       <c r="E59" s="3"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5">
       <c r="A60" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B60">
         <v>5.8</v>
@@ -2500,9 +2310,9 @@
       </c>
       <c r="E60" s="3"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5">
       <c r="A61" s="3" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="B61">
         <v>5.8</v>
@@ -2512,9 +2322,9 @@
       </c>
       <c r="E61" s="3"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5">
       <c r="A62" s="3" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="B62">
         <v>5.8</v>
@@ -2524,9 +2334,9 @@
       </c>
       <c r="E62" s="3"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5">
       <c r="A63" s="3" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="B63">
         <v>5.8</v>
@@ -2536,198 +2346,603 @@
       </c>
       <c r="E63" s="3"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5">
+      <c r="A64" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="B64" s="19">
+        <v>6.5</v>
+      </c>
+      <c r="C64" s="19">
+        <v>7.5</v>
+      </c>
       <c r="E64" s="3"/>
     </row>
-    <row r="65" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5">
+      <c r="A65" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B65" s="19">
+        <v>6</v>
+      </c>
+      <c r="C65" s="19">
+        <v>7</v>
+      </c>
       <c r="E65" s="3"/>
     </row>
-    <row r="66" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5">
+      <c r="A66" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="B66" s="19">
+        <v>6</v>
+      </c>
+      <c r="C66" s="19">
+        <v>7</v>
+      </c>
       <c r="E66" s="3"/>
     </row>
-    <row r="67" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5">
+      <c r="A67" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B67" s="19">
+        <v>6</v>
+      </c>
+      <c r="C67" s="19">
+        <v>8</v>
+      </c>
       <c r="E67" s="3"/>
     </row>
-    <row r="68" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5">
+      <c r="A68" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B68" s="19">
+        <v>5.5</v>
+      </c>
+      <c r="C68" s="19">
+        <v>7.5</v>
+      </c>
       <c r="E68" s="3"/>
     </row>
-    <row r="69" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5">
+      <c r="A69" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B69" s="19">
+        <v>5.5</v>
+      </c>
+      <c r="C69" s="19">
+        <v>7</v>
+      </c>
       <c r="E69" s="3"/>
     </row>
-    <row r="70" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5">
+      <c r="A70" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="B70" s="19">
+        <v>6</v>
+      </c>
+      <c r="C70" s="19">
+        <v>7.5</v>
+      </c>
       <c r="E70" s="3"/>
     </row>
-    <row r="71" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5">
+      <c r="A71" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B71" s="19">
+        <v>6</v>
+      </c>
+      <c r="C71" s="19">
+        <v>8</v>
+      </c>
       <c r="E71" s="3"/>
     </row>
-    <row r="72" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5">
+      <c r="A72" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="B72" s="19">
+        <v>6</v>
+      </c>
+      <c r="C72" s="19">
+        <v>8</v>
+      </c>
       <c r="E72" s="3"/>
     </row>
-    <row r="73" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5">
+      <c r="A73" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B73" s="19">
+        <v>5.5</v>
+      </c>
+      <c r="C73" s="19">
+        <v>6.5</v>
+      </c>
       <c r="E73" s="3"/>
     </row>
-    <row r="74" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5">
+      <c r="A74" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B74" s="19">
+        <v>6</v>
+      </c>
+      <c r="C74" s="19">
+        <v>7</v>
+      </c>
       <c r="E74" s="3"/>
     </row>
-    <row r="75" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5">
+      <c r="A75" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="B75" s="19">
+        <v>5.5</v>
+      </c>
+      <c r="C75" s="19">
+        <v>7.5</v>
+      </c>
       <c r="E75" s="3"/>
     </row>
-    <row r="76" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5">
+      <c r="A76" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="B76" s="19">
+        <v>6</v>
+      </c>
+      <c r="C76" s="19">
+        <v>7</v>
+      </c>
       <c r="E76" s="3"/>
     </row>
-    <row r="77" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5">
+      <c r="A77" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B77" s="19">
+        <v>6</v>
+      </c>
+      <c r="C77" s="19">
+        <v>7.5</v>
+      </c>
       <c r="E77" s="3"/>
     </row>
-    <row r="78" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5">
+      <c r="A78" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B78" s="22">
+        <v>6</v>
+      </c>
+      <c r="C78" s="22">
+        <v>7</v>
+      </c>
       <c r="E78" s="3"/>
     </row>
-    <row r="79" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5">
+      <c r="A79" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="B79" s="22">
+        <v>5.5</v>
+      </c>
+      <c r="C79" s="22">
+        <v>7.5</v>
+      </c>
       <c r="E79" s="3"/>
     </row>
-    <row r="80" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5">
+      <c r="A80" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="B80" s="22">
+        <v>4</v>
+      </c>
+      <c r="C80" s="22">
+        <v>5</v>
+      </c>
       <c r="E80" s="3"/>
     </row>
-    <row r="81" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5">
+      <c r="A81" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="B81" s="22">
+        <v>6.5</v>
+      </c>
+      <c r="C81" s="22">
+        <v>7</v>
+      </c>
       <c r="E81" s="3"/>
     </row>
-    <row r="82" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5">
+      <c r="A82" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B82" s="19">
+        <v>6</v>
+      </c>
+      <c r="C82" s="19">
+        <v>7.5</v>
+      </c>
       <c r="E82" s="3"/>
     </row>
-    <row r="83" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5">
+      <c r="A83" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B83" s="19">
+        <v>5.5</v>
+      </c>
+      <c r="C83" s="19">
+        <v>7</v>
+      </c>
       <c r="E83" s="3"/>
     </row>
-    <row r="84" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5">
+      <c r="A84" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B84" s="22">
+        <v>5.5</v>
+      </c>
+      <c r="C84" s="22">
+        <v>7.5</v>
+      </c>
       <c r="E84" s="3"/>
     </row>
-    <row r="85" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5">
+      <c r="A85" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="B85" s="19">
+        <v>5</v>
+      </c>
+      <c r="C85" s="19">
+        <v>6.5</v>
+      </c>
       <c r="E85" s="3"/>
     </row>
-    <row r="86" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5">
+      <c r="A86" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B86" s="19">
+        <v>5.5</v>
+      </c>
+      <c r="C86" s="19">
+        <v>6.5</v>
+      </c>
       <c r="E86" s="3"/>
     </row>
-    <row r="87" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5">
+      <c r="A87" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B87" s="19">
+        <v>6</v>
+      </c>
+      <c r="C87" s="19">
+        <v>7.5</v>
+      </c>
       <c r="E87" s="3"/>
     </row>
-    <row r="88" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5">
+      <c r="A88" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="B88" s="19">
+        <v>5</v>
+      </c>
+      <c r="C88" s="19">
+        <v>6.5</v>
+      </c>
       <c r="E88" s="3"/>
     </row>
-    <row r="89" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5">
+      <c r="A89" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B89" s="19">
+        <v>5.5</v>
+      </c>
+      <c r="C89" s="19">
+        <v>6.5</v>
+      </c>
       <c r="E89" s="3"/>
     </row>
-    <row r="90" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5">
+      <c r="A90" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B90" s="19">
+        <v>5</v>
+      </c>
+      <c r="C90" s="19">
+        <v>6</v>
+      </c>
       <c r="E90" s="3"/>
     </row>
-    <row r="91" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5">
+      <c r="A91" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="B91" s="19">
+        <v>5</v>
+      </c>
+      <c r="C91" s="19">
+        <v>6</v>
+      </c>
       <c r="E91" s="3"/>
     </row>
-    <row r="92" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5">
+      <c r="A92" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="B92" s="19">
+        <v>5.6</v>
+      </c>
+      <c r="C92" s="19">
+        <v>7.5</v>
+      </c>
       <c r="E92" s="3"/>
     </row>
-    <row r="93" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5">
+      <c r="A93" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="B93" s="19">
+        <v>6</v>
+      </c>
+      <c r="C93" s="19">
+        <v>7.5</v>
+      </c>
       <c r="E93" s="3"/>
     </row>
-    <row r="94" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5">
+      <c r="A94" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B94" s="19">
+        <v>6</v>
+      </c>
+      <c r="C94" s="19">
+        <v>7</v>
+      </c>
       <c r="E94" s="3"/>
     </row>
-    <row r="95" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5">
+      <c r="A95" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B95" s="19">
+        <v>5.5</v>
+      </c>
+      <c r="C95" s="19">
+        <v>6.5</v>
+      </c>
       <c r="E95" s="3"/>
     </row>
-    <row r="96" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5">
+      <c r="A96" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="B96" s="19">
+        <v>6</v>
+      </c>
+      <c r="C96" s="19">
+        <v>7.5</v>
+      </c>
       <c r="E96" s="3"/>
     </row>
-    <row r="97" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5">
+      <c r="A97" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B97" s="19">
+        <v>6</v>
+      </c>
+      <c r="C97" s="19">
+        <v>7.5</v>
+      </c>
       <c r="E97" s="3"/>
     </row>
-    <row r="98" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5">
+      <c r="A98" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B98" s="19">
+        <v>6</v>
+      </c>
+      <c r="C98" s="19">
+        <v>7.5</v>
+      </c>
       <c r="E98" s="3"/>
     </row>
-    <row r="99" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5">
+      <c r="A99" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="B99" s="19">
+        <v>6</v>
+      </c>
+      <c r="C99" s="19">
+        <v>7.5</v>
+      </c>
       <c r="E99" s="3"/>
     </row>
-    <row r="100" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5">
+      <c r="A100" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="B100" s="19">
+        <v>6</v>
+      </c>
+      <c r="C100" s="19">
+        <v>7.5</v>
+      </c>
       <c r="E100" s="3"/>
     </row>
-    <row r="101" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5">
+      <c r="A101" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B101" s="19">
+        <v>5.5</v>
+      </c>
+      <c r="C101" s="19">
+        <v>6</v>
+      </c>
       <c r="E101" s="3"/>
     </row>
-    <row r="102" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5">
+      <c r="A102" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="B102" s="19">
+        <v>5.5</v>
+      </c>
+      <c r="C102" s="19">
+        <v>7</v>
+      </c>
       <c r="E102" s="3"/>
     </row>
-    <row r="103" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5">
+      <c r="A103" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B103" s="19">
+        <v>4.5</v>
+      </c>
+      <c r="C103" s="19">
+        <v>7.5</v>
+      </c>
       <c r="E103" s="3"/>
     </row>
-    <row r="104" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5">
+      <c r="A104" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="B104" s="19">
+        <v>5</v>
+      </c>
+      <c r="C104" s="19">
+        <v>7.5</v>
+      </c>
       <c r="E104" s="3"/>
     </row>
-    <row r="105" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5">
+      <c r="A105" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="B105" s="19">
+        <v>4.5</v>
+      </c>
+      <c r="C105" s="19">
+        <v>7.5</v>
+      </c>
       <c r="E105" s="3"/>
     </row>
-    <row r="106" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5">
+      <c r="A106" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="B106" s="19">
+        <v>5</v>
+      </c>
+      <c r="C106" s="19">
+        <v>7.5</v>
+      </c>
       <c r="E106" s="3"/>
     </row>
-    <row r="107" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5">
+      <c r="A107" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="B107" s="19">
+        <v>5.5</v>
+      </c>
+      <c r="C107" s="19">
+        <v>7</v>
+      </c>
       <c r="E107" s="3"/>
     </row>
-    <row r="108" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5">
+      <c r="A108" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="B108" s="24">
+        <v>4.5</v>
+      </c>
+      <c r="C108" s="24">
+        <v>5.5</v>
+      </c>
       <c r="E108" s="3"/>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B109" s="19">
+        <v>5</v>
+      </c>
+      <c r="C109" s="19">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="B110" s="19">
+        <v>4.5</v>
+      </c>
+      <c r="C110" s="19">
+        <v>6.5</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A15:A17">
-    <cfRule type="duplicateValues" dxfId="62" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A51">
+    <cfRule type="duplicateValues" dxfId="39" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A58">
+    <cfRule type="duplicateValues" dxfId="37" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A59">
+    <cfRule type="duplicateValues" dxfId="34" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A60">
+    <cfRule type="duplicateValues" dxfId="31" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A61">
+    <cfRule type="duplicateValues" dxfId="28" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A62:A63">
+    <cfRule type="duplicateValues" dxfId="25" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18:G19">
-    <cfRule type="duplicateValues" dxfId="61" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A51">
-    <cfRule type="duplicateValues" dxfId="60" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A51">
-    <cfRule type="duplicateValues" dxfId="59" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A58">
-    <cfRule type="duplicateValues" dxfId="58" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A58">
-    <cfRule type="duplicateValues" dxfId="57" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A58">
-    <cfRule type="duplicateValues" dxfId="56" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A59">
-    <cfRule type="duplicateValues" dxfId="55" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A59">
-    <cfRule type="duplicateValues" dxfId="54" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A59">
-    <cfRule type="duplicateValues" dxfId="53" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A60">
-    <cfRule type="duplicateValues" dxfId="52" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A60">
-    <cfRule type="duplicateValues" dxfId="51" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A60">
-    <cfRule type="duplicateValues" dxfId="50" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A61">
-    <cfRule type="duplicateValues" dxfId="49" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A61">
-    <cfRule type="duplicateValues" dxfId="48" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A61">
-    <cfRule type="duplicateValues" dxfId="47" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A62:A63">
-    <cfRule type="duplicateValues" dxfId="46" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A62:A63">
-    <cfRule type="duplicateValues" dxfId="45" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A62:A63">
-    <cfRule type="duplicateValues" dxfId="44" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="22"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2736,25 +2951,25 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="15" customHeight="1">
       <c r="A1" s="7" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1">
       <c r="A2" s="8">
         <v>0</v>
       </c>
@@ -2765,7 +2980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="15" customHeight="1">
       <c r="A3" s="8">
         <v>1</v>
       </c>
@@ -2776,7 +2991,7 @@
         <v>5.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="15" customHeight="1">
       <c r="A4" s="8">
         <v>2</v>
       </c>
@@ -2787,7 +3002,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="15" customHeight="1">
       <c r="A5" s="8">
         <v>3</v>
       </c>
@@ -2798,10 +3013,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="15" customHeight="1">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="15" customHeight="1">
       <c r="A8" s="4"/>
     </row>
   </sheetData>
@@ -2813,116 +3028,116 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="15" customHeight="1">
       <c r="A1" s="7" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1">
       <c r="A2" s="9" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="B2" s="3">
         <v>0.99399999999999999</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1">
       <c r="A3" s="9" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="B3" s="3">
         <v>3.6950899999999999E-5</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="B4" s="3">
         <v>11.628251000000001</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B5" s="3">
         <v>-1.1878</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="B6" s="3">
         <v>-8.4931999999999999</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="B8" s="3">
         <v>0.99399999999999999</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" customHeight="1">
       <c r="A10" s="10"/>
     </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="15" customHeight="1">
       <c r="A11" s="4"/>
     </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="15" customHeight="1">
       <c r="A12" s="4"/>
     </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="15" customHeight="1">
       <c r="A13" s="4"/>
     </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="15" customHeight="1">
       <c r="A14" s="4"/>
     </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="15" customHeight="1">
       <c r="A15" s="4"/>
     </row>
   </sheetData>
@@ -2934,61 +3149,61 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="11" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="12">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="12">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="12">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" s="12">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" s="12">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" s="4"/>
     </row>
   </sheetData>
@@ -3000,26 +3215,26 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>177</v>
-      </c>
       <c r="C1" s="11" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="12" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="B2" s="3">
         <v>1.0541326</v>
@@ -3028,9 +3243,9 @@
         <v>-9.8126979999999999E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" s="12" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="B3" s="3">
         <v>1.0744899999999999</v>
@@ -3039,16 +3254,16 @@
         <v>-1.3431848999999999E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" s="13"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" s="4"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" s="4"/>
     </row>
   </sheetData>
@@ -3060,7 +3275,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BAE779D-EE07-4BAA-A5AD-49FE70D75EAE}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3069,7 +3284,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E172"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
@@ -3077,29 +3292,29 @@
     <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>113</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>114</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>115</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15" customHeight="1">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="C2" s="3">
         <v>23</v>
@@ -3112,12 +3327,12 @@
         <v>521.4312698</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="15" customHeight="1">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="C3" s="3">
         <v>19</v>
@@ -3130,12 +3345,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="15" customHeight="1">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3">
         <v>19</v>
@@ -3148,12 +3363,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="15" customHeight="1">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="C5" s="3">
         <v>19</v>
@@ -3166,12 +3381,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="15" customHeight="1">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="C6" s="3">
         <v>19</v>
@@ -3184,12 +3399,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="15" customHeight="1">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C7" s="3">
         <v>19</v>
@@ -3202,12 +3417,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="15" customHeight="1">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C8" s="3">
         <v>19</v>
@@ -3220,12 +3435,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="15" customHeight="1">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C9" s="3">
         <v>19</v>
@@ -3238,12 +3453,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="15" customHeight="1">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C10" s="3">
         <v>20</v>
@@ -3256,12 +3471,12 @@
         <v>343.20422000000008</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="15" customHeight="1">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="C11" s="3">
         <v>19</v>
@@ -3274,12 +3489,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="15" customHeight="1">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="C12" s="3">
         <v>19</v>
@@ -3292,12 +3507,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="15" customHeight="1">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C13" s="3">
         <v>19</v>
@@ -3310,12 +3525,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="15" customHeight="1">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C14" s="3">
         <v>19</v>
@@ -3328,12 +3543,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="15" customHeight="1">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="C15" s="3">
         <v>19</v>
@@ -3346,12 +3561,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="15" customHeight="1">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="C16" s="3">
         <v>12</v>
@@ -3364,12 +3579,12 @@
         <v>70.512592799999993</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="15" customHeight="1">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="C17" s="3">
         <v>12</v>
@@ -3382,12 +3597,12 @@
         <v>70.512592799999993</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="15" customHeight="1">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="C18" s="3">
         <v>19</v>
@@ -3400,12 +3615,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" ht="15" customHeight="1">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="C19" s="3">
         <v>19</v>
@@ -3418,12 +3633,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" ht="15" customHeight="1">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C20" s="3">
         <v>19</v>
@@ -3436,12 +3651,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" ht="15" customHeight="1">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C21" s="3">
         <v>19</v>
@@ -3454,12 +3669,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="15" customHeight="1">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C22" s="3">
         <v>19</v>
@@ -3472,12 +3687,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" ht="15" customHeight="1">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C23" s="3">
         <v>19</v>
@@ -3490,12 +3705,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" ht="15" customHeight="1">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="C24" s="3">
         <v>19</v>
@@ -3508,12 +3723,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" ht="15" customHeight="1">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="C25" s="3">
         <v>19</v>
@@ -3526,12 +3741,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" ht="15" customHeight="1">
       <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="C26" s="3">
         <v>19</v>
@@ -3544,12 +3759,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" ht="15" customHeight="1">
       <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="C27" s="3">
         <v>19</v>
@@ -3562,12 +3777,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" ht="15" customHeight="1">
       <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>31</v>
+        <v>117</v>
       </c>
       <c r="C28" s="3">
         <v>20</v>
@@ -3580,12 +3795,12 @@
         <v>343.20422000000008</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" ht="15" customHeight="1">
       <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="C29" s="3">
         <v>22</v>
@@ -3598,12 +3813,12 @@
         <v>457.41815080000003</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" ht="15" customHeight="1">
       <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="C30" s="3">
         <v>19</v>
@@ -3616,12 +3831,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" ht="15" customHeight="1">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C31" s="3">
         <v>16</v>
@@ -3634,12 +3849,12 @@
         <v>170.02558720000002</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" ht="15" customHeight="1">
       <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="C32" s="3">
         <v>19</v>
@@ -3652,12 +3867,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" ht="15" customHeight="1">
       <c r="A33" s="2">
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="C33" s="3">
         <v>19</v>
@@ -3670,12 +3885,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" ht="15" customHeight="1">
       <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="C34" s="3">
         <v>19</v>
@@ -3688,12 +3903,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" ht="15" customHeight="1">
       <c r="A35" s="2">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C35" s="3">
         <v>19</v>
@@ -3706,12 +3921,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" ht="15" customHeight="1">
       <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="C36" s="3">
         <v>19</v>
@@ -3724,12 +3939,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="15" customHeight="1">
       <c r="A37" s="2">
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="C37" s="3">
         <v>19</v>
@@ -3742,12 +3957,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" ht="15" customHeight="1">
       <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="C38" s="3">
         <v>19</v>
@@ -3760,12 +3975,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" ht="15" customHeight="1">
       <c r="A39" s="2">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C39" s="3">
         <v>19</v>
@@ -3778,12 +3993,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" ht="15" customHeight="1">
       <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="C40" s="3">
         <v>12</v>
@@ -3796,12 +4011,12 @@
         <v>70.512592799999993</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" ht="15" customHeight="1">
       <c r="A41" s="2">
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="C41" s="3">
         <v>19</v>
@@ -3814,12 +4029,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" ht="15" customHeight="1">
       <c r="A42" s="2">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="C42" s="3">
         <v>19</v>
@@ -3832,12 +4047,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" ht="15" customHeight="1">
       <c r="A43" s="2">
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C43" s="3">
         <v>19</v>
@@ -3850,12 +4065,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" ht="15" customHeight="1">
       <c r="A44" s="2">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="C44" s="3">
         <v>19</v>
@@ -3868,12 +4083,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" ht="15" customHeight="1">
       <c r="A45" s="2">
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="C45" s="3">
         <v>19</v>
@@ -3886,12 +4101,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" ht="15" customHeight="1">
       <c r="A46" s="2">
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="C46" s="3">
         <v>19</v>
@@ -3904,12 +4119,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" ht="15" customHeight="1">
       <c r="A47" s="2">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="C47" s="3">
         <v>19</v>
@@ -3922,12 +4137,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" ht="15" customHeight="1">
       <c r="A48" s="2">
         <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="C48" s="3">
         <v>12</v>
@@ -3940,12 +4155,12 @@
         <v>70.512592799999993</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" ht="15" customHeight="1">
       <c r="A49" s="2">
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="C49" s="3">
         <v>19</v>
@@ -3958,12 +4173,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" ht="15" customHeight="1">
       <c r="A50" s="2">
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="C50" s="3">
         <v>19</v>
@@ -3976,12 +4191,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" ht="15" customHeight="1">
       <c r="A51" s="2">
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="C51" s="3">
         <v>19</v>
@@ -3994,12 +4209,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" ht="15" customHeight="1">
       <c r="A52" s="2">
         <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="C52" s="3">
         <v>19</v>
@@ -4012,12 +4227,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" ht="15" customHeight="1">
       <c r="A53" s="2">
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="C53" s="3">
         <v>19</v>
@@ -4030,12 +4245,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" ht="15" customHeight="1">
       <c r="A54" s="2">
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="C54" s="3">
         <v>19</v>
@@ -4048,12 +4263,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" ht="15" customHeight="1">
       <c r="A55" s="2">
         <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="C55" s="3">
         <v>19</v>
@@ -4066,12 +4281,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" ht="15" customHeight="1">
       <c r="A56" s="2">
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="C56" s="3">
         <v>19</v>
@@ -4084,12 +4299,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" ht="15" customHeight="1">
       <c r="A57" s="2">
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="C57" s="3">
         <v>19</v>
@@ -4102,12 +4317,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" ht="15" customHeight="1">
       <c r="A58" s="2">
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C58" s="3">
         <v>19</v>
@@ -4120,12 +4335,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" ht="15" customHeight="1">
       <c r="A59" s="2">
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="C59" s="3">
         <v>19</v>
@@ -4138,12 +4353,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" ht="15" customHeight="1">
       <c r="A60" s="2">
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C60" s="3">
         <v>20</v>
@@ -4156,12 +4371,12 @@
         <v>343.20422000000008</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" ht="15" customHeight="1">
       <c r="A61" s="2">
         <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="C61" s="3">
         <v>19</v>
@@ -4174,12 +4389,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" ht="15" customHeight="1">
       <c r="A62" s="2">
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="C62" s="3">
         <v>19</v>
@@ -4192,12 +4407,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" ht="15" customHeight="1">
       <c r="A63" s="2">
         <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="C63" s="3">
         <v>19</v>
@@ -4210,12 +4425,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" ht="15" customHeight="1">
       <c r="A64" s="2">
         <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="C64" s="3">
         <v>19</v>
@@ -4228,12 +4443,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" ht="15" customHeight="1">
       <c r="A65" s="2">
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="C65" s="3">
         <v>19</v>
@@ -4246,12 +4461,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" ht="15" customHeight="1">
       <c r="A66" s="2">
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="C66" s="3">
         <v>19</v>
@@ -4264,12 +4479,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" ht="15" customHeight="1">
       <c r="A67" s="2">
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="C67" s="3">
         <v>19</v>
@@ -4282,12 +4497,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" ht="15" customHeight="1">
       <c r="A68" s="2">
         <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="C68" s="3">
         <v>19</v>
@@ -4300,12 +4515,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" ht="15" customHeight="1">
       <c r="A69" s="2">
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="C69" s="3">
         <v>19</v>
@@ -4318,12 +4533,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" ht="15" customHeight="1">
       <c r="A70" s="2">
         <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="C70" s="3">
         <v>19</v>
@@ -4336,12 +4551,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" ht="15" customHeight="1">
       <c r="A71" s="2">
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="C71" s="3">
         <v>19</v>
@@ -4354,12 +4569,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" ht="15" customHeight="1">
       <c r="A72" s="2">
         <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C72" s="3">
         <v>19</v>
@@ -4372,12 +4587,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" ht="15" customHeight="1">
       <c r="A73" s="2">
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C73" s="3">
         <v>19</v>
@@ -4390,12 +4605,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" ht="15" customHeight="1">
       <c r="A74" s="2">
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="C74" s="3">
         <v>19</v>
@@ -4408,12 +4623,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" ht="15" customHeight="1">
       <c r="A75" s="2">
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="C75" s="3">
         <v>19</v>
@@ -4426,12 +4641,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" ht="15" customHeight="1">
       <c r="A76" s="2">
         <v>75</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="C76" s="3">
         <v>19</v>
@@ -4444,12 +4659,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" ht="15" customHeight="1">
       <c r="A77" s="2">
         <v>76</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="C77" s="3">
         <v>19</v>
@@ -4462,12 +4677,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" ht="15" customHeight="1">
       <c r="A78" s="2">
         <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="C78" s="3">
         <v>19</v>
@@ -4480,12 +4695,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" ht="15" customHeight="1">
       <c r="A79" s="2">
         <v>78</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="C79" s="3">
         <v>19</v>
@@ -4498,12 +4713,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" ht="15" customHeight="1">
       <c r="A80" s="2">
         <v>79</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C80" s="3">
         <v>16</v>
@@ -4516,12 +4731,12 @@
         <v>170.02558720000002</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" ht="15" customHeight="1">
       <c r="A81" s="2">
         <v>80</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="C81" s="3">
         <v>20</v>
@@ -4534,12 +4749,12 @@
         <v>343.20422000000008</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" ht="15" customHeight="1">
       <c r="A82" s="2">
         <v>81</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="C82" s="3">
         <v>19</v>
@@ -4552,12 +4767,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" ht="15" customHeight="1">
       <c r="A83" s="2">
         <v>82</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="C83" s="3">
         <v>16</v>
@@ -4570,12 +4785,12 @@
         <v>170.02558720000002</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" ht="15" customHeight="1">
       <c r="A84" s="2">
         <v>83</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="C84" s="3">
         <v>19</v>
@@ -4588,12 +4803,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" ht="15" customHeight="1">
       <c r="A85" s="2">
         <v>84</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="C85" s="3">
         <v>19</v>
@@ -4606,12 +4821,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" ht="15" customHeight="1">
       <c r="A86" s="2">
         <v>85</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="C86" s="3">
         <v>19</v>
@@ -4624,12 +4839,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" ht="15" customHeight="1">
       <c r="A87" s="2">
         <v>86</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C87" s="3">
         <v>19</v>
@@ -4642,12 +4857,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" ht="15" customHeight="1">
       <c r="A88" s="2">
         <v>87</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="C88" s="3">
         <v>19</v>
@@ -4660,12 +4875,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" ht="15" customHeight="1">
       <c r="A89" s="2">
         <v>88</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="C89" s="3">
         <v>19</v>
@@ -4678,12 +4893,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" ht="15" customHeight="1">
       <c r="A90" s="2">
         <v>89</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="C90" s="3">
         <v>19</v>
@@ -4696,12 +4911,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" ht="15" customHeight="1">
       <c r="A91" s="2">
         <v>90</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>94</v>
+        <v>49</v>
       </c>
       <c r="C91" s="3">
         <v>19</v>
@@ -4714,12 +4929,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" ht="15" customHeight="1">
       <c r="A92" s="2">
         <v>91</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="C92" s="3">
         <v>20</v>
@@ -4732,12 +4947,12 @@
         <v>343.20422000000008</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" ht="15" customHeight="1">
       <c r="A93" s="2">
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="C93" s="3">
         <v>19</v>
@@ -4750,12 +4965,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" ht="15" customHeight="1">
       <c r="A94" s="2">
         <v>93</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="C94" s="3">
         <v>24</v>
@@ -4768,12 +4983,12 @@
         <v>590.04849120000006</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" ht="15" customHeight="1">
       <c r="A95" s="2">
         <v>94</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="C95" s="3">
         <v>19</v>
@@ -4786,12 +5001,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" ht="15" customHeight="1">
       <c r="A96" s="2">
         <v>95</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C96" s="3">
         <v>19</v>
@@ -4804,12 +5019,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" ht="15" customHeight="1">
       <c r="A97" s="2">
         <v>96</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C97" s="3">
         <v>19</v>
@@ -4822,12 +5037,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" ht="15" customHeight="1">
       <c r="A98" s="2">
         <v>97</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>101</v>
+        <v>53</v>
       </c>
       <c r="C98" s="3">
         <v>19</v>
@@ -4840,12 +5055,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" ht="15" customHeight="1">
       <c r="A99" s="2">
         <v>98</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="C99" s="3">
         <v>19</v>
@@ -4858,12 +5073,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" ht="15" customHeight="1">
       <c r="A100" s="2">
         <v>99</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="C100" s="3">
         <v>19</v>
@@ -4876,12 +5091,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" ht="15" customHeight="1">
       <c r="A101" s="2">
         <v>100</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="C101" s="3">
         <v>21</v>
@@ -4894,12 +5109,12 @@
         <v>398.00913420000006</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" ht="15" customHeight="1">
       <c r="A102" s="2">
         <v>101</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>105</v>
+        <v>58</v>
       </c>
       <c r="C102" s="3">
         <v>21</v>
@@ -4912,12 +5127,12 @@
         <v>398.00913420000006</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" ht="15" customHeight="1">
       <c r="A103" s="2">
         <v>102</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="C103" s="3">
         <v>19</v>
@@ -4930,12 +5145,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" ht="15" customHeight="1">
       <c r="A104" s="2">
         <v>103</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C104" s="3">
         <v>19</v>
@@ -4948,12 +5163,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" ht="15" customHeight="1">
       <c r="A105" s="2">
         <v>104</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C105" s="3">
         <v>19</v>
@@ -4966,12 +5181,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" ht="15" customHeight="1">
       <c r="A106" s="2">
         <v>105</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C106" s="3">
         <v>19</v>
@@ -4984,12 +5199,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" ht="15" customHeight="1">
       <c r="A107" s="2">
         <v>106</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C107" s="3">
         <v>19</v>
@@ -5002,171 +5217,160 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="4"/>
-    </row>
-    <row r="110" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5">
+      <c r="A108" s="25">
+        <v>107</v>
+      </c>
+      <c r="B108" s="26" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="15" customHeight="1">
+      <c r="A109" s="25">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="15" customHeight="1">
       <c r="A110" s="4"/>
     </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:2">
       <c r="B115" s="15"/>
     </row>
-    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:2">
       <c r="B117" s="15"/>
     </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:2">
       <c r="B118" s="15"/>
     </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:2">
       <c r="B120" s="15"/>
     </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:2">
       <c r="B122" s="15"/>
     </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:2">
       <c r="B123" s="15"/>
     </row>
-    <row r="124" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:2">
       <c r="B124" s="3"/>
     </row>
-    <row r="125" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:2">
       <c r="B125" s="3"/>
     </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:2">
       <c r="B126" s="3"/>
     </row>
-    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:2">
       <c r="B127" s="15"/>
     </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:2">
       <c r="B130" s="15"/>
     </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:2">
       <c r="B131" s="15"/>
     </row>
-    <row r="133" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:2">
       <c r="B133" s="15"/>
     </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:2">
       <c r="B134" s="15"/>
     </row>
-    <row r="136" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:2">
       <c r="B136" s="15"/>
     </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:2">
       <c r="B138" s="15"/>
     </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:2">
       <c r="B139" s="15"/>
     </row>
-    <row r="141" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:2">
       <c r="B141" s="15"/>
     </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:2">
       <c r="B149" s="15"/>
     </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:2">
       <c r="B151" s="15"/>
     </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:2">
       <c r="B156" s="15"/>
     </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:2">
       <c r="B160" s="16"/>
     </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:2">
       <c r="B161" s="15"/>
     </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:2">
       <c r="B162" s="15"/>
     </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:2">
       <c r="B164" s="17"/>
     </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:2">
       <c r="B167" s="3"/>
     </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:2">
       <c r="B168" s="3"/>
     </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:2">
       <c r="B169" s="3"/>
     </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:2">
       <c r="B170" s="3"/>
     </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:2">
       <c r="B171" s="3"/>
     </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:2">
       <c r="B172" s="3"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B173:B1048576 B1:B110 I12">
-    <cfRule type="duplicateValues" dxfId="43" priority="25"/>
+  <conditionalFormatting sqref="B173:B1048576 I12 B1:B110">
+    <cfRule type="duplicateValues" dxfId="21" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B173:B1048576 B1:B110 I12">
-    <cfRule type="duplicateValues" dxfId="42" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B110 B173:B1048576 I12">
-    <cfRule type="duplicateValues" dxfId="41" priority="20"/>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="20" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B124:B126">
-    <cfRule type="duplicateValues" dxfId="40" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B160">
-    <cfRule type="duplicateValues" dxfId="39" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B160">
-    <cfRule type="duplicateValues" dxfId="38" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B167">
-    <cfRule type="duplicateValues" dxfId="37" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B167">
-    <cfRule type="duplicateValues" dxfId="36" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B167">
-    <cfRule type="duplicateValues" dxfId="35" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B168">
-    <cfRule type="duplicateValues" dxfId="34" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B168">
-    <cfRule type="duplicateValues" dxfId="33" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B168">
-    <cfRule type="duplicateValues" dxfId="32" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B169">
-    <cfRule type="duplicateValues" dxfId="31" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B169">
-    <cfRule type="duplicateValues" dxfId="30" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B169">
-    <cfRule type="duplicateValues" dxfId="29" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B170">
-    <cfRule type="duplicateValues" dxfId="28" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B170">
-    <cfRule type="duplicateValues" dxfId="27" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B170">
-    <cfRule type="duplicateValues" dxfId="26" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171:B172">
-    <cfRule type="duplicateValues" dxfId="25" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B171:B172">
-    <cfRule type="duplicateValues" dxfId="24" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B171:B172">
-    <cfRule type="duplicateValues" dxfId="23" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="B173:B1048576 I12 B1:B110">
+    <cfRule type="duplicateValues" dxfId="1" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -5176,25 +5380,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -5205,7 +5409,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="15" customHeight="1">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -5216,7 +5420,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="15" customHeight="1">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -5227,7 +5431,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="15" customHeight="1">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -5238,7 +5442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="15" customHeight="1">
       <c r="A6" s="2">
         <v>2</v>
       </c>
@@ -5249,7 +5453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="15" customHeight="1">
       <c r="A7" s="2">
         <v>2</v>
       </c>
@@ -5260,7 +5464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="15" customHeight="1">
       <c r="A8" s="2">
         <v>3</v>
       </c>
@@ -5271,7 +5475,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="15" customHeight="1">
       <c r="A9" s="2">
         <v>3</v>
       </c>
@@ -5282,7 +5486,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="15" customHeight="1">
       <c r="A10" s="2">
         <v>3</v>
       </c>
@@ -5293,7 +5497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="15" customHeight="1">
       <c r="A11" s="2">
         <v>4</v>
       </c>
@@ -5304,7 +5508,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="15" customHeight="1">
       <c r="A12" s="2">
         <v>4</v>
       </c>
@@ -5315,7 +5519,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="15" customHeight="1">
       <c r="A13" s="2">
         <v>4</v>
       </c>
@@ -5326,7 +5530,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="15" customHeight="1">
       <c r="A14" s="2">
         <v>5</v>
       </c>
@@ -5337,7 +5541,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="15" customHeight="1">
       <c r="A15" s="2">
         <v>5</v>
       </c>
@@ -5348,7 +5552,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="15" customHeight="1">
       <c r="A16" s="2">
         <v>5</v>
       </c>
@@ -5359,7 +5563,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="15" customHeight="1">
       <c r="A17" s="2">
         <v>6</v>
       </c>
@@ -5370,7 +5574,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="15" customHeight="1">
       <c r="A18" s="2">
         <v>6</v>
       </c>
@@ -5381,7 +5585,7 @@
         <v>3.66</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="15" customHeight="1">
       <c r="A19" s="2">
         <v>6</v>
       </c>
@@ -5392,10 +5596,10 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="15" customHeight="1">
       <c r="A21" s="4"/>
     </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="15" customHeight="1">
       <c r="A22" s="4"/>
     </row>
   </sheetData>
@@ -5407,58 +5611,58 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" customHeight="1">
       <c r="A6" s="4"/>
     </row>
   </sheetData>
@@ -5470,32 +5674,32 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" customHeight="1">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="C2" s="3">
         <v>0.125</v>
@@ -5504,12 +5708,12 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15" customHeight="1">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="C3" s="3">
         <v>2.5000000000000001E-2</v>
@@ -5518,12 +5722,12 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15" customHeight="1">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="C4" s="3">
         <v>1.7500000000000002E-2</v>
@@ -5532,12 +5736,12 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15" customHeight="1">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="C5" s="3">
         <v>0.01</v>
@@ -5546,10 +5750,10 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15" customHeight="1">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15" customHeight="1">
       <c r="A8" s="4"/>
     </row>
   </sheetData>
@@ -5561,33 +5765,33 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="70" customWidth="1"/>
     <col min="3" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" customHeight="1">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="C2" s="3">
         <v>0.98</v>
@@ -5596,12 +5800,12 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15" customHeight="1">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C3" s="3">
         <v>0.99</v>
@@ -5610,12 +5814,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15" customHeight="1">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="C4" s="3">
         <v>1</v>
@@ -5624,12 +5828,12 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15" customHeight="1">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="C5" s="3">
         <v>1.01</v>
@@ -5638,12 +5842,12 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15" customHeight="1">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C6" s="3">
         <v>1.03</v>
@@ -5652,7 +5856,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15" customHeight="1">
       <c r="A8" s="4"/>
     </row>
   </sheetData>
@@ -5664,33 +5868,33 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" customHeight="1">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C2" s="3">
         <v>160</v>
@@ -5699,12 +5903,12 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15" customHeight="1">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="C3" s="3">
         <v>140</v>
@@ -5713,12 +5917,12 @@
         <v>90000</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15" customHeight="1">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="C4" s="3">
         <v>115</v>
@@ -5727,12 +5931,12 @@
         <v>70000</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15" customHeight="1">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="C5" s="3">
         <v>85</v>
@@ -5741,12 +5945,12 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15" customHeight="1">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="C6" s="3">
         <v>60</v>
@@ -5755,10 +5959,10 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15" customHeight="1">
       <c r="A8" s="4"/>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15" customHeight="1">
       <c r="A9" s="4"/>
     </row>
   </sheetData>
@@ -5770,167 +5974,167 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="B2" s="3">
         <v>9.2499999999999995E-6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="B3" s="3">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="B4" s="3">
         <v>3.06</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="B6" s="3">
         <v>4.5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="B7" s="3">
         <v>-2</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" customHeight="1">
       <c r="A8" s="5" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="B8" s="3">
         <v>213.96744000000001</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="B9" s="3">
         <v>-39.579185000000003</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" customHeight="1">
       <c r="A10" s="5" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="B10" s="3">
         <v>2.3020512000000002</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="B11" s="3">
         <v>0</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15" customHeight="1">
       <c r="A12" s="5" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="B12" s="3">
         <v>1</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15" customHeight="1">
       <c r="A14" s="6"/>
     </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="15" customHeight="1">
       <c r="A15" s="4"/>
     </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="15" customHeight="1">
       <c r="A16" s="4"/>
     </row>
-    <row r="17" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" ht="15" customHeight="1">
       <c r="A17" s="4"/>
     </row>
-    <row r="18" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="15" customHeight="1">
       <c r="A18" s="4"/>
     </row>
-    <row r="19" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" ht="15" customHeight="1">
       <c r="A19" s="4"/>
     </row>
-    <row r="20" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" ht="15" customHeight="1">
       <c r="A20" s="4"/>
     </row>
-    <row r="21" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" ht="15" customHeight="1">
       <c r="A21" s="4"/>
     </row>
   </sheetData>
@@ -5942,7 +6146,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
@@ -5950,27 +6154,27 @@
     <col min="5" max="6" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="15" customHeight="1">
       <c r="A1" s="7" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>116</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15" customHeight="1">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -5990,7 +6194,7 @@
         <v>-12.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="8">
         <v>2</v>
       </c>
@@ -6010,7 +6214,7 @@
         <v>-12.061</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="15" customHeight="1">
       <c r="A4" s="8">
         <v>3</v>
       </c>
@@ -6030,7 +6234,7 @@
         <v>-11.297000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="15" customHeight="1">
       <c r="A5" s="8">
         <v>4</v>
       </c>
@@ -6050,7 +6254,7 @@
         <v>-10.79</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="15" customHeight="1">
       <c r="A6" s="8">
         <v>5</v>
       </c>
@@ -6070,13 +6274,13 @@
         <v>-10.1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="15" customHeight="1">
       <c r="A8" s="4"/>
     </row>
-    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="15" customHeight="1">
       <c r="A9" s="4"/>
     </row>
-    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="15" customHeight="1">
       <c r="A10" s="4"/>
     </row>
   </sheetData>

--- a/SMAF_lookup.xlsx
+++ b/SMAF_lookup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uflorida-my.sharepoint.com/personal/mohkam_singh_ufl_edu/Documents/Mohkam Singh - WORDLY/Research Projects/PhD Research/gSHAPE/SMAF for gSHAPE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A4D5D69C-A193-448A-9D17-6DCFDECF773D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{39853F55-285A-4AB7-8616-A9DF61BA0260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ph_factors" sheetId="14" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="201">
   <si>
     <t>Clean crop name</t>
   </si>
@@ -387,7 +387,7 @@
     <t>teff</t>
   </si>
   <si>
-    <t>eucalytus</t>
+    <t>eucalyptus</t>
   </si>
   <si>
     <t>crop_code</t>
@@ -5224,6 +5224,16 @@
       <c r="B108" s="26" t="s">
         <v>110</v>
       </c>
+      <c r="C108" s="3">
+        <v>21</v>
+      </c>
+      <c r="D108" s="3">
+        <v>27</v>
+      </c>
+      <c r="E108" s="3">
+        <f t="shared" ref="E108" si="4">213.96744-39.579185*C108+2.3020512*C108^2</f>
+        <v>398.00913420000006</v>
+      </c>
     </row>
     <row r="109" spans="1:5" ht="15" customHeight="1">
       <c r="A109" s="25">
@@ -5232,9 +5242,33 @@
       <c r="B109" t="s">
         <v>108</v>
       </c>
+      <c r="C109" s="3">
+        <v>19</v>
+      </c>
+      <c r="D109" s="3">
+        <v>25</v>
+      </c>
+      <c r="E109" s="3">
+        <f t="shared" ref="E109" si="5">213.96744-39.579185*C109+2.3020512*C109^2</f>
+        <v>293.00340819999997</v>
+      </c>
     </row>
     <row r="110" spans="1:5" ht="15" customHeight="1">
-      <c r="A110" s="4"/>
+      <c r="A110" s="25">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>111</v>
+      </c>
+      <c r="C110">
+        <v>19</v>
+      </c>
+      <c r="D110">
+        <v>25</v>
+      </c>
+      <c r="E110">
+        <v>293.00340819999997</v>
+      </c>
     </row>
     <row r="115" spans="2:2">
       <c r="B115" s="15"/>

--- a/SMAF_lookup.xlsx
+++ b/SMAF_lookup.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30317"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uflorida-my.sharepoint.com/personal/mohkam_singh_ufl_edu/Documents/Mohkam Singh - WORDLY/Research Projects/PhD Research/gSHAPE/SMAF for gSHAPE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohkam.singh\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C16A6451-5FD5-48A6-AC8C-4C7CBED5ADEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2208D0-B078-43A6-B2A8-D24E8CF1EF12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="10140" windowHeight="10170" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ph_factors" sheetId="14" r:id="rId1"/>
@@ -88,18 +88,9 @@
     <t>banana</t>
   </si>
   <si>
-    <t>barley, malt barley</t>
-  </si>
-  <si>
-    <t>beans, dried</t>
-  </si>
-  <si>
     <t>beet, red</t>
   </si>
   <si>
-    <t>bermuda grass, coastal</t>
-  </si>
-  <si>
     <t>blackberry</t>
   </si>
   <si>
@@ -187,9 +178,6 @@
     <t>fescue, tall</t>
   </si>
   <si>
-    <t>flaxseed; flax</t>
-  </si>
-  <si>
     <t>foxtail, meadow</t>
   </si>
   <si>
@@ -259,9 +247,6 @@
     <t>papaya</t>
   </si>
   <si>
-    <t>pea, field; peas</t>
-  </si>
-  <si>
     <t>peach</t>
   </si>
   <si>
@@ -322,9 +307,6 @@
     <t>sorghum</t>
   </si>
   <si>
-    <t>sorghum, grain sorghum</t>
-  </si>
-  <si>
     <t>soybean</t>
   </si>
   <si>
@@ -388,9 +370,6 @@
     <t>wheat, spring</t>
   </si>
   <si>
-    <t>winter wheat</t>
-  </si>
-  <si>
     <t>zucchini</t>
   </si>
   <si>
@@ -647,13 +626,34 @@
   </si>
   <si>
     <t>b</t>
+  </si>
+  <si>
+    <t>barley</t>
+  </si>
+  <si>
+    <t>beans</t>
+  </si>
+  <si>
+    <t>flaxseed</t>
+  </si>
+  <si>
+    <t>peas</t>
+  </si>
+  <si>
+    <t>sorghum, grain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wheat, winter </t>
+  </si>
+  <si>
+    <t>bermuda grass</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -741,6 +741,11 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="11">
@@ -832,7 +837,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -884,21 +889,32 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="43">
+  <dxfs count="44">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1590,13 +1606,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF1CC01C-BF2E-442A-817B-F6A0C0A3903D}">
   <dimension ref="A1:G110"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75">
+    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -1607,7 +1623,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
         <v>3</v>
       </c>
@@ -1619,7 +1635,7 @@
       </c>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="18" t="s">
         <v>4</v>
       </c>
@@ -1631,7 +1647,7 @@
       </c>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1643,7 +1659,7 @@
       </c>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="18" t="s">
         <v>6</v>
       </c>
@@ -1655,7 +1671,7 @@
       </c>
       <c r="G5" s="3"/>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="18" t="s">
         <v>7</v>
       </c>
@@ -1667,7 +1683,7 @@
       </c>
       <c r="G6" s="3"/>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1679,7 +1695,7 @@
       </c>
       <c r="G7" s="3"/>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1690,9 +1706,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>190</v>
       </c>
       <c r="B9">
         <v>5.5</v>
@@ -1701,9 +1717,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="15" t="s">
-        <v>11</v>
+        <v>191</v>
       </c>
       <c r="B10" s="15">
         <v>6</v>
@@ -1712,9 +1728,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="18" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B11" s="17">
         <v>5.5</v>
@@ -1723,9 +1739,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="25" t="s">
-        <v>13</v>
+        <v>196</v>
       </c>
       <c r="B12">
         <v>5.8</v>
@@ -1734,9 +1750,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="18" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B13" s="17">
         <v>5.5</v>
@@ -1745,9 +1761,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B14">
         <v>4.3</v>
@@ -1756,9 +1772,9 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="27" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B15" s="17">
         <v>6</v>
@@ -1767,9 +1783,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="27" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B16" s="17">
         <v>6</v>
@@ -1778,9 +1794,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="27" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B17" s="17">
         <v>6</v>
@@ -1789,9 +1805,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="18" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B18" s="17">
         <v>5.5</v>
@@ -1802,9 +1818,9 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="18" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B19" s="17">
         <v>6</v>
@@ -1815,9 +1831,9 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="15" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B20" s="15">
         <v>5.5</v>
@@ -1826,9 +1842,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B21">
         <v>5.5</v>
@@ -1837,9 +1853,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="15" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B22" s="15">
         <v>6.2</v>
@@ -1848,9 +1864,9 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B23">
         <v>5.5</v>
@@ -1859,9 +1875,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="17" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B24" s="17">
         <v>5.5</v>
@@ -1870,9 +1886,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="18" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B25" s="17">
         <v>5.5</v>
@@ -1881,9 +1897,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="18" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B26" s="17">
         <v>6</v>
@@ -1892,9 +1908,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="18" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B27" s="17">
         <v>6</v>
@@ -1903,9 +1919,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="19" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B28" s="20">
         <v>6</v>
@@ -1914,9 +1930,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="19" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B29" s="20">
         <v>5.5</v>
@@ -1925,9 +1941,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="15" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B30" s="15">
         <v>5</v>
@@ -1936,9 +1952,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="25" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B31">
         <v>5.8</v>
@@ -1947,9 +1963,9 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="25" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B32">
         <v>5.8</v>
@@ -1958,9 +1974,9 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="25" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B33">
         <v>5.8</v>
@@ -1969,9 +1985,9 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="15" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B34" s="15">
         <v>5.8</v>
@@ -1980,9 +1996,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B35">
         <v>5.5</v>
@@ -1991,9 +2007,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="18" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B36" s="20">
         <v>4</v>
@@ -2002,9 +2018,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B37">
         <v>5.5</v>
@@ -2013,9 +2029,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="15" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B38" s="15">
         <v>6</v>
@@ -2024,9 +2040,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="18" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B39" s="17">
         <v>4.5</v>
@@ -2035,9 +2051,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="15" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B40" s="15">
         <v>5.5</v>
@@ -2046,9 +2062,9 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="25" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B41">
         <v>5.8</v>
@@ -2057,9 +2073,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="15" t="s">
-        <v>43</v>
+        <v>192</v>
       </c>
       <c r="B42" s="15">
         <v>6</v>
@@ -2068,9 +2084,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="18" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B43" s="20">
         <v>6.5</v>
@@ -2079,9 +2095,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="15" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B44" s="15">
         <v>6</v>
@@ -2090,9 +2106,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B45">
         <v>6</v>
@@ -2101,9 +2117,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="15" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B46" s="15">
         <v>5.5</v>
@@ -2112,9 +2128,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B47">
         <v>5.5</v>
@@ -2123,9 +2139,9 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="18" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B48" s="17">
         <v>4.5</v>
@@ -2134,9 +2150,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="18" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B49" s="17">
         <v>6</v>
@@ -2145,9 +2161,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="18" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B50" s="17">
         <v>5.5</v>
@@ -2156,9 +2172,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="27" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B51" s="20">
         <v>5.5</v>
@@ -2167,9 +2183,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="15" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B52" s="15">
         <v>6</v>
@@ -2178,9 +2194,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B53">
         <v>6</v>
@@ -2189,9 +2205,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="18" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B54" s="17">
         <v>5</v>
@@ -2200,9 +2216,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="18" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B55" s="17">
         <v>5.5</v>
@@ -2211,9 +2227,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="15" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B56" s="15">
         <v>6</v>
@@ -2222,9 +2238,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="18" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B57" s="17">
         <v>6</v>
@@ -2233,9 +2249,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="27" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B58" s="17">
         <v>5</v>
@@ -2244,9 +2260,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="27" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B59" s="17">
         <v>5</v>
@@ -2255,9 +2271,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="26" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B60">
         <v>5.8</v>
@@ -2266,9 +2282,9 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="29" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B61" s="15">
         <v>6</v>
@@ -2277,9 +2293,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="26" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B62">
         <v>5.5</v>
@@ -2288,9 +2304,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="26" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B63">
         <v>5.6</v>
@@ -2299,9 +2315,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="25" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B64">
         <v>5.8</v>
@@ -2310,9 +2326,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B65">
         <v>6</v>
@@ -2321,9 +2337,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>67</v>
+        <v>193</v>
       </c>
       <c r="B66">
         <v>6</v>
@@ -2332,9 +2348,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B67">
         <v>6</v>
@@ -2343,9 +2359,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" s="15" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B68" s="15">
         <v>6</v>
@@ -2354,9 +2370,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="18" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B69" s="17">
         <v>5</v>
@@ -2365,9 +2381,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="18" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B70" s="17">
         <v>5.5</v>
@@ -2376,9 +2392,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="15" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B71" s="15">
         <v>6</v>
@@ -2387,9 +2403,9 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" s="18" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B72" s="17">
         <v>5</v>
@@ -2398,9 +2414,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" s="18" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B73" s="17">
         <v>4.5</v>
@@ -2409,9 +2425,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" s="18" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B74" s="17">
         <v>5</v>
@@ -2420,9 +2436,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" s="15" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B75" s="15">
         <v>4</v>
@@ -2431,9 +2447,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B76">
         <v>5</v>
@@ -2442,9 +2458,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" s="18" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B77" s="17">
         <v>5.6</v>
@@ -2453,9 +2469,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="18" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B78" s="17">
         <v>6</v>
@@ -2464,9 +2480,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B79">
         <v>5</v>
@@ -2475,9 +2491,9 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" s="18" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B80" s="17">
         <v>6</v>
@@ -2486,9 +2502,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="18" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B81" s="17">
         <v>5.5</v>
@@ -2497,9 +2513,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B82">
         <v>5.5</v>
@@ -2508,9 +2524,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="25" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B83">
         <v>5.8</v>
@@ -2519,9 +2535,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="25" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B84">
         <v>5.8</v>
@@ -2530,9 +2546,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" s="18" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B85" s="17">
         <v>6</v>
@@ -2541,9 +2557,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" s="18" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B86" s="17">
         <v>6</v>
@@ -2552,9 +2568,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>88</v>
+        <v>194</v>
       </c>
       <c r="B87">
         <v>5.5</v>
@@ -2563,9 +2579,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B88">
         <v>5.5</v>
@@ -2574,9 +2590,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="18" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B89" s="17">
         <v>6</v>
@@ -2585,9 +2601,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" s="15" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B90" s="15">
         <v>6</v>
@@ -2596,9 +2612,9 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B91">
         <v>5</v>
@@ -2607,9 +2623,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" s="21" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B92" s="17">
         <v>6</v>
@@ -2618,9 +2634,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" s="18" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B93" s="17">
         <v>6</v>
@@ -2629,9 +2645,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B94">
         <v>5</v>
@@ -2640,9 +2656,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" s="15" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B95" s="15">
         <v>6.5</v>
@@ -2651,9 +2667,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B96">
         <v>5</v>
@@ -2662,9 +2678,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="22" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B97" s="22">
         <v>4.5</v>
@@ -2673,9 +2689,9 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="18" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B98" s="17">
         <v>5</v>
@@ -2684,9 +2700,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="25" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B99">
         <v>5.8</v>
@@ -2695,9 +2711,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B100">
         <v>5</v>
@@ -2706,9 +2722,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B101">
         <v>5.5</v>
@@ -2717,9 +2733,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" s="28" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B102" s="15">
         <v>6</v>
@@ -2728,9 +2744,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="103" spans="1:3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" s="18" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B103" s="17">
         <v>5.5</v>
@@ -2739,9 +2755,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" s="18" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B104" s="17">
         <v>5.5</v>
@@ -2750,9 +2766,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="105" spans="1:3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" s="15" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B105" s="15">
         <v>6</v>
@@ -2761,9 +2777,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="106" spans="1:3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" s="15" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B106" s="15">
         <v>6</v>
@@ -2772,9 +2788,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="107" spans="1:3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B107">
         <v>5.5</v>
@@ -2783,9 +2799,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="108" spans="1:3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B108">
         <v>5.5</v>
@@ -2794,9 +2810,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="109" spans="1:3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>110</v>
+        <v>195</v>
       </c>
       <c r="B109">
         <v>5.5</v>
@@ -2805,9 +2821,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" s="25" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="B110" s="15">
         <v>6</v>
@@ -2822,43 +2838,43 @@
       <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="F18:G19">
-    <cfRule type="duplicateValues" dxfId="42" priority="41"/>
+  <conditionalFormatting sqref="A2:A109">
+    <cfRule type="duplicateValues" dxfId="43" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A17">
-    <cfRule type="duplicateValues" dxfId="41" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51">
-    <cfRule type="duplicateValues" dxfId="40" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58">
-    <cfRule type="duplicateValues" dxfId="38" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59">
-    <cfRule type="duplicateValues" dxfId="35" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A60">
-    <cfRule type="duplicateValues" dxfId="32" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61">
-    <cfRule type="duplicateValues" dxfId="29" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A62:A63">
-    <cfRule type="duplicateValues" dxfId="26" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A109">
-    <cfRule type="duplicateValues" dxfId="23" priority="1"/>
+  <conditionalFormatting sqref="F18:G19">
+    <cfRule type="duplicateValues" dxfId="24" priority="41"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2867,25 +2883,25 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="8">
         <v>0</v>
       </c>
@@ -2896,7 +2912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1">
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8">
         <v>1</v>
       </c>
@@ -2907,7 +2923,7 @@
         <v>5.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1">
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8">
         <v>2</v>
       </c>
@@ -2918,7 +2934,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1">
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="8">
         <v>3</v>
       </c>
@@ -2929,10 +2945,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1">
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1">
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4"/>
     </row>
   </sheetData>
@@ -2944,116 +2960,116 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="B2" s="3">
         <v>0.99399999999999999</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B3" s="3">
         <v>3.6950899999999999E-5</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B4" s="3">
         <v>11.628251000000001</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="B5" s="3">
         <v>-1.1878</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="B6" s="3">
         <v>-8.4931999999999999</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="B8" s="3">
         <v>0.99399999999999999</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10"/>
     </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1">
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4"/>
     </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1">
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4"/>
     </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1">
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4"/>
     </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1">
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4"/>
     </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1">
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4"/>
     </row>
   </sheetData>
@@ -3065,61 +3081,61 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="12">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="12">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="12">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="12">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="4"/>
     </row>
   </sheetData>
@@ -3131,26 +3147,26 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="B2" s="3">
         <v>1.0541326</v>
@@ -3159,9 +3175,9 @@
         <v>-9.8126979999999999E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B3" s="3">
         <v>1.0744899999999999</v>
@@ -3170,16 +3186,16 @@
         <v>-1.3431848999999999E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="13"/>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="4"/>
     </row>
   </sheetData>
@@ -3191,7 +3207,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BAE779D-EE07-4BAA-A5AD-49FE70D75EAE}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3200,33 +3216,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H110"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
     <col min="3" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="8" max="8" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" customHeight="1">
+    <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -3240,12 +3256,12 @@
         <v>29</v>
       </c>
       <c r="E2" s="3">
-        <f>213.96744-39.579185*C2+2.3020512*C2^2</f>
+        <f t="shared" ref="E2:E38" si="0">213.96744-39.579185*C2+2.3020512*C2^2</f>
         <v>521.4312698</v>
       </c>
       <c r="H2" s="16"/>
     </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1">
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -3259,12 +3275,12 @@
         <v>25</v>
       </c>
       <c r="E3" s="3">
-        <f>213.96744-39.579185*C3+2.3020512*C3^2</f>
+        <f t="shared" si="0"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H3" s="18"/>
     </row>
-    <row r="4" spans="1:8" ht="15" customHeight="1">
+    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -3278,11 +3294,11 @@
         <v>25</v>
       </c>
       <c r="E4" s="3">
-        <f>213.96744-39.579185*C4+2.3020512*C4^2</f>
-        <v>293.00340819999997</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1">
+        <f t="shared" si="0"/>
+        <v>293.00340819999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -3296,12 +3312,12 @@
         <v>25</v>
       </c>
       <c r="E5" s="3">
-        <f>213.96744-39.579185*C5+2.3020512*C5^2</f>
+        <f t="shared" si="0"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H5" s="18"/>
     </row>
-    <row r="6" spans="1:8" ht="15" customHeight="1">
+    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -3315,12 +3331,12 @@
         <v>25</v>
       </c>
       <c r="E6" s="3">
-        <f>213.96744-39.579185*C6+2.3020512*C6^2</f>
+        <f t="shared" si="0"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H6" s="18"/>
     </row>
-    <row r="7" spans="1:8" ht="15" customHeight="1">
+    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -3334,11 +3350,11 @@
         <v>25</v>
       </c>
       <c r="E7" s="3">
-        <f>213.96744-39.579185*C7+2.3020512*C7^2</f>
-        <v>293.00340819999997</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1">
+        <f t="shared" si="0"/>
+        <v>293.00340819999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -3352,16 +3368,16 @@
         <v>25</v>
       </c>
       <c r="E8" s="3">
-        <f>213.96744-39.579185*C8+2.3020512*C8^2</f>
-        <v>293.00340819999997</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1">
+        <f t="shared" si="0"/>
+        <v>293.00340819999997</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>10</v>
+      <c r="B9" s="31" t="s">
+        <v>190</v>
       </c>
       <c r="C9" s="3">
         <v>19</v>
@@ -3370,16 +3386,16 @@
         <v>25</v>
       </c>
       <c r="E9" s="3">
-        <f>213.96744-39.579185*C9+2.3020512*C9^2</f>
-        <v>293.00340819999997</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15" customHeight="1">
+        <f t="shared" si="0"/>
+        <v>293.00340819999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>11</v>
+      <c r="B10" s="31" t="s">
+        <v>191</v>
       </c>
       <c r="C10" s="3">
         <v>20</v>
@@ -3388,17 +3404,17 @@
         <v>26</v>
       </c>
       <c r="E10" s="3">
-        <f>213.96744-39.579185*C10+2.3020512*C10^2</f>
+        <f t="shared" si="0"/>
         <v>343.20422000000008</v>
       </c>
       <c r="H10" s="15"/>
     </row>
-    <row r="11" spans="1:8" ht="15" customHeight="1">
+    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C11" s="3">
         <v>19</v>
@@ -3407,17 +3423,17 @@
         <v>25</v>
       </c>
       <c r="E11" s="3">
-        <f>213.96744-39.579185*C11+2.3020512*C11^2</f>
+        <f t="shared" si="0"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H11" s="18"/>
     </row>
-    <row r="12" spans="1:8" ht="15" customHeight="1">
+    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>13</v>
+      <c r="B12" s="31" t="s">
+        <v>196</v>
       </c>
       <c r="C12" s="3">
         <v>19</v>
@@ -3426,17 +3442,17 @@
         <v>25</v>
       </c>
       <c r="E12" s="3">
-        <f>213.96744-39.579185*C12+2.3020512*C12^2</f>
+        <f t="shared" si="0"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H12" s="25"/>
     </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1">
+    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C13" s="3">
         <v>19</v>
@@ -3445,17 +3461,17 @@
         <v>25</v>
       </c>
       <c r="E13" s="3">
-        <f>213.96744-39.579185*C13+2.3020512*C13^2</f>
+        <f t="shared" si="0"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H13" s="18"/>
     </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1">
+    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" s="3">
         <v>19</v>
@@ -3464,16 +3480,16 @@
         <v>25</v>
       </c>
       <c r="E14" s="3">
-        <f>213.96744-39.579185*C14+2.3020512*C14^2</f>
-        <v>293.00340819999997</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1">
+        <f t="shared" si="0"/>
+        <v>293.00340819999997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C15" s="3">
         <v>19</v>
@@ -3482,17 +3498,17 @@
         <v>6</v>
       </c>
       <c r="E15" s="3">
-        <f>213.96744-39.579185*C15+2.3020512*C15^2</f>
+        <f t="shared" si="0"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H15" s="27"/>
     </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1">
+    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C16" s="3">
         <v>12</v>
@@ -3501,17 +3517,17 @@
         <v>18</v>
       </c>
       <c r="E16" s="3">
-        <f>213.96744-39.579185*C16+2.3020512*C16^2</f>
+        <f t="shared" si="0"/>
         <v>70.512592799999993</v>
       </c>
       <c r="H16" s="27"/>
     </row>
-    <row r="17" spans="1:8" ht="15" customHeight="1">
+    <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C17" s="3">
         <v>12</v>
@@ -3520,17 +3536,17 @@
         <v>18</v>
       </c>
       <c r="E17" s="3">
-        <f>213.96744-39.579185*C17+2.3020512*C17^2</f>
+        <f t="shared" si="0"/>
         <v>70.512592799999993</v>
       </c>
       <c r="H17" s="27"/>
     </row>
-    <row r="18" spans="1:8" ht="15" customHeight="1">
+    <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C18" s="3">
         <v>19</v>
@@ -3539,17 +3555,17 @@
         <v>25</v>
       </c>
       <c r="E18" s="3">
-        <f>213.96744-39.579185*C18+2.3020512*C18^2</f>
+        <f t="shared" si="0"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H18" s="18"/>
     </row>
-    <row r="19" spans="1:8" ht="15" customHeight="1">
+    <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C19" s="3">
         <v>19</v>
@@ -3558,17 +3574,17 @@
         <v>25</v>
       </c>
       <c r="E19" s="3">
-        <f>213.96744-39.579185*C19+2.3020512*C19^2</f>
+        <f t="shared" si="0"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H19" s="18"/>
     </row>
-    <row r="20" spans="1:8" ht="15" customHeight="1">
+    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C20" s="3">
         <v>19</v>
@@ -3577,17 +3593,17 @@
         <v>25</v>
       </c>
       <c r="E20" s="3">
-        <f>213.96744-39.579185*C20+2.3020512*C20^2</f>
+        <f t="shared" si="0"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H20" s="15"/>
     </row>
-    <row r="21" spans="1:8" ht="15" customHeight="1">
+    <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C21" s="3">
         <v>19</v>
@@ -3596,16 +3612,16 @@
         <v>25</v>
       </c>
       <c r="E21" s="3">
-        <f>213.96744-39.579185*C21+2.3020512*C21^2</f>
-        <v>293.00340819999997</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1">
+        <f t="shared" si="0"/>
+        <v>293.00340819999997</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C22" s="3">
         <v>19</v>
@@ -3614,17 +3630,17 @@
         <v>25</v>
       </c>
       <c r="E22" s="3">
-        <f>213.96744-39.579185*C22+2.3020512*C22^2</f>
+        <f t="shared" si="0"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H22" s="15"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C23" s="3">
         <v>19</v>
@@ -3633,16 +3649,16 @@
         <v>25</v>
       </c>
       <c r="E23" s="3">
-        <f>213.96744-39.579185*C23+2.3020512*C23^2</f>
-        <v>293.00340819999997</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="15" customHeight="1">
+        <f t="shared" si="0"/>
+        <v>293.00340819999997</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="23">
         <v>108</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C24" s="3">
         <v>19</v>
@@ -3651,17 +3667,17 @@
         <v>25</v>
       </c>
       <c r="E24" s="3">
-        <f>213.96744-39.579185*C24+2.3020512*C24^2</f>
+        <f t="shared" si="0"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H24" s="17"/>
     </row>
-    <row r="25" spans="1:8" ht="15" customHeight="1">
+    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>23</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C25" s="3">
         <v>19</v>
@@ -3670,17 +3686,17 @@
         <v>25</v>
       </c>
       <c r="E25" s="3">
-        <f>213.96744-39.579185*C25+2.3020512*C25^2</f>
+        <f t="shared" si="0"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H25" s="18"/>
     </row>
-    <row r="26" spans="1:8" ht="15" customHeight="1">
+    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>24</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C26" s="3">
         <v>19</v>
@@ -3689,17 +3705,17 @@
         <v>25</v>
       </c>
       <c r="E26" s="3">
-        <f>213.96744-39.579185*C26+2.3020512*C26^2</f>
+        <f t="shared" si="0"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H26" s="18"/>
     </row>
-    <row r="27" spans="1:8" ht="15" customHeight="1">
+    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>25</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C27" s="3">
         <v>19</v>
@@ -3708,17 +3724,17 @@
         <v>25</v>
       </c>
       <c r="E27" s="3">
-        <f>213.96744-39.579185*C27+2.3020512*C27^2</f>
+        <f t="shared" si="0"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H27" s="18"/>
     </row>
-    <row r="28" spans="1:8" ht="15" customHeight="1">
+    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>26</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C28" s="3">
         <v>19</v>
@@ -3727,17 +3743,17 @@
         <v>25</v>
       </c>
       <c r="E28" s="3">
-        <f>213.96744-39.579185*C28+2.3020512*C28^2</f>
+        <f t="shared" si="0"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H28" s="19"/>
     </row>
-    <row r="29" spans="1:8" ht="15" customHeight="1">
+    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C29" s="3">
         <v>22</v>
@@ -3746,17 +3762,17 @@
         <v>28</v>
       </c>
       <c r="E29" s="3">
-        <f>213.96744-39.579185*C29+2.3020512*C29^2</f>
+        <f t="shared" si="0"/>
         <v>457.41815080000003</v>
       </c>
       <c r="H29" s="19"/>
     </row>
-    <row r="30" spans="1:8" ht="15" customHeight="1">
+    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C30" s="3">
         <v>19</v>
@@ -3765,17 +3781,17 @@
         <v>25</v>
       </c>
       <c r="E30" s="3">
-        <f>213.96744-39.579185*C30+2.3020512*C30^2</f>
+        <f t="shared" si="0"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H30" s="15"/>
     </row>
-    <row r="31" spans="1:8" ht="15" customHeight="1">
+    <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>32</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C31" s="3">
         <v>19</v>
@@ -3784,17 +3800,17 @@
         <v>25</v>
       </c>
       <c r="E31" s="3">
-        <f>213.96744-39.579185*C31+2.3020512*C31^2</f>
+        <f t="shared" si="0"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H31" s="25"/>
     </row>
-    <row r="32" spans="1:8" ht="15" customHeight="1">
+    <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C32" s="3">
         <v>19</v>
@@ -3803,17 +3819,17 @@
         <v>25</v>
       </c>
       <c r="E32" s="3">
-        <f>213.96744-39.579185*C32+2.3020512*C32^2</f>
+        <f t="shared" si="0"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H32" s="25"/>
     </row>
-    <row r="33" spans="1:8" ht="15" customHeight="1">
+    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>30</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>34</v>
+      <c r="B33" s="31" t="s">
+        <v>31</v>
       </c>
       <c r="C33" s="3">
         <v>16</v>
@@ -3822,17 +3838,17 @@
         <v>22</v>
       </c>
       <c r="E33" s="3">
-        <f>213.96744-39.579185*C33+2.3020512*C33^2</f>
+        <f t="shared" si="0"/>
         <v>170.02558720000002</v>
       </c>
       <c r="H33" s="25"/>
     </row>
-    <row r="34" spans="1:8" ht="15" customHeight="1">
+    <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C34" s="3">
         <v>19</v>
@@ -3841,17 +3857,17 @@
         <v>25</v>
       </c>
       <c r="E34" s="3">
-        <f>213.96744-39.579185*C34+2.3020512*C34^2</f>
+        <f t="shared" si="0"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H34" s="15"/>
     </row>
-    <row r="35" spans="1:8" ht="15" customHeight="1">
+    <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C35" s="3">
         <v>19</v>
@@ -3860,16 +3876,16 @@
         <v>25</v>
       </c>
       <c r="E35" s="3">
-        <f>213.96744-39.579185*C35+2.3020512*C35^2</f>
-        <v>293.00340819999997</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="15" customHeight="1">
+        <f t="shared" si="0"/>
+        <v>293.00340819999997</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C36" s="3">
         <v>19</v>
@@ -3878,17 +3894,17 @@
         <v>25</v>
       </c>
       <c r="E36" s="3">
-        <f>213.96744-39.579185*C36+2.3020512*C36^2</f>
+        <f t="shared" si="0"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H36" s="18"/>
     </row>
-    <row r="37" spans="1:8" ht="15" customHeight="1">
+    <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C37" s="3">
         <v>19</v>
@@ -3897,16 +3913,16 @@
         <v>25</v>
       </c>
       <c r="E37" s="3">
-        <f>213.96744-39.579185*C37+2.3020512*C37^2</f>
-        <v>293.00340819999997</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="15" customHeight="1">
+        <f t="shared" si="0"/>
+        <v>293.00340819999997</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C38" s="3">
         <v>19</v>
@@ -3915,17 +3931,17 @@
         <v>25</v>
       </c>
       <c r="E38" s="3">
-        <f>213.96744-39.579185*C38+2.3020512*C38^2</f>
+        <f t="shared" si="0"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H38" s="15"/>
     </row>
-    <row r="39" spans="1:8" ht="15" customHeight="1">
+    <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="23">
         <v>109</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C39" s="26">
         <v>19</v>
@@ -3938,12 +3954,12 @@
       </c>
       <c r="H39" s="18"/>
     </row>
-    <row r="40" spans="1:8" ht="15" customHeight="1">
+    <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>38</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C40" s="3">
         <v>19</v>
@@ -3952,17 +3968,17 @@
         <v>25</v>
       </c>
       <c r="E40" s="3">
-        <f>213.96744-39.579185*C40+2.3020512*C40^2</f>
+        <f t="shared" ref="E40:E71" si="1">213.96744-39.579185*C40+2.3020512*C40^2</f>
         <v>293.00340819999997</v>
       </c>
       <c r="H40" s="15"/>
     </row>
-    <row r="41" spans="1:8" ht="15" customHeight="1">
+    <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>39</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C41" s="3">
         <v>12</v>
@@ -3971,17 +3987,17 @@
         <v>18</v>
       </c>
       <c r="E41" s="3">
-        <f>213.96744-39.579185*C41+2.3020512*C41^2</f>
+        <f t="shared" si="1"/>
         <v>70.512592799999993</v>
       </c>
       <c r="H41" s="25"/>
     </row>
-    <row r="42" spans="1:8" ht="15" customHeight="1">
+    <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>40</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>43</v>
+      <c r="B42" s="31" t="s">
+        <v>192</v>
       </c>
       <c r="C42" s="3">
         <v>19</v>
@@ -3990,17 +4006,17 @@
         <v>25</v>
       </c>
       <c r="E42" s="3">
-        <f>213.96744-39.579185*C42+2.3020512*C42^2</f>
+        <f t="shared" si="1"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H42" s="15"/>
     </row>
-    <row r="43" spans="1:8" ht="15" customHeight="1">
+    <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>41</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C43" s="3">
         <v>19</v>
@@ -4009,17 +4025,17 @@
         <v>25</v>
       </c>
       <c r="E43" s="3">
-        <f>213.96744-39.579185*C43+2.3020512*C43^2</f>
+        <f t="shared" si="1"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H43" s="18"/>
     </row>
-    <row r="44" spans="1:8" ht="15" customHeight="1">
+    <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>42</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C44" s="3">
         <v>19</v>
@@ -4028,17 +4044,17 @@
         <v>25</v>
       </c>
       <c r="E44" s="3">
-        <f>213.96744-39.579185*C44+2.3020512*C44^2</f>
+        <f t="shared" si="1"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H44" s="15"/>
     </row>
-    <row r="45" spans="1:8" ht="15" customHeight="1">
+    <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>43</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C45" s="3">
         <v>19</v>
@@ -4047,16 +4063,16 @@
         <v>25</v>
       </c>
       <c r="E45" s="3">
-        <f>213.96744-39.579185*C45+2.3020512*C45^2</f>
-        <v>293.00340819999997</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="15" customHeight="1">
+        <f t="shared" si="1"/>
+        <v>293.00340819999997</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>44</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C46" s="3">
         <v>19</v>
@@ -4065,17 +4081,17 @@
         <v>25</v>
       </c>
       <c r="E46" s="3">
-        <f>213.96744-39.579185*C46+2.3020512*C46^2</f>
+        <f t="shared" si="1"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H46" s="15"/>
     </row>
-    <row r="47" spans="1:8" ht="15" customHeight="1">
+    <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>45</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C47" s="3">
         <v>19</v>
@@ -4084,16 +4100,16 @@
         <v>25</v>
       </c>
       <c r="E47" s="3">
-        <f>213.96744-39.579185*C47+2.3020512*C47^2</f>
-        <v>293.00340819999997</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="15" customHeight="1">
+        <f t="shared" si="1"/>
+        <v>293.00340819999997</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>105</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C48" s="3">
         <v>19</v>
@@ -4102,17 +4118,17 @@
         <v>25</v>
       </c>
       <c r="E48" s="3">
-        <f>213.96744-39.579185*C48+2.3020512*C48^2</f>
+        <f t="shared" si="1"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H48" s="18"/>
     </row>
-    <row r="49" spans="1:8" ht="15" customHeight="1">
+    <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>46</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C49" s="3">
         <v>19</v>
@@ -4121,17 +4137,17 @@
         <v>25</v>
       </c>
       <c r="E49" s="3">
-        <f>213.96744-39.579185*C49+2.3020512*C49^2</f>
+        <f t="shared" si="1"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H49" s="18"/>
     </row>
-    <row r="50" spans="1:8" ht="15" customHeight="1">
+    <row r="50" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>47</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C50" s="3">
         <v>12</v>
@@ -4140,17 +4156,17 @@
         <v>18</v>
       </c>
       <c r="E50" s="3">
-        <f>213.96744-39.579185*C50+2.3020512*C50^2</f>
+        <f t="shared" si="1"/>
         <v>70.512592799999993</v>
       </c>
       <c r="H50" s="18"/>
     </row>
-    <row r="51" spans="1:8" ht="15" customHeight="1">
+    <row r="51" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>48</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C51" s="3">
         <v>19</v>
@@ -4159,17 +4175,17 @@
         <v>25</v>
       </c>
       <c r="E51" s="3">
-        <f>213.96744-39.579185*C51+2.3020512*C51^2</f>
+        <f t="shared" si="1"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H51" s="27"/>
     </row>
-    <row r="52" spans="1:8" ht="15" customHeight="1">
+    <row r="52" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>49</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C52" s="3">
         <v>19</v>
@@ -4178,17 +4194,17 @@
         <v>25</v>
       </c>
       <c r="E52" s="3">
-        <f>213.96744-39.579185*C52+2.3020512*C52^2</f>
+        <f t="shared" si="1"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H52" s="15"/>
     </row>
-    <row r="53" spans="1:8" ht="15" customHeight="1">
+    <row r="53" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>50</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C53" s="3">
         <v>19</v>
@@ -4197,16 +4213,16 @@
         <v>25</v>
       </c>
       <c r="E53" s="3">
-        <f>213.96744-39.579185*C53+2.3020512*C53^2</f>
-        <v>293.00340819999997</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="15" customHeight="1">
+        <f t="shared" si="1"/>
+        <v>293.00340819999997</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>51</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>55</v>
+      <c r="B54" s="31" t="s">
+        <v>51</v>
       </c>
       <c r="C54" s="3">
         <v>19</v>
@@ -4215,17 +4231,17 @@
         <v>25</v>
       </c>
       <c r="E54" s="3">
-        <f>213.96744-39.579185*C54+2.3020512*C54^2</f>
+        <f t="shared" si="1"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H54" s="18"/>
     </row>
-    <row r="55" spans="1:8" ht="15" customHeight="1">
+    <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>52</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C55" s="3">
         <v>19</v>
@@ -4234,17 +4250,17 @@
         <v>25</v>
       </c>
       <c r="E55" s="3">
-        <f>213.96744-39.579185*C55+2.3020512*C55^2</f>
+        <f t="shared" si="1"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H55" s="18"/>
     </row>
-    <row r="56" spans="1:8" ht="15" customHeight="1">
+    <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>53</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C56" s="3">
         <v>19</v>
@@ -4253,17 +4269,17 @@
         <v>6</v>
       </c>
       <c r="E56" s="3">
-        <f>213.96744-39.579185*C56+2.3020512*C56^2</f>
+        <f t="shared" si="1"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H56" s="15"/>
     </row>
-    <row r="57" spans="1:8" ht="15" customHeight="1">
+    <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>54</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C57" s="3">
         <v>19</v>
@@ -4272,17 +4288,17 @@
         <v>25</v>
       </c>
       <c r="E57" s="3">
-        <f>213.96744-39.579185*C57+2.3020512*C57^2</f>
+        <f t="shared" si="1"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H57" s="18"/>
     </row>
-    <row r="58" spans="1:8" ht="15" customHeight="1">
+    <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>104</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C58" s="3">
         <v>19</v>
@@ -4291,17 +4307,17 @@
         <v>25</v>
       </c>
       <c r="E58" s="3">
-        <f>213.96744-39.579185*C58+2.3020512*C58^2</f>
+        <f t="shared" si="1"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H58" s="27"/>
     </row>
-    <row r="59" spans="1:8" ht="15" customHeight="1">
+    <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>106</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C59" s="3">
         <v>19</v>
@@ -4310,17 +4326,17 @@
         <v>25</v>
       </c>
       <c r="E59" s="3">
-        <f>213.96744-39.579185*C59+2.3020512*C59^2</f>
+        <f t="shared" si="1"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H59" s="27"/>
     </row>
-    <row r="60" spans="1:8" ht="15" customHeight="1">
+    <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>55</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C60" s="3">
         <v>19</v>
@@ -4329,17 +4345,17 @@
         <v>25</v>
       </c>
       <c r="E60" s="3">
-        <f>213.96744-39.579185*C60+2.3020512*C60^2</f>
+        <f t="shared" si="1"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H60" s="26"/>
     </row>
-    <row r="61" spans="1:8" ht="15" customHeight="1">
+    <row r="61" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>56</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C61" s="3">
         <v>19</v>
@@ -4348,17 +4364,17 @@
         <v>25</v>
       </c>
       <c r="E61" s="3">
-        <f>213.96744-39.579185*C61+2.3020512*C61^2</f>
+        <f t="shared" si="1"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H61" s="29"/>
     </row>
-    <row r="62" spans="1:8" ht="15" customHeight="1">
+    <row r="62" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>57</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C62" s="3">
         <v>19</v>
@@ -4367,17 +4383,17 @@
         <v>25</v>
       </c>
       <c r="E62" s="3">
-        <f>213.96744-39.579185*C62+2.3020512*C62^2</f>
+        <f t="shared" si="1"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H62" s="26"/>
     </row>
-    <row r="63" spans="1:8" ht="15" customHeight="1">
+    <row r="63" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>58</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C63" s="3">
         <v>19</v>
@@ -4386,17 +4402,17 @@
         <v>25</v>
       </c>
       <c r="E63" s="3">
-        <f>213.96744-39.579185*C63+2.3020512*C63^2</f>
+        <f t="shared" si="1"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H63" s="26"/>
     </row>
-    <row r="64" spans="1:8" ht="15" customHeight="1">
+    <row r="64" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>59</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C64" s="3">
         <v>20</v>
@@ -4405,17 +4421,17 @@
         <v>26</v>
       </c>
       <c r="E64" s="3">
-        <f>213.96744-39.579185*C64+2.3020512*C64^2</f>
+        <f t="shared" si="1"/>
         <v>343.20422000000008</v>
       </c>
       <c r="H64" s="25"/>
     </row>
-    <row r="65" spans="1:8" ht="15" customHeight="1">
+    <row r="65" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>60</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C65" s="3">
         <v>19</v>
@@ -4424,16 +4440,16 @@
         <v>25</v>
       </c>
       <c r="E65" s="3">
-        <f>213.96744-39.579185*C65+2.3020512*C65^2</f>
-        <v>293.00340819999997</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="15" customHeight="1">
+        <f t="shared" si="1"/>
+        <v>293.00340819999997</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>61</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>67</v>
+      <c r="B66" s="31" t="s">
+        <v>193</v>
       </c>
       <c r="C66" s="3">
         <v>19</v>
@@ -4442,16 +4458,16 @@
         <v>25</v>
       </c>
       <c r="E66" s="3">
-        <f>213.96744-39.579185*C66+2.3020512*C66^2</f>
-        <v>293.00340819999997</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="15" customHeight="1">
+        <f t="shared" si="1"/>
+        <v>293.00340819999997</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>62</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C67" s="3">
         <v>19</v>
@@ -4460,16 +4476,16 @@
         <v>25</v>
       </c>
       <c r="E67" s="3">
-        <f>213.96744-39.579185*C67+2.3020512*C67^2</f>
-        <v>293.00340819999997</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="15" customHeight="1">
+        <f t="shared" si="1"/>
+        <v>293.00340819999997</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>63</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C68" s="3">
         <v>19</v>
@@ -4478,17 +4494,17 @@
         <v>25</v>
       </c>
       <c r="E68" s="3">
-        <f>213.96744-39.579185*C68+2.3020512*C68^2</f>
+        <f t="shared" si="1"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H68" s="15"/>
     </row>
-    <row r="69" spans="1:8" ht="15" customHeight="1">
+    <row r="69" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>64</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C69" s="3">
         <v>19</v>
@@ -4497,17 +4513,17 @@
         <v>25</v>
       </c>
       <c r="E69" s="3">
-        <f>213.96744-39.579185*C69+2.3020512*C69^2</f>
+        <f t="shared" si="1"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H69" s="18"/>
     </row>
-    <row r="70" spans="1:8" ht="15" customHeight="1">
+    <row r="70" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>65</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C70" s="3">
         <v>19</v>
@@ -4516,17 +4532,17 @@
         <v>25</v>
       </c>
       <c r="E70" s="3">
-        <f>213.96744-39.579185*C70+2.3020512*C70^2</f>
+        <f t="shared" si="1"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H70" s="18"/>
     </row>
-    <row r="71" spans="1:8" ht="15" customHeight="1">
+    <row r="71" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>66</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C71" s="3">
         <v>19</v>
@@ -4535,17 +4551,17 @@
         <v>25</v>
       </c>
       <c r="E71" s="3">
-        <f>213.96744-39.579185*C71+2.3020512*C71^2</f>
+        <f t="shared" si="1"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H71" s="15"/>
     </row>
-    <row r="72" spans="1:8" ht="15" customHeight="1">
+    <row r="72" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>67</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C72" s="3">
         <v>19</v>
@@ -4554,17 +4570,17 @@
         <v>25</v>
       </c>
       <c r="E72" s="3">
-        <f>213.96744-39.579185*C72+2.3020512*C72^2</f>
+        <f t="shared" ref="E72:E103" si="2">213.96744-39.579185*C72+2.3020512*C72^2</f>
         <v>293.00340819999997</v>
       </c>
       <c r="H72" s="18"/>
     </row>
-    <row r="73" spans="1:8" ht="15" customHeight="1">
+    <row r="73" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>103</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C73" s="3">
         <v>19</v>
@@ -4573,17 +4589,17 @@
         <v>25</v>
       </c>
       <c r="E73" s="3">
-        <f>213.96744-39.579185*C73+2.3020512*C73^2</f>
+        <f t="shared" si="2"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H73" s="18"/>
     </row>
-    <row r="74" spans="1:8" ht="15" customHeight="1">
+    <row r="74" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>68</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C74" s="3">
         <v>19</v>
@@ -4592,17 +4608,17 @@
         <v>25</v>
       </c>
       <c r="E74" s="3">
-        <f>213.96744-39.579185*C74+2.3020512*C74^2</f>
+        <f t="shared" si="2"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H74" s="18"/>
     </row>
-    <row r="75" spans="1:8" ht="15" customHeight="1">
+    <row r="75" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <v>69</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C75" s="3">
         <v>19</v>
@@ -4611,17 +4627,17 @@
         <v>25</v>
       </c>
       <c r="E75" s="3">
-        <f>213.96744-39.579185*C75+2.3020512*C75^2</f>
+        <f t="shared" si="2"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H75" s="15"/>
     </row>
-    <row r="76" spans="1:8" ht="15" customHeight="1">
+    <row r="76" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>70</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C76" s="3">
         <v>19</v>
@@ -4630,16 +4646,16 @@
         <v>25</v>
       </c>
       <c r="E76" s="3">
-        <f>213.96744-39.579185*C76+2.3020512*C76^2</f>
-        <v>293.00340819999997</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" ht="15" customHeight="1">
+        <f t="shared" si="2"/>
+        <v>293.00340819999997</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <v>71</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C77" s="3">
         <v>19</v>
@@ -4648,17 +4664,17 @@
         <v>25</v>
       </c>
       <c r="E77" s="3">
-        <f>213.96744-39.579185*C77+2.3020512*C77^2</f>
+        <f t="shared" si="2"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H77" s="18"/>
     </row>
-    <row r="78" spans="1:8" ht="15" customHeight="1">
+    <row r="78" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>72</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C78" s="3">
         <v>19</v>
@@ -4667,17 +4683,17 @@
         <v>25</v>
       </c>
       <c r="E78" s="3">
-        <f>213.96744-39.579185*C78+2.3020512*C78^2</f>
+        <f t="shared" si="2"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H78" s="18"/>
     </row>
-    <row r="79" spans="1:8" ht="15" customHeight="1">
+    <row r="79" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>73</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C79" s="3">
         <v>19</v>
@@ -4686,16 +4702,16 @@
         <v>25</v>
       </c>
       <c r="E79" s="3">
-        <f>213.96744-39.579185*C79+2.3020512*C79^2</f>
-        <v>293.00340819999997</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" ht="15" customHeight="1">
+        <f t="shared" si="2"/>
+        <v>293.00340819999997</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>74</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C80" s="3">
         <v>19</v>
@@ -4704,17 +4720,17 @@
         <v>25</v>
       </c>
       <c r="E80" s="3">
-        <f>213.96744-39.579185*C80+2.3020512*C80^2</f>
+        <f t="shared" si="2"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H80" s="18"/>
     </row>
-    <row r="81" spans="1:8" ht="15" customHeight="1">
+    <row r="81" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>75</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C81" s="3">
         <v>19</v>
@@ -4723,17 +4739,17 @@
         <v>25</v>
       </c>
       <c r="E81" s="3">
-        <f>213.96744-39.579185*C81+2.3020512*C81^2</f>
+        <f t="shared" si="2"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H81" s="18"/>
     </row>
-    <row r="82" spans="1:8" ht="15" customHeight="1">
+    <row r="82" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>76</v>
       </c>
-      <c r="B82" s="3" t="s">
-        <v>83</v>
+      <c r="B82" s="31" t="s">
+        <v>78</v>
       </c>
       <c r="C82" s="3">
         <v>19</v>
@@ -4742,16 +4758,16 @@
         <v>25</v>
       </c>
       <c r="E82" s="3">
-        <f>213.96744-39.579185*C82+2.3020512*C82^2</f>
-        <v>293.00340819999997</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" ht="15" customHeight="1">
+        <f t="shared" si="2"/>
+        <v>293.00340819999997</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <v>77</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C83" s="3">
         <v>19</v>
@@ -4760,17 +4776,17 @@
         <v>6</v>
       </c>
       <c r="E83" s="3">
-        <f>213.96744-39.579185*C83+2.3020512*C83^2</f>
+        <f t="shared" si="2"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H83" s="25"/>
     </row>
-    <row r="84" spans="1:8" ht="15" customHeight="1">
+    <row r="84" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>78</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C84" s="3">
         <v>19</v>
@@ -4779,17 +4795,17 @@
         <v>25</v>
       </c>
       <c r="E84" s="3">
-        <f>213.96744-39.579185*C84+2.3020512*C84^2</f>
+        <f t="shared" si="2"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H84" s="25"/>
     </row>
-    <row r="85" spans="1:8" ht="15" customHeight="1">
+    <row r="85" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
         <v>79</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C85" s="3">
         <v>16</v>
@@ -4798,17 +4814,17 @@
         <v>22</v>
       </c>
       <c r="E85" s="3">
-        <f>213.96744-39.579185*C85+2.3020512*C85^2</f>
+        <f t="shared" si="2"/>
         <v>170.02558720000002</v>
       </c>
       <c r="H85" s="18"/>
     </row>
-    <row r="86" spans="1:8" ht="15" customHeight="1">
+    <row r="86" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>80</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C86" s="3">
         <v>20</v>
@@ -4817,17 +4833,17 @@
         <v>26</v>
       </c>
       <c r="E86" s="3">
-        <f>213.96744-39.579185*C86+2.3020512*C86^2</f>
+        <f t="shared" si="2"/>
         <v>343.20422000000008</v>
       </c>
       <c r="H86" s="18"/>
     </row>
-    <row r="87" spans="1:8" ht="15" customHeight="1">
+    <row r="87" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <v>81</v>
       </c>
-      <c r="B87" s="3" t="s">
-        <v>88</v>
+      <c r="B87" s="31" t="s">
+        <v>194</v>
       </c>
       <c r="C87" s="3">
         <v>19</v>
@@ -4836,16 +4852,16 @@
         <v>25</v>
       </c>
       <c r="E87" s="3">
-        <f>213.96744-39.579185*C87+2.3020512*C87^2</f>
-        <v>293.00340819999997</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" ht="15" customHeight="1">
+        <f t="shared" si="2"/>
+        <v>293.00340819999997</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>82</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C88" s="3">
         <v>16</v>
@@ -4854,16 +4870,16 @@
         <v>22</v>
       </c>
       <c r="E88" s="3">
-        <f>213.96744-39.579185*C88+2.3020512*C88^2</f>
+        <f t="shared" si="2"/>
         <v>170.02558720000002</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15" customHeight="1">
+    <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
         <v>83</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C89" s="3">
         <v>19</v>
@@ -4872,17 +4888,17 @@
         <v>25</v>
       </c>
       <c r="E89" s="3">
-        <f>213.96744-39.579185*C89+2.3020512*C89^2</f>
+        <f t="shared" si="2"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H89" s="18"/>
     </row>
-    <row r="90" spans="1:8" ht="15" customHeight="1">
+    <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>84</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C90" s="3">
         <v>19</v>
@@ -4891,17 +4907,17 @@
         <v>25</v>
       </c>
       <c r="E90" s="3">
-        <f>213.96744-39.579185*C90+2.3020512*C90^2</f>
+        <f t="shared" si="2"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H90" s="15"/>
     </row>
-    <row r="91" spans="1:8" ht="15" customHeight="1">
+    <row r="91" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
         <v>85</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C91" s="3">
         <v>19</v>
@@ -4910,16 +4926,16 @@
         <v>25</v>
       </c>
       <c r="E91" s="3">
-        <f>213.96744-39.579185*C91+2.3020512*C91^2</f>
-        <v>293.00340819999997</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" ht="15" customHeight="1">
+        <f t="shared" si="2"/>
+        <v>293.00340819999997</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <v>86</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C92" s="3">
         <v>19</v>
@@ -4928,17 +4944,17 @@
         <v>25</v>
       </c>
       <c r="E92" s="3">
-        <f>213.96744-39.579185*C92+2.3020512*C92^2</f>
+        <f t="shared" si="2"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H92" s="21"/>
     </row>
-    <row r="93" spans="1:8" ht="15" customHeight="1">
+    <row r="93" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="2">
         <v>87</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C93" s="3">
         <v>19</v>
@@ -4947,17 +4963,17 @@
         <v>25</v>
       </c>
       <c r="E93" s="3">
-        <f>213.96744-39.579185*C93+2.3020512*C93^2</f>
+        <f t="shared" si="2"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H93" s="18"/>
     </row>
-    <row r="94" spans="1:8" ht="15" customHeight="1">
+    <row r="94" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <v>88</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C94" s="3">
         <v>19</v>
@@ -4966,16 +4982,16 @@
         <v>25</v>
       </c>
       <c r="E94" s="3">
-        <f>213.96744-39.579185*C94+2.3020512*C94^2</f>
-        <v>293.00340819999997</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" ht="15" customHeight="1">
+        <f t="shared" si="2"/>
+        <v>293.00340819999997</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="2">
         <v>89</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C95" s="3">
         <v>19</v>
@@ -4984,17 +5000,17 @@
         <v>25</v>
       </c>
       <c r="E95" s="3">
-        <f>213.96744-39.579185*C95+2.3020512*C95^2</f>
+        <f t="shared" si="2"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H95" s="15"/>
     </row>
-    <row r="96" spans="1:8" ht="15" customHeight="1">
+    <row r="96" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="23">
         <v>90</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C96" s="3">
         <v>19</v>
@@ -5003,16 +5019,16 @@
         <v>25</v>
       </c>
       <c r="E96" s="3">
-        <f>213.96744-39.579185*C96+2.3020512*C96^2</f>
-        <v>293.00340819999997</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" ht="15" customHeight="1">
+        <f t="shared" si="2"/>
+        <v>293.00340819999997</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="23">
         <v>110</v>
       </c>
       <c r="B97" s="26" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C97" s="3">
         <v>19</v>
@@ -5021,17 +5037,17 @@
         <v>25</v>
       </c>
       <c r="E97" s="3">
-        <f>213.96744-39.579185*C97+2.3020512*C97^2</f>
+        <f t="shared" si="2"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H97" s="22"/>
     </row>
-    <row r="98" spans="1:8" ht="15" customHeight="1">
+    <row r="98" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="23">
         <v>107</v>
       </c>
       <c r="B98" s="24" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C98" s="3">
         <v>21</v>
@@ -5040,17 +5056,17 @@
         <v>27</v>
       </c>
       <c r="E98" s="3">
-        <f>213.96744-39.579185*C98+2.3020512*C98^2</f>
+        <f t="shared" si="2"/>
         <v>398.00913420000006</v>
       </c>
       <c r="H98" s="18"/>
     </row>
-    <row r="99" spans="1:8" ht="15" customHeight="1">
+    <row r="99" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="2">
         <v>91</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C99" s="3">
         <v>20</v>
@@ -5059,17 +5075,17 @@
         <v>26</v>
       </c>
       <c r="E99" s="3">
-        <f>213.96744-39.579185*C99+2.3020512*C99^2</f>
+        <f t="shared" si="2"/>
         <v>343.20422000000008</v>
       </c>
       <c r="H99" s="25"/>
     </row>
-    <row r="100" spans="1:8" ht="15" customHeight="1">
+    <row r="100" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
         <v>92</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C100" s="3">
         <v>19</v>
@@ -5078,16 +5094,16 @@
         <v>25</v>
       </c>
       <c r="E100" s="3">
-        <f>213.96744-39.579185*C100+2.3020512*C100^2</f>
-        <v>293.00340819999997</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" ht="15" customHeight="1">
+        <f t="shared" si="2"/>
+        <v>293.00340819999997</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="2">
         <v>93</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C101" s="3">
         <v>24</v>
@@ -5096,16 +5112,16 @@
         <v>30</v>
       </c>
       <c r="E101" s="3">
-        <f>213.96744-39.579185*C101+2.3020512*C101^2</f>
+        <f t="shared" si="2"/>
         <v>590.04849120000006</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15" customHeight="1">
+    <row r="102" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
         <v>94</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C102" s="3">
         <v>19</v>
@@ -5114,17 +5130,17 @@
         <v>25</v>
       </c>
       <c r="E102" s="3">
-        <f>213.96744-39.579185*C102+2.3020512*C102^2</f>
+        <f t="shared" si="2"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H102" s="28"/>
     </row>
-    <row r="103" spans="1:8" ht="15" customHeight="1">
+    <row r="103" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="2">
         <v>95</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C103" s="3">
         <v>19</v>
@@ -5133,17 +5149,17 @@
         <v>25</v>
       </c>
       <c r="E103" s="3">
-        <f>213.96744-39.579185*C103+2.3020512*C103^2</f>
+        <f t="shared" si="2"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H103" s="18"/>
     </row>
-    <row r="104" spans="1:8" ht="15" customHeight="1">
+    <row r="104" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
         <v>96</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C104" s="3">
         <v>19</v>
@@ -5152,17 +5168,17 @@
         <v>25</v>
       </c>
       <c r="E104" s="3">
-        <f>213.96744-39.579185*C104+2.3020512*C104^2</f>
+        <f t="shared" ref="E104:E110" si="3">213.96744-39.579185*C104+2.3020512*C104^2</f>
         <v>293.00340819999997</v>
       </c>
       <c r="H104" s="18"/>
     </row>
-    <row r="105" spans="1:8" ht="15" customHeight="1">
+    <row r="105" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="2">
         <v>97</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C105" s="3">
         <v>19</v>
@@ -5171,17 +5187,17 @@
         <v>25</v>
       </c>
       <c r="E105" s="3">
-        <f>213.96744-39.579185*C105+2.3020512*C105^2</f>
+        <f t="shared" si="3"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H105" s="15"/>
     </row>
-    <row r="106" spans="1:8" ht="15" customHeight="1">
+    <row r="106" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
         <v>98</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C106" s="3">
         <v>19</v>
@@ -5190,17 +5206,17 @@
         <v>25</v>
       </c>
       <c r="E106" s="3">
-        <f>213.96744-39.579185*C106+2.3020512*C106^2</f>
+        <f t="shared" si="3"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H106" s="15"/>
     </row>
-    <row r="107" spans="1:8" ht="15" customHeight="1">
+    <row r="107" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="2">
         <v>99</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C107" s="3">
         <v>19</v>
@@ -5209,16 +5225,16 @@
         <v>25</v>
       </c>
       <c r="E107" s="3">
-        <f>213.96744-39.579185*C107+2.3020512*C107^2</f>
-        <v>293.00340819999997</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8">
+        <f t="shared" si="3"/>
+        <v>293.00340819999997</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A108" s="2">
         <v>100</v>
       </c>
       <c r="B108" s="25" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C108" s="3">
         <v>21</v>
@@ -5227,16 +5243,16 @@
         <v>27</v>
       </c>
       <c r="E108" s="3">
-        <f>213.96744-39.579185*C108+2.3020512*C108^2</f>
+        <f t="shared" si="3"/>
         <v>398.00913420000006</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="15" customHeight="1">
+    <row r="109" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="2">
         <v>101</v>
       </c>
-      <c r="B109" s="25" t="s">
-        <v>110</v>
+      <c r="B109" t="s">
+        <v>195</v>
       </c>
       <c r="C109" s="25">
         <v>21</v>
@@ -5245,16 +5261,16 @@
         <v>27</v>
       </c>
       <c r="E109" s="25">
-        <f>213.96744-39.579185*C109+2.3020512*C109^2</f>
+        <f t="shared" si="3"/>
         <v>398.00913420000006</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="15" customHeight="1">
+    <row r="110" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="30">
         <v>102</v>
       </c>
       <c r="B110" s="25" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C110" s="3">
         <v>19</v>
@@ -5263,7 +5279,7 @@
         <v>6</v>
       </c>
       <c r="E110" s="3">
-        <f>213.96744-39.579185*C110+2.3020512*C110^2</f>
+        <f t="shared" si="3"/>
         <v>293.00340819999997</v>
       </c>
       <c r="H110" s="25"/>
@@ -5274,78 +5290,79 @@
       <sortCondition ref="B1:B110"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="B111 B1:B109 B221:B1048576">
-    <cfRule type="duplicateValues" dxfId="22" priority="20"/>
+  <conditionalFormatting sqref="B111 B1:B108 B221:B1048576 H2:H109">
+    <cfRule type="duplicateValues" dxfId="23" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B111 B1:B108 B221:B1048576">
+    <cfRule type="duplicateValues" dxfId="22" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B221:B1048576 I12 B1:B108">
+    <cfRule type="duplicateValues" dxfId="21" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H17">
-    <cfRule type="duplicateValues" dxfId="21" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H51">
-    <cfRule type="duplicateValues" dxfId="20" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H58">
-    <cfRule type="duplicateValues" dxfId="18" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H59">
-    <cfRule type="duplicateValues" dxfId="15" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H60">
-    <cfRule type="duplicateValues" dxfId="12" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H61">
-    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H62:H63">
-    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B111 B1:B109 B221:B1048576 H2:H109">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B221:B1048576 I12 B1:B109">
-    <cfRule type="duplicateValues" dxfId="2" priority="45"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B221:B1048576 I12 B1:B109">
-    <cfRule type="duplicateValues" dxfId="1" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
+  <conditionalFormatting sqref="B109">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -5356,7 +5373,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1">
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -5367,7 +5384,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1">
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -5378,7 +5395,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1">
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -5389,7 +5406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1">
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>2</v>
       </c>
@@ -5400,7 +5417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1">
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>2</v>
       </c>
@@ -5411,7 +5428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1">
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>3</v>
       </c>
@@ -5422,7 +5439,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1">
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>3</v>
       </c>
@@ -5433,7 +5450,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1">
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>3</v>
       </c>
@@ -5444,7 +5461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1">
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>4</v>
       </c>
@@ -5455,7 +5472,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1">
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>4</v>
       </c>
@@ -5466,7 +5483,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1">
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>4</v>
       </c>
@@ -5477,7 +5494,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1">
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>5</v>
       </c>
@@ -5488,7 +5505,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1">
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>5</v>
       </c>
@@ -5499,7 +5516,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1">
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>5</v>
       </c>
@@ -5510,7 +5527,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1">
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>6</v>
       </c>
@@ -5521,7 +5538,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1">
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>6</v>
       </c>
@@ -5532,7 +5549,7 @@
         <v>3.66</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1">
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>6</v>
       </c>
@@ -5543,10 +5560,10 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1">
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4"/>
     </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1">
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4"/>
     </row>
   </sheetData>
@@ -5558,58 +5575,58 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>
     </row>
   </sheetData>
@@ -5621,32 +5638,32 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" customHeight="1">
+    <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C2" s="3">
         <v>0.125</v>
@@ -5655,12 +5672,12 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C3" s="3">
         <v>2.5000000000000001E-2</v>
@@ -5669,12 +5686,12 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C4" s="3">
         <v>1.7500000000000002E-2</v>
@@ -5683,12 +5700,12 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C5" s="3">
         <v>0.01</v>
@@ -5697,10 +5714,10 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4"/>
     </row>
   </sheetData>
@@ -5712,33 +5729,33 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="70" customWidth="1"/>
     <col min="3" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" customHeight="1">
+    <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C2" s="3">
         <v>0.98</v>
@@ -5747,12 +5764,12 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C3" s="3">
         <v>0.99</v>
@@ -5761,12 +5778,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C4" s="3">
         <v>1</v>
@@ -5775,12 +5792,12 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C5" s="3">
         <v>1.01</v>
@@ -5789,12 +5806,12 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C6" s="3">
         <v>1.03</v>
@@ -5803,7 +5820,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4"/>
     </row>
   </sheetData>
@@ -5815,33 +5832,33 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" customHeight="1">
+    <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C2" s="3">
         <v>160</v>
@@ -5850,12 +5867,12 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C3" s="3">
         <v>140</v>
@@ -5864,12 +5881,12 @@
         <v>90000</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C4" s="3">
         <v>115</v>
@@ -5878,12 +5895,12 @@
         <v>70000</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C5" s="3">
         <v>85</v>
@@ -5892,12 +5909,12 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C6" s="3">
         <v>60</v>
@@ -5906,10 +5923,10 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4"/>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4"/>
     </row>
   </sheetData>
@@ -5921,167 +5938,167 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B2" s="3">
         <v>9.2499999999999995E-6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="B3" s="3">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B4" s="3">
         <v>3.06</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B6" s="3">
         <v>4.5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B7" s="3">
         <v>-2</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B8" s="3">
         <v>213.96744000000001</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B9" s="3">
         <v>-39.579185000000003</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B10" s="3">
         <v>2.3020512000000002</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B11" s="3">
         <v>0</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="B12" s="3">
         <v>1</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6"/>
     </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1">
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4"/>
     </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1">
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4"/>
     </row>
-    <row r="17" spans="1:1" ht="15" customHeight="1">
+    <row r="17" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4"/>
     </row>
-    <row r="18" spans="1:1" ht="15" customHeight="1">
+    <row r="18" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4"/>
     </row>
-    <row r="19" spans="1:1" ht="15" customHeight="1">
+    <row r="19" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4"/>
     </row>
-    <row r="20" spans="1:1" ht="15" customHeight="1">
+    <row r="20" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4"/>
     </row>
-    <row r="21" spans="1:1" ht="15" customHeight="1">
+    <row r="21" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4"/>
     </row>
   </sheetData>
@@ -6093,7 +6110,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
@@ -6101,27 +6118,27 @@
     <col min="5" max="6" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" customHeight="1">
+    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -6141,7 +6158,7 @@
         <v>-12.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" customHeight="1">
+    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8">
         <v>2</v>
       </c>
@@ -6161,7 +6178,7 @@
         <v>-12.061</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15" customHeight="1">
+    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8">
         <v>3</v>
       </c>
@@ -6181,7 +6198,7 @@
         <v>-11.297000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15" customHeight="1">
+    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="8">
         <v>4</v>
       </c>
@@ -6201,7 +6218,7 @@
         <v>-10.79</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15" customHeight="1">
+    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8">
         <v>5</v>
       </c>
@@ -6221,13 +6238,13 @@
         <v>-10.1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15" customHeight="1">
+    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4"/>
     </row>
-    <row r="9" spans="1:6" ht="15" customHeight="1">
+    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4"/>
     </row>
-    <row r="10" spans="1:6" ht="15" customHeight="1">
+    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4"/>
     </row>
   </sheetData>

--- a/SMAF_lookup.xlsx
+++ b/SMAF_lookup.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohkam.singh\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uflorida-my.sharepoint.com/personal/mohkam_singh_ufl_edu/Documents/Mohkam Singh - WORDLY/Research Projects/PhD Research/gSHAPE/Github Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2208D0-B078-43A6-B2A8-D24E8CF1EF12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="164" documentId="11_95635A838F67E66DF7088085E56DEBB51F12BD57" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EB48831-8FE0-1D46-AC60-A5C02F33EEE0}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="10140" windowHeight="10170" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="500" firstSheet="12" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ph_factors" sheetId="14" r:id="rId1"/>
@@ -26,7 +26,20 @@
     <sheet name="bd_constants" sheetId="10" r:id="rId11"/>
     <sheet name="exk_texture_params" sheetId="11" r:id="rId12"/>
     <sheet name="exk_constants" sheetId="12" r:id="rId13"/>
-    <sheet name="Sheet1" sheetId="13" r:id="rId14"/>
+    <sheet name="ec_crop_factors" sheetId="15" r:id="rId14"/>
+    <sheet name="ec_texture_factors" sheetId="16" r:id="rId15"/>
+    <sheet name="ec_method_codes" sheetId="17" r:id="rId16"/>
+    <sheet name="ec_constants" sheetId="18" r:id="rId17"/>
+    <sheet name="sar_branch_params" sheetId="19" r:id="rId18"/>
+    <sheet name="sar_constants" sheetId="20" r:id="rId19"/>
+    <sheet name="agg_om_factors" sheetId="21" r:id="rId20"/>
+    <sheet name="agg_texture_factors" sheetId="22" r:id="rId21"/>
+    <sheet name="agg_fe_factors" sheetId="23" r:id="rId22"/>
+    <sheet name="agg_constants" sheetId="24" r:id="rId23"/>
+    <sheet name="pmn_om_factors" sheetId="25" r:id="rId24"/>
+    <sheet name="pmn_texture_factors" sheetId="26" r:id="rId25"/>
+    <sheet name="pmn_climate_factors" sheetId="27" r:id="rId26"/>
+    <sheet name="pmn_constants" sheetId="28" r:id="rId27"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">crop_factors!$A$1:$E$109</definedName>
@@ -56,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="286">
   <si>
     <t>Clean crop name</t>
   </si>
@@ -88,9 +101,18 @@
     <t>banana</t>
   </si>
   <si>
+    <t>barley, malt barley</t>
+  </si>
+  <si>
+    <t>beans, dried</t>
+  </si>
+  <si>
     <t>beet, red</t>
   </si>
   <si>
+    <t>bermuda grass, coastal</t>
+  </si>
+  <si>
     <t>blackberry</t>
   </si>
   <si>
@@ -178,6 +200,9 @@
     <t>fescue, tall</t>
   </si>
   <si>
+    <t>flaxseed; flax</t>
+  </si>
+  <si>
     <t>foxtail, meadow</t>
   </si>
   <si>
@@ -247,6 +272,9 @@
     <t>papaya</t>
   </si>
   <si>
+    <t>pea, field; peas</t>
+  </si>
+  <si>
     <t>peach</t>
   </si>
   <si>
@@ -307,6 +335,9 @@
     <t>sorghum</t>
   </si>
   <si>
+    <t>sorghum, grain sorghum</t>
+  </si>
+  <si>
     <t>soybean</t>
   </si>
   <si>
@@ -370,6 +401,9 @@
     <t>wheat, spring</t>
   </si>
   <si>
+    <t>winter wheat</t>
+  </si>
+  <si>
     <t>zucchini</t>
   </si>
   <si>
@@ -628,25 +662,271 @@
     <t>b</t>
   </si>
   <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>wheat, duram</t>
+  </si>
+  <si>
+    <t>tritcale</t>
+  </si>
+  <si>
+    <t>sorghum, grain sorhum</t>
+  </si>
+  <si>
+    <t>3, 7</t>
+  </si>
+  <si>
+    <t>mod. tolerance</t>
+  </si>
+  <si>
+    <t>flaxseed</t>
+  </si>
+  <si>
+    <t>bermuda grass</t>
+  </si>
+  <si>
+    <t>beans</t>
+  </si>
+  <si>
     <t>barley</t>
   </si>
   <si>
-    <t>beans</t>
-  </si>
-  <si>
-    <t>flaxseed</t>
-  </si>
-  <si>
-    <t>peas</t>
-  </si>
-  <si>
-    <t>sorghum, grain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wheat, winter </t>
-  </si>
-  <si>
-    <t>bermuda grass</t>
+    <t>cit</t>
+  </si>
+  <si>
+    <t>ref</t>
+  </si>
+  <si>
+    <t>dt</t>
+  </si>
+  <si>
+    <t>tsat</t>
+  </si>
+  <si>
+    <t>f_txt</t>
+  </si>
+  <si>
+    <t>1:1 soil:water extract (EC1:1), dS/m</t>
+  </si>
+  <si>
+    <t>one_to_one</t>
+  </si>
+  <si>
+    <t>saturated paste extract (ECsat), dS/m</t>
+  </si>
+  <si>
+    <t>sat_paste</t>
+  </si>
+  <si>
+    <t>lower clamp on final score (sheet rule: if y&lt;0 then 0)</t>
+  </si>
+  <si>
+    <t>m denominator dT^2 coefficient</t>
+  </si>
+  <si>
+    <t>m_den_c</t>
+  </si>
+  <si>
+    <t>m denominator dT coefficient</t>
+  </si>
+  <si>
+    <t>m_den_b</t>
+  </si>
+  <si>
+    <t>m denominator intercept</t>
+  </si>
+  <si>
+    <t>m_den_a</t>
+  </si>
+  <si>
+    <t>m numerator dT coefficient</t>
+  </si>
+  <si>
+    <t>m_num_b</t>
+  </si>
+  <si>
+    <t>m numerator intercept: m = (a - b*dT)/(c + d*dT - e*dT^2)</t>
+  </si>
+  <si>
+    <t>m_num_a</t>
+  </si>
+  <si>
+    <t>score between the break point and T</t>
+  </si>
+  <si>
+    <t>plateau</t>
+  </si>
+  <si>
+    <t>T1:1 = (Tsat / 1.77) * f(txt); sat paste is ~1.77x more concentrated than 1:1</t>
+  </si>
+  <si>
+    <t>dilution_factor</t>
+  </si>
+  <si>
+    <t>slope of the EC1:1 rising limb: y = 5.88 * EC</t>
+  </si>
+  <si>
+    <t>ec11_rise_slope</t>
+  </si>
+  <si>
+    <t>EC1:1 below this uses the low-EC rising limb</t>
+  </si>
+  <si>
+    <t>ec11_break</t>
+  </si>
+  <si>
+    <t>slope of the ECsat rising limb: y = 3.33 * EC</t>
+  </si>
+  <si>
+    <t>sat_rise_slope</t>
+  </si>
+  <si>
+    <t>ECsat below this uses the low-EC rising limb</t>
+  </si>
+  <si>
+    <t>sat_break</t>
+  </si>
+  <si>
+    <t>polynomial</t>
+  </si>
+  <si>
+    <t>hi</t>
+  </si>
+  <si>
+    <t>med</t>
+  </si>
+  <si>
+    <t>reciprocal_power</t>
+  </si>
+  <si>
+    <t>lo</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>form</t>
+  </si>
+  <si>
+    <t>branch</t>
+  </si>
+  <si>
+    <t>EC above this selects the 'hi' branch; between the breaks selects 'med'</t>
+  </si>
+  <si>
+    <t>ec_break_hi</t>
+  </si>
+  <si>
+    <t>EC below this selects the 'lo' branch</t>
+  </si>
+  <si>
+    <t>ec_break_lo</t>
+  </si>
+  <si>
+    <t>d2</t>
+  </si>
+  <si>
+    <t>all other suborders</t>
+  </si>
+  <si>
+    <t>Ultisols</t>
+  </si>
+  <si>
+    <t>d3</t>
+  </si>
+  <si>
+    <t>fe_class</t>
+  </si>
+  <si>
+    <t>upper clamp</t>
+  </si>
+  <si>
+    <t>lower clamp (sheet rule: if score&lt;0, then 0)</t>
+  </si>
+  <si>
+    <t>score assigned above plateau_x</t>
+  </si>
+  <si>
+    <t>plateau_score</t>
+  </si>
+  <si>
+    <t>above this AGG (%) the score is set to the plateau value</t>
+  </si>
+  <si>
+    <t>plateau_x</t>
+  </si>
+  <si>
+    <t>sinusoidal frequency (x in % aggregate stability)</t>
+  </si>
+  <si>
+    <t>sinusoidal amplitude</t>
+  </si>
+  <si>
+    <t>sinusoidal offset: y = a + b*cos(c*x - d)</t>
+  </si>
+  <si>
+    <t>max_range</t>
+  </si>
+  <si>
+    <t>c2</t>
+  </si>
+  <si>
+    <t>lo degree days / lo ppt</t>
+  </si>
+  <si>
+    <t>lo degree days / hi ppt</t>
+  </si>
+  <si>
+    <t>hi degree days / lo ppt</t>
+  </si>
+  <si>
+    <t>hi degree days / hi ppt</t>
+  </si>
+  <si>
+    <t>c3</t>
+  </si>
+  <si>
+    <t>climate_class</t>
+  </si>
+  <si>
+    <t>lower clamp</t>
+  </si>
+  <si>
+    <t>c1 quadratic squared coefficient</t>
+  </si>
+  <si>
+    <t>c1_coef_c</t>
+  </si>
+  <si>
+    <t>c1 quadratic linear coefficient</t>
+  </si>
+  <si>
+    <t>c1_coef_b</t>
+  </si>
+  <si>
+    <t>c1 = c1_coef_a + c1_coef_b*R + c1_coef_c*R^2, R = max_range</t>
+  </si>
+  <si>
+    <t>c1_coef_a</t>
+  </si>
+  <si>
+    <t>logistic scale term</t>
+  </si>
+  <si>
+    <t>logistic asymptote: y = a / (1 + b*exp(-c*x))</t>
   </si>
 </sst>
 </file>
@@ -666,40 +946,40 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF666666"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF1F4E5F"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF5A3E85"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF1E6B52"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -741,14 +1021,17 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -809,8 +1092,20 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -833,11 +1128,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -899,22 +1210,19 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{8419C8DE-5505-FC44-8716-8E50CE5C372E}"/>
   </cellStyles>
-  <dxfs count="44">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="43">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1606,13 +1914,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF1CC01C-BF2E-442A-817B-F6A0C0A3903D}">
   <dimension ref="A1:G110"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -1623,7 +1931,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
         <v>3</v>
       </c>
@@ -1635,7 +1943,7 @@
       </c>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="18" t="s">
         <v>4</v>
       </c>
@@ -1647,7 +1955,7 @@
       </c>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1659,7 +1967,7 @@
       </c>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="18" t="s">
         <v>6</v>
       </c>
@@ -1671,7 +1979,7 @@
       </c>
       <c r="G5" s="3"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="18" t="s">
         <v>7</v>
       </c>
@@ -1683,7 +1991,7 @@
       </c>
       <c r="G6" s="3"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1695,7 +2003,7 @@
       </c>
       <c r="G7" s="3"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1706,9 +2014,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>190</v>
+        <v>10</v>
       </c>
       <c r="B9">
         <v>5.5</v>
@@ -1717,9 +2025,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="15" t="s">
-        <v>191</v>
+        <v>11</v>
       </c>
       <c r="B10" s="15">
         <v>6</v>
@@ -1728,9 +2036,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="18" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B11" s="17">
         <v>5.5</v>
@@ -1739,9 +2047,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="25" t="s">
-        <v>196</v>
+        <v>13</v>
       </c>
       <c r="B12">
         <v>5.8</v>
@@ -1750,9 +2058,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="18" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B13" s="17">
         <v>5.5</v>
@@ -1761,9 +2069,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B14">
         <v>4.3</v>
@@ -1772,9 +2080,9 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="27" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B15" s="17">
         <v>6</v>
@@ -1783,9 +2091,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="27" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B16" s="17">
         <v>6</v>
@@ -1794,9 +2102,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="27" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B17" s="17">
         <v>6</v>
@@ -1805,9 +2113,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="18" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B18" s="17">
         <v>5.5</v>
@@ -1818,9 +2126,9 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="18" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B19" s="17">
         <v>6</v>
@@ -1831,9 +2139,9 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="15" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B20" s="15">
         <v>5.5</v>
@@ -1842,9 +2150,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B21">
         <v>5.5</v>
@@ -1853,9 +2161,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="15" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B22" s="15">
         <v>6.2</v>
@@ -1864,9 +2172,9 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B23">
         <v>5.5</v>
@@ -1875,9 +2183,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="17" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B24" s="17">
         <v>5.5</v>
@@ -1886,9 +2194,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="18" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B25" s="17">
         <v>5.5</v>
@@ -1897,9 +2205,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="18" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B26" s="17">
         <v>6</v>
@@ -1908,9 +2216,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="18" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B27" s="17">
         <v>6</v>
@@ -1919,9 +2227,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="19" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B28" s="20">
         <v>6</v>
@@ -1930,9 +2238,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="19" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B29" s="20">
         <v>5.5</v>
@@ -1941,9 +2249,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="15" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B30" s="15">
         <v>5</v>
@@ -1952,9 +2260,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="25" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B31">
         <v>5.8</v>
@@ -1963,9 +2271,9 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="25" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B32">
         <v>5.8</v>
@@ -1974,9 +2282,9 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="25" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B33">
         <v>5.8</v>
@@ -1985,9 +2293,9 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="15" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B34" s="15">
         <v>5.8</v>
@@ -1996,9 +2304,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B35">
         <v>5.5</v>
@@ -2007,9 +2315,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B36" s="20">
         <v>4</v>
@@ -2018,9 +2326,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B37">
         <v>5.5</v>
@@ -2029,9 +2337,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="15" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B38" s="15">
         <v>6</v>
@@ -2040,9 +2348,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="18" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B39" s="17">
         <v>4.5</v>
@@ -2051,9 +2359,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="15" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B40" s="15">
         <v>5.5</v>
@@ -2062,9 +2370,9 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="25" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B41">
         <v>5.8</v>
@@ -2073,9 +2381,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="15" t="s">
-        <v>192</v>
+        <v>43</v>
       </c>
       <c r="B42" s="15">
         <v>6</v>
@@ -2084,9 +2392,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="18" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B43" s="20">
         <v>6.5</v>
@@ -2095,9 +2403,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="15" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B44" s="15">
         <v>6</v>
@@ -2106,9 +2414,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B45">
         <v>6</v>
@@ -2117,9 +2425,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="15" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B46" s="15">
         <v>5.5</v>
@@ -2128,9 +2436,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B47">
         <v>5.5</v>
@@ -2139,9 +2447,9 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="18" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B48" s="17">
         <v>4.5</v>
@@ -2150,9 +2458,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="18" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B49" s="17">
         <v>6</v>
@@ -2161,9 +2469,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="18" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B50" s="17">
         <v>5.5</v>
@@ -2172,9 +2480,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="27" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B51" s="20">
         <v>5.5</v>
@@ -2183,9 +2491,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="15" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B52" s="15">
         <v>6</v>
@@ -2194,9 +2502,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B53">
         <v>6</v>
@@ -2205,9 +2513,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="18" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B54" s="17">
         <v>5</v>
@@ -2216,9 +2524,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="18" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B55" s="17">
         <v>5.5</v>
@@ -2227,9 +2535,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" s="15" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B56" s="15">
         <v>6</v>
@@ -2238,9 +2546,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="18" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B57" s="17">
         <v>6</v>
@@ -2249,9 +2557,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="27" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B58" s="17">
         <v>5</v>
@@ -2260,9 +2568,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="27" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B59" s="17">
         <v>5</v>
@@ -2271,9 +2579,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" s="26" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B60">
         <v>5.8</v>
@@ -2282,9 +2590,9 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" s="29" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B61" s="15">
         <v>6</v>
@@ -2293,9 +2601,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" s="26" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B62">
         <v>5.5</v>
@@ -2304,9 +2612,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" s="26" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B63">
         <v>5.6</v>
@@ -2315,9 +2623,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" s="25" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B64">
         <v>5.8</v>
@@ -2326,9 +2634,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B65">
         <v>6</v>
@@ -2337,9 +2645,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>193</v>
+        <v>67</v>
       </c>
       <c r="B66">
         <v>6</v>
@@ -2348,9 +2656,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B67">
         <v>6</v>
@@ -2359,9 +2667,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="15" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B68" s="15">
         <v>6</v>
@@ -2370,9 +2678,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="18" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B69" s="17">
         <v>5</v>
@@ -2381,9 +2689,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="18" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B70" s="17">
         <v>5.5</v>
@@ -2392,9 +2700,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" s="15" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B71" s="15">
         <v>6</v>
@@ -2403,9 +2711,9 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="18" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B72" s="17">
         <v>5</v>
@@ -2414,9 +2722,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="18" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B73" s="17">
         <v>4.5</v>
@@ -2425,9 +2733,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="18" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B74" s="17">
         <v>5</v>
@@ -2436,9 +2744,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" s="15" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B75" s="15">
         <v>4</v>
@@ -2447,9 +2755,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B76">
         <v>5</v>
@@ -2458,9 +2766,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="18" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B77" s="17">
         <v>5.6</v>
@@ -2469,9 +2777,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="18" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B78" s="17">
         <v>6</v>
@@ -2480,9 +2788,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B79">
         <v>5</v>
@@ -2491,9 +2799,9 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="18" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B80" s="17">
         <v>6</v>
@@ -2502,9 +2810,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="18" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B81" s="17">
         <v>5.5</v>
@@ -2513,9 +2821,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B82">
         <v>5.5</v>
@@ -2524,9 +2832,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83" s="25" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B83">
         <v>5.8</v>
@@ -2535,9 +2843,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A84" s="25" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B84">
         <v>5.8</v>
@@ -2546,9 +2854,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="18" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B85" s="17">
         <v>6</v>
@@ -2557,9 +2865,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="18" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B86" s="17">
         <v>6</v>
@@ -2568,9 +2876,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>194</v>
+        <v>88</v>
       </c>
       <c r="B87">
         <v>5.5</v>
@@ -2579,9 +2887,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B88">
         <v>5.5</v>
@@ -2590,9 +2898,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="18" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B89" s="17">
         <v>6</v>
@@ -2601,9 +2909,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="15" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B90" s="15">
         <v>6</v>
@@ -2612,9 +2920,9 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B91">
         <v>5</v>
@@ -2623,9 +2931,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="21" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B92" s="17">
         <v>6</v>
@@ -2634,9 +2942,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="18" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B93" s="17">
         <v>6</v>
@@ -2645,9 +2953,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B94">
         <v>5</v>
@@ -2656,9 +2964,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A95" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B95" s="15">
         <v>6.5</v>
@@ -2667,9 +2975,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B96">
         <v>5</v>
@@ -2678,9 +2986,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97" s="22" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B97" s="22">
         <v>4.5</v>
@@ -2689,9 +2997,9 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="18" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B98" s="17">
         <v>5</v>
@@ -2700,9 +3008,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" s="25" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B99">
         <v>5.8</v>
@@ -2711,9 +3019,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B100">
         <v>5</v>
@@ -2722,9 +3030,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B101">
         <v>5.5</v>
@@ -2733,9 +3041,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102" s="28" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B102" s="15">
         <v>6</v>
@@ -2744,9 +3052,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A103" s="18" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B103" s="17">
         <v>5.5</v>
@@ -2755,9 +3063,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A104" s="18" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B104" s="17">
         <v>5.5</v>
@@ -2766,9 +3074,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105" s="15" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B105" s="15">
         <v>6</v>
@@ -2777,9 +3085,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106" s="15" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B106" s="15">
         <v>6</v>
@@ -2788,9 +3096,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B107">
         <v>5.5</v>
@@ -2799,9 +3107,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B108">
         <v>5.5</v>
@@ -2810,9 +3118,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
       <c r="B109">
         <v>5.5</v>
@@ -2821,9 +3129,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A110" s="25" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B110" s="15">
         <v>6</v>
@@ -2839,42 +3147,42 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A2:A109">
-    <cfRule type="duplicateValues" dxfId="43" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A17">
-    <cfRule type="duplicateValues" dxfId="42" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51">
-    <cfRule type="duplicateValues" dxfId="41" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58">
-    <cfRule type="duplicateValues" dxfId="39" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59">
-    <cfRule type="duplicateValues" dxfId="36" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A60">
-    <cfRule type="duplicateValues" dxfId="33" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61">
-    <cfRule type="duplicateValues" dxfId="30" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A62:A63">
-    <cfRule type="duplicateValues" dxfId="27" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18:G19">
-    <cfRule type="duplicateValues" dxfId="24" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="41"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2883,25 +3191,25 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8">
         <v>0</v>
       </c>
@@ -2912,7 +3220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>1</v>
       </c>
@@ -2923,7 +3231,7 @@
         <v>5.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
         <v>2</v>
       </c>
@@ -2934,7 +3242,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>3</v>
       </c>
@@ -2945,10 +3253,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
     </row>
   </sheetData>
@@ -2960,116 +3268,116 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B2" s="3">
         <v>0.99399999999999999</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B3" s="3">
         <v>3.6950899999999999E-5</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B4" s="3">
         <v>11.628251000000001</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B5" s="3">
         <v>-1.1878</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B6" s="3">
         <v>-8.4931999999999999</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B8" s="3">
         <v>0.99399999999999999</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10"/>
     </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4"/>
     </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4"/>
     </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4"/>
     </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4"/>
     </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4"/>
     </row>
   </sheetData>
@@ -3081,61 +3389,61 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="12">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
     </row>
   </sheetData>
@@ -3147,26 +3455,26 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B2" s="3">
         <v>1.0541326</v>
@@ -3175,9 +3483,9 @@
         <v>-9.8126979999999999E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B3" s="3">
         <v>1.0744899999999999</v>
@@ -3186,16 +3494,16 @@
         <v>-1.3431848999999999E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="13"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="4"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
     </row>
   </sheetData>
@@ -3205,10 +3513,2500 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BAE779D-EE07-4BAA-A5AD-49FE70D75EAE}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{836DB690-0274-1B49-B2C0-097C9048DAF6}">
+  <dimension ref="A1:F110"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.83203125" style="31"/>
+    <col min="2" max="2" width="22.1640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>210</v>
+      </c>
+      <c r="D1" s="35" t="s">
+        <v>209</v>
+      </c>
+      <c r="E1" s="35" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1" s="35" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="32">
+        <v>1</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="32">
+        <v>2</v>
+      </c>
+      <c r="D2" s="32">
+        <v>7.3</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F2" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="32">
+        <v>2</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="32">
+        <v>1.5</v>
+      </c>
+      <c r="D3" s="32">
+        <v>19</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F3" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="32">
+        <v>3</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="32">
+        <v>1.6</v>
+      </c>
+      <c r="D4" s="32">
+        <v>10</v>
+      </c>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="32">
+        <v>4</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="32">
+        <v>1.6</v>
+      </c>
+      <c r="D5" s="32">
+        <v>24</v>
+      </c>
+      <c r="E5" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F5" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="32">
+        <v>5</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="32">
+        <v>7.1</v>
+      </c>
+      <c r="D6" s="32">
+        <v>10</v>
+      </c>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="32">
+        <v>6</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="32">
+        <v>1.6</v>
+      </c>
+      <c r="D7" s="32">
+        <v>10</v>
+      </c>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="32">
+        <v>7</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="32">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D8" s="32">
+        <v>10</v>
+      </c>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="32">
+        <v>8</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>206</v>
+      </c>
+      <c r="C9" s="32">
+        <v>6</v>
+      </c>
+      <c r="D9" s="32">
+        <v>7.1</v>
+      </c>
+      <c r="E9" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F9" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="32">
+        <v>9</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>205</v>
+      </c>
+      <c r="C10" s="32">
+        <v>1</v>
+      </c>
+      <c r="D10" s="32">
+        <v>19</v>
+      </c>
+      <c r="E10" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F10" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="32">
+        <v>10</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="32">
+        <v>4</v>
+      </c>
+      <c r="D11" s="32">
+        <v>9</v>
+      </c>
+      <c r="E11" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F11" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="32">
+        <v>11</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="C12" s="32">
+        <v>6.9</v>
+      </c>
+      <c r="D12" s="32">
+        <v>6.4</v>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F12" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="32">
+        <v>12</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="32">
+        <v>1.5</v>
+      </c>
+      <c r="D13" s="32">
+        <v>22</v>
+      </c>
+      <c r="E13" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F13" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="32">
+        <v>13</v>
+      </c>
+      <c r="B14" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="32">
+        <v>2</v>
+      </c>
+      <c r="D14" s="32">
+        <v>10</v>
+      </c>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="32">
+        <v>14</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="32">
+        <v>9</v>
+      </c>
+      <c r="D15" s="32">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="32">
+        <v>15</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="32">
+        <v>1.3</v>
+      </c>
+      <c r="D16" s="32">
+        <v>10</v>
+      </c>
+      <c r="E16" s="32" t="s">
+        <v>202</v>
+      </c>
+      <c r="F16" s="32"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="32">
+        <v>16</v>
+      </c>
+      <c r="B17" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="32">
+        <v>1.3</v>
+      </c>
+      <c r="D17" s="32">
+        <v>10</v>
+      </c>
+      <c r="E17" s="32" t="s">
+        <v>202</v>
+      </c>
+      <c r="F17" s="32"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="32">
+        <v>17</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="32">
+        <v>1.5</v>
+      </c>
+      <c r="D18" s="32">
+        <v>22</v>
+      </c>
+      <c r="E18" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F18" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="32">
+        <v>18</v>
+      </c>
+      <c r="B19" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="32">
+        <v>2.8</v>
+      </c>
+      <c r="D19" s="32">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E19" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F19" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="32">
+        <v>19</v>
+      </c>
+      <c r="B20" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="32">
+        <v>6</v>
+      </c>
+      <c r="D20" s="32">
+        <v>10</v>
+      </c>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="32">
+        <v>20</v>
+      </c>
+      <c r="B21" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="32">
+        <v>1.8</v>
+      </c>
+      <c r="D21" s="32">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="E21" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F21" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="32">
+        <v>21</v>
+      </c>
+      <c r="B22" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="32">
+        <v>3</v>
+      </c>
+      <c r="D22" s="32">
+        <v>10</v>
+      </c>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="32">
+        <v>22</v>
+      </c>
+      <c r="B23" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="32">
+        <v>1</v>
+      </c>
+      <c r="D23" s="32">
+        <v>14</v>
+      </c>
+      <c r="E23" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F23" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="33">
+        <v>108</v>
+      </c>
+      <c r="B24" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="32">
+        <v>1.7</v>
+      </c>
+      <c r="D24" s="32">
+        <v>12</v>
+      </c>
+      <c r="E24" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F24" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="32">
+        <v>23</v>
+      </c>
+      <c r="B25" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="32">
+        <v>2.5</v>
+      </c>
+      <c r="D25" s="32">
+        <v>10</v>
+      </c>
+      <c r="E25" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F25" s="32"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" s="32">
+        <v>24</v>
+      </c>
+      <c r="B26" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="32">
+        <v>1.8</v>
+      </c>
+      <c r="D26" s="32">
+        <v>6.2</v>
+      </c>
+      <c r="E26" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F26" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="32">
+        <v>25</v>
+      </c>
+      <c r="B27" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" s="32">
+        <v>1.5</v>
+      </c>
+      <c r="D27" s="32">
+        <v>10</v>
+      </c>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="32">
+        <v>26</v>
+      </c>
+      <c r="B28" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="32">
+        <v>1.5</v>
+      </c>
+      <c r="D28" s="32">
+        <v>5.7</v>
+      </c>
+      <c r="E28" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F28" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="32">
+        <v>28</v>
+      </c>
+      <c r="B29" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="32">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="D29" s="32">
+        <v>19</v>
+      </c>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" s="32">
+        <v>29</v>
+      </c>
+      <c r="B30" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="32">
+        <v>2</v>
+      </c>
+      <c r="D30" s="32">
+        <v>10</v>
+      </c>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" s="32">
+        <v>30</v>
+      </c>
+      <c r="B31" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" s="32">
+        <v>1.7</v>
+      </c>
+      <c r="D31" s="32">
+        <v>12</v>
+      </c>
+      <c r="E31" s="32"/>
+      <c r="F31" s="32"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" s="32">
+        <v>31</v>
+      </c>
+      <c r="B32" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="32">
+        <v>1.7</v>
+      </c>
+      <c r="D32" s="32">
+        <v>12</v>
+      </c>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" s="32">
+        <v>32</v>
+      </c>
+      <c r="B33" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="32">
+        <v>1.8</v>
+      </c>
+      <c r="D33" s="32">
+        <v>7.4</v>
+      </c>
+      <c r="E33" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F33" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" s="32">
+        <v>33</v>
+      </c>
+      <c r="B34" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="32">
+        <v>7.7</v>
+      </c>
+      <c r="D34" s="32">
+        <v>5.2</v>
+      </c>
+      <c r="E34" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F34" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" s="32">
+        <v>34</v>
+      </c>
+      <c r="B35" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" s="32">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D35" s="32">
+        <v>12</v>
+      </c>
+      <c r="E35" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F35" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" s="32">
+        <v>35</v>
+      </c>
+      <c r="B36" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" s="32">
+        <v>2</v>
+      </c>
+      <c r="D36" s="32">
+        <v>10</v>
+      </c>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" s="32">
+        <v>36</v>
+      </c>
+      <c r="B37" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C37" s="32">
+        <v>2.5</v>
+      </c>
+      <c r="D37" s="32">
+        <v>13</v>
+      </c>
+      <c r="E37" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F37" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" s="32">
+        <v>37</v>
+      </c>
+      <c r="B38" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="32">
+        <v>4</v>
+      </c>
+      <c r="D38" s="32">
+        <v>3.6</v>
+      </c>
+      <c r="E38" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F38" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" s="36">
+        <v>109</v>
+      </c>
+      <c r="B39" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39" s="33">
+        <v>6</v>
+      </c>
+      <c r="D39" s="33">
+        <v>10</v>
+      </c>
+      <c r="E39" s="33"/>
+      <c r="F39" s="33"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40" s="32">
+        <v>38</v>
+      </c>
+      <c r="B40" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="C40" s="32">
+        <v>1.6</v>
+      </c>
+      <c r="D40" s="32">
+        <v>9.6</v>
+      </c>
+      <c r="E40" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F40" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" s="32">
+        <v>39</v>
+      </c>
+      <c r="B41" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41" s="32">
+        <v>3.9</v>
+      </c>
+      <c r="D41" s="32">
+        <v>5.3</v>
+      </c>
+      <c r="E41" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F41" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42" s="32">
+        <v>40</v>
+      </c>
+      <c r="B42" s="35" t="s">
+        <v>203</v>
+      </c>
+      <c r="C42" s="32">
+        <v>1.7</v>
+      </c>
+      <c r="D42" s="32">
+        <v>12</v>
+      </c>
+      <c r="E42" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F42" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43" s="32">
+        <v>41</v>
+      </c>
+      <c r="B43" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" s="32">
+        <v>1.5</v>
+      </c>
+      <c r="D43" s="32">
+        <v>9.6</v>
+      </c>
+      <c r="E43" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F43" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44" s="32">
+        <v>42</v>
+      </c>
+      <c r="B44" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C44" s="32">
+        <v>2</v>
+      </c>
+      <c r="D44" s="32">
+        <v>10</v>
+      </c>
+      <c r="E44" s="32"/>
+      <c r="F44" s="32"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45" s="32">
+        <v>43</v>
+      </c>
+      <c r="B45" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45" s="32">
+        <v>1.5</v>
+      </c>
+      <c r="D45" s="32">
+        <v>9.6</v>
+      </c>
+      <c r="E45" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F45" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46" s="32">
+        <v>44</v>
+      </c>
+      <c r="B46" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="C46" s="32">
+        <v>1.8</v>
+      </c>
+      <c r="D46" s="32">
+        <v>16</v>
+      </c>
+      <c r="E46" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F46" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" s="32">
+        <v>45</v>
+      </c>
+      <c r="B47" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C47" s="32">
+        <v>4</v>
+      </c>
+      <c r="D47" s="32">
+        <v>10</v>
+      </c>
+      <c r="E47" s="32"/>
+      <c r="F47" s="32"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48" s="36">
+        <v>105</v>
+      </c>
+      <c r="B48" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C48" s="32">
+        <v>5</v>
+      </c>
+      <c r="D48" s="32">
+        <v>8</v>
+      </c>
+      <c r="E48" s="32"/>
+      <c r="F48" s="32">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A49" s="32">
+        <v>46</v>
+      </c>
+      <c r="B49" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="C49" s="32">
+        <v>4</v>
+      </c>
+      <c r="D49" s="32">
+        <v>10</v>
+      </c>
+      <c r="E49" s="32"/>
+      <c r="F49" s="32"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50" s="32">
+        <v>47</v>
+      </c>
+      <c r="B50" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C50" s="32">
+        <v>1.3</v>
+      </c>
+      <c r="D50" s="32">
+        <v>10</v>
+      </c>
+      <c r="E50" s="32" t="s">
+        <v>202</v>
+      </c>
+      <c r="F50" s="32"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51" s="32">
+        <v>48</v>
+      </c>
+      <c r="B51" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="C51" s="32">
+        <v>4</v>
+      </c>
+      <c r="D51" s="32">
+        <v>10</v>
+      </c>
+      <c r="E51" s="32"/>
+      <c r="F51" s="32"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A52" s="32">
+        <v>49</v>
+      </c>
+      <c r="B52" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="C52" s="32">
+        <v>1</v>
+      </c>
+      <c r="D52" s="32">
+        <v>10</v>
+      </c>
+      <c r="E52" s="32"/>
+      <c r="F52" s="32"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A53" s="32">
+        <v>50</v>
+      </c>
+      <c r="B53" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="C53" s="32">
+        <v>1.3</v>
+      </c>
+      <c r="D53" s="32">
+        <v>13</v>
+      </c>
+      <c r="E53" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F53" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A54" s="32">
+        <v>51</v>
+      </c>
+      <c r="B54" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="C54" s="32">
+        <v>4</v>
+      </c>
+      <c r="D54" s="32">
+        <v>10</v>
+      </c>
+      <c r="E54" s="32"/>
+      <c r="F54" s="32"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A55" s="32">
+        <v>52</v>
+      </c>
+      <c r="B55" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C55" s="32">
+        <v>2</v>
+      </c>
+      <c r="D55" s="32">
+        <v>10</v>
+      </c>
+      <c r="E55" s="32"/>
+      <c r="F55" s="32"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A56" s="32">
+        <v>53</v>
+      </c>
+      <c r="B56" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="C56" s="32">
+        <v>8</v>
+      </c>
+      <c r="D56" s="32">
+        <v>5</v>
+      </c>
+      <c r="E56" s="32" t="s">
+        <v>202</v>
+      </c>
+      <c r="F56" s="32"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A57" s="32">
+        <v>54</v>
+      </c>
+      <c r="B57" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="C57" s="32">
+        <v>2</v>
+      </c>
+      <c r="D57" s="32">
+        <v>10</v>
+      </c>
+      <c r="E57" s="32"/>
+      <c r="F57" s="32"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A58" s="36">
+        <v>104</v>
+      </c>
+      <c r="B58" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="C58" s="33">
+        <v>5</v>
+      </c>
+      <c r="D58" s="33">
+        <v>8</v>
+      </c>
+      <c r="E58" s="33"/>
+      <c r="F58" s="33">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A59" s="36">
+        <v>106</v>
+      </c>
+      <c r="B59" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="C59" s="33">
+        <v>5</v>
+      </c>
+      <c r="D59" s="33">
+        <v>8</v>
+      </c>
+      <c r="E59" s="33"/>
+      <c r="F59" s="33">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A60" s="32">
+        <v>55</v>
+      </c>
+      <c r="B60" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="C60" s="32">
+        <v>2.5</v>
+      </c>
+      <c r="D60" s="32">
+        <v>10</v>
+      </c>
+      <c r="E60" s="32"/>
+      <c r="F60" s="32"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A61" s="32">
+        <v>56</v>
+      </c>
+      <c r="B61" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C61" s="32">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D61" s="32">
+        <v>0</v>
+      </c>
+      <c r="E61" s="32"/>
+      <c r="F61" s="32"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A62" s="32">
+        <v>57</v>
+      </c>
+      <c r="B62" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C62" s="32">
+        <v>1.2</v>
+      </c>
+      <c r="D62" s="32">
+        <v>16</v>
+      </c>
+      <c r="E62" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F62" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A63" s="32">
+        <v>58</v>
+      </c>
+      <c r="B63" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C63" s="32">
+        <v>1.7</v>
+      </c>
+      <c r="D63" s="32">
+        <v>16</v>
+      </c>
+      <c r="E63" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F63" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A64" s="32">
+        <v>59</v>
+      </c>
+      <c r="B64" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="C64" s="32">
+        <v>1.5</v>
+      </c>
+      <c r="D64" s="32">
+        <v>6.2</v>
+      </c>
+      <c r="E64" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F64" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A65" s="32">
+        <v>60</v>
+      </c>
+      <c r="B65" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="C65" s="32">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D65" s="32">
+        <v>10</v>
+      </c>
+      <c r="E65" s="32"/>
+      <c r="F65" s="32"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A66" s="32">
+        <v>61</v>
+      </c>
+      <c r="B66" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C66" s="32">
+        <v>1.6</v>
+      </c>
+      <c r="D66" s="32">
+        <v>10</v>
+      </c>
+      <c r="E66" s="32"/>
+      <c r="F66" s="32"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A67" s="32">
+        <v>62</v>
+      </c>
+      <c r="B67" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="C67" s="32">
+        <v>1.7</v>
+      </c>
+      <c r="D67" s="32">
+        <v>21</v>
+      </c>
+      <c r="E67" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F67" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A68" s="32">
+        <v>63</v>
+      </c>
+      <c r="B68" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="C68" s="32">
+        <v>3.2</v>
+      </c>
+      <c r="D68" s="32">
+        <v>29</v>
+      </c>
+      <c r="E68" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F68" s="32"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A69" s="32">
+        <v>64</v>
+      </c>
+      <c r="B69" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C69" s="32">
+        <v>1.6</v>
+      </c>
+      <c r="D69" s="32">
+        <v>10</v>
+      </c>
+      <c r="E69" s="32"/>
+      <c r="F69" s="32"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A70" s="32">
+        <v>65</v>
+      </c>
+      <c r="B70" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C70" s="32">
+        <v>2</v>
+      </c>
+      <c r="D70" s="32">
+        <v>10</v>
+      </c>
+      <c r="E70" s="32"/>
+      <c r="F70" s="32"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A71" s="32">
+        <v>66</v>
+      </c>
+      <c r="B71" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="C71" s="32">
+        <v>1.5</v>
+      </c>
+      <c r="D71" s="32">
+        <v>14</v>
+      </c>
+      <c r="E71" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F71" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A72" s="32">
+        <v>67</v>
+      </c>
+      <c r="B72" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="C72" s="32">
+        <v>6</v>
+      </c>
+      <c r="D72" s="32">
+        <v>10</v>
+      </c>
+      <c r="E72" s="32"/>
+      <c r="F72" s="32"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A73" s="31">
+        <v>103</v>
+      </c>
+      <c r="B73" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="C73" s="32">
+        <v>6</v>
+      </c>
+      <c r="D73" s="32">
+        <v>10</v>
+      </c>
+      <c r="E73" s="32"/>
+      <c r="F73" s="32"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A74" s="32">
+        <v>68</v>
+      </c>
+      <c r="B74" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="C74" s="32">
+        <v>6</v>
+      </c>
+      <c r="D74" s="32">
+        <v>10</v>
+      </c>
+      <c r="E74" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F74" s="34" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A75" s="32">
+        <v>69</v>
+      </c>
+      <c r="B75" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="C75" s="32">
+        <v>6</v>
+      </c>
+      <c r="D75" s="32">
+        <v>10</v>
+      </c>
+      <c r="E75" s="32"/>
+      <c r="F75" s="32"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A76" s="32">
+        <v>70</v>
+      </c>
+      <c r="B76" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="C76" s="32">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D76" s="32">
+        <v>10</v>
+      </c>
+      <c r="E76" s="32"/>
+      <c r="F76" s="32"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A77" s="32">
+        <v>71</v>
+      </c>
+      <c r="B77" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="C77" s="32">
+        <v>1.5</v>
+      </c>
+      <c r="D77" s="32">
+        <v>18</v>
+      </c>
+      <c r="E77" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F77" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A78" s="32">
+        <v>72</v>
+      </c>
+      <c r="B78" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C78" s="32">
+        <v>4</v>
+      </c>
+      <c r="D78" s="32">
+        <v>0</v>
+      </c>
+      <c r="E78" s="32"/>
+      <c r="F78" s="32"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A79" s="32">
+        <v>73</v>
+      </c>
+      <c r="B79" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C79" s="32">
+        <v>1.7</v>
+      </c>
+      <c r="D79" s="32">
+        <v>12</v>
+      </c>
+      <c r="E79" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F79" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A80" s="32">
+        <v>74</v>
+      </c>
+      <c r="B80" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C80" s="32">
+        <v>1.2</v>
+      </c>
+      <c r="D80" s="32">
+        <v>13</v>
+      </c>
+      <c r="E80" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F80" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A81" s="32">
+        <v>75</v>
+      </c>
+      <c r="B81" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="C81" s="32">
+        <v>1.6</v>
+      </c>
+      <c r="D81" s="32">
+        <v>10</v>
+      </c>
+      <c r="E81" s="32"/>
+      <c r="F81" s="32"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A82" s="32">
+        <v>76</v>
+      </c>
+      <c r="B82" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="C82" s="32">
+        <v>3</v>
+      </c>
+      <c r="D82" s="32">
+        <v>12</v>
+      </c>
+      <c r="E82" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F82" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A83" s="32">
+        <v>77</v>
+      </c>
+      <c r="B83" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="C83" s="34">
+        <v>5.6</v>
+      </c>
+      <c r="D83" s="34">
+        <v>7.6</v>
+      </c>
+      <c r="E83" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F83" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A84" s="32">
+        <v>78</v>
+      </c>
+      <c r="B84" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="C84" s="32">
+        <v>5.6</v>
+      </c>
+      <c r="D84" s="32">
+        <v>7.6</v>
+      </c>
+      <c r="E84" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F84" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A85" s="32">
+        <v>79</v>
+      </c>
+      <c r="B85" s="32" t="s">
+        <v>86</v>
+      </c>
+      <c r="C85" s="32">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D85" s="32">
+        <v>10</v>
+      </c>
+      <c r="E85" s="32"/>
+      <c r="F85" s="32"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A86" s="32">
+        <v>80</v>
+      </c>
+      <c r="B86" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="C86" s="32">
+        <v>5</v>
+      </c>
+      <c r="D86" s="32">
+        <v>8.1325000000000003</v>
+      </c>
+      <c r="E86" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F86" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A87" s="32">
+        <v>81</v>
+      </c>
+      <c r="B87" s="32" t="s">
+        <v>200</v>
+      </c>
+      <c r="C87" s="32">
+        <v>6</v>
+      </c>
+      <c r="D87" s="32">
+        <v>10</v>
+      </c>
+      <c r="E87" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F87" s="32"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A88" s="32">
+        <v>82</v>
+      </c>
+      <c r="B88" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="C88" s="32">
+        <v>5</v>
+      </c>
+      <c r="D88" s="32">
+        <v>20</v>
+      </c>
+      <c r="E88" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F88" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A89" s="32">
+        <v>83</v>
+      </c>
+      <c r="B89" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="C89" s="32">
+        <v>2</v>
+      </c>
+      <c r="D89" s="32">
+        <v>7.6</v>
+      </c>
+      <c r="E89" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F89" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A90" s="32">
+        <v>84</v>
+      </c>
+      <c r="B90" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C90" s="32">
+        <v>3.2</v>
+      </c>
+      <c r="D90" s="32">
+        <v>16</v>
+      </c>
+      <c r="E90" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F90" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A91" s="32">
+        <v>85</v>
+      </c>
+      <c r="B91" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="C91" s="32">
+        <v>1</v>
+      </c>
+      <c r="D91" s="32">
+        <v>33</v>
+      </c>
+      <c r="E91" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F91" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A92" s="32">
+        <v>86</v>
+      </c>
+      <c r="B92" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="C92" s="32">
+        <v>2.8</v>
+      </c>
+      <c r="D92" s="32">
+        <v>4.3</v>
+      </c>
+      <c r="E92" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F92" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A93" s="32">
+        <v>87</v>
+      </c>
+      <c r="B93" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="C93" s="32">
+        <v>7</v>
+      </c>
+      <c r="D93" s="32">
+        <v>5.9</v>
+      </c>
+      <c r="E93" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F93" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A94" s="32">
+        <v>88</v>
+      </c>
+      <c r="B94" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="C94" s="32">
+        <v>1.7</v>
+      </c>
+      <c r="D94" s="32">
+        <v>5.9</v>
+      </c>
+      <c r="E94" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F94" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A95" s="32">
+        <v>89</v>
+      </c>
+      <c r="B95" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="C95" s="32">
+        <v>2.5</v>
+      </c>
+      <c r="D95" s="32">
+        <v>10</v>
+      </c>
+      <c r="E95" s="32"/>
+      <c r="F95" s="32"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A96" s="32">
+        <v>90</v>
+      </c>
+      <c r="B96" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="C96" s="32">
+        <v>1.5</v>
+      </c>
+      <c r="D96" s="32">
+        <v>11</v>
+      </c>
+      <c r="E96" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F96" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A97" s="33">
+        <v>110</v>
+      </c>
+      <c r="B97" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="C97" s="33">
+        <v>1.6</v>
+      </c>
+      <c r="D97" s="33">
+        <v>10</v>
+      </c>
+      <c r="E97" s="33"/>
+      <c r="F97" s="33"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A98" s="33">
+        <v>107</v>
+      </c>
+      <c r="B98" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="C98" s="33">
+        <v>1.8</v>
+      </c>
+      <c r="D98" s="33">
+        <v>7.4</v>
+      </c>
+      <c r="E98" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="F98" s="33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A99" s="32">
+        <v>91</v>
+      </c>
+      <c r="B99" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C99" s="32">
+        <v>2</v>
+      </c>
+      <c r="D99" s="33">
+        <v>6.2</v>
+      </c>
+      <c r="E99" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F99" s="32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A100" s="32">
+        <v>92</v>
+      </c>
+      <c r="B100" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="C100" s="32">
+        <v>2</v>
+      </c>
+      <c r="D100" s="32">
+        <v>10</v>
+      </c>
+      <c r="E100" s="32"/>
+      <c r="F100" s="32"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A101" s="32">
+        <v>93</v>
+      </c>
+      <c r="B101" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="C101" s="32">
+        <v>2.5</v>
+      </c>
+      <c r="D101" s="32">
+        <v>9.9</v>
+      </c>
+      <c r="E101" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F101" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A102" s="32">
+        <v>94</v>
+      </c>
+      <c r="B102" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C102" s="32">
+        <v>7.1</v>
+      </c>
+      <c r="D102" s="32">
+        <v>0</v>
+      </c>
+      <c r="E102" s="32"/>
+      <c r="F102" s="32"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A103" s="32">
+        <v>95</v>
+      </c>
+      <c r="B103" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="C103" s="32">
+        <v>0.9</v>
+      </c>
+      <c r="D103" s="32">
+        <v>9</v>
+      </c>
+      <c r="E103" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F103" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A104" s="32">
+        <v>96</v>
+      </c>
+      <c r="B104" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="C104" s="32">
+        <v>3</v>
+      </c>
+      <c r="D104" s="32">
+        <v>11</v>
+      </c>
+      <c r="E104" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F104" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A105" s="32">
+        <v>97</v>
+      </c>
+      <c r="B105" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="C105" s="32">
+        <v>2</v>
+      </c>
+      <c r="D105" s="32">
+        <v>10</v>
+      </c>
+      <c r="E105" s="32"/>
+      <c r="F105" s="32"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A106" s="32">
+        <v>98</v>
+      </c>
+      <c r="B106" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="C106" s="32">
+        <v>2.5</v>
+      </c>
+      <c r="D106" s="32">
+        <v>10</v>
+      </c>
+      <c r="E106" s="32"/>
+      <c r="F106" s="32"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A107" s="32">
+        <v>99</v>
+      </c>
+      <c r="B107" s="32" t="s">
+        <v>198</v>
+      </c>
+      <c r="C107" s="32">
+        <v>5.7</v>
+      </c>
+      <c r="D107" s="32">
+        <v>5.4</v>
+      </c>
+      <c r="E107" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F107" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A108" s="32">
+        <v>100</v>
+      </c>
+      <c r="B108" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="C108" s="32">
+        <v>6</v>
+      </c>
+      <c r="D108" s="32">
+        <v>7.1</v>
+      </c>
+      <c r="E108" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F108" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A109" s="32">
+        <v>101</v>
+      </c>
+      <c r="B109" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="C109" s="32">
+        <v>6</v>
+      </c>
+      <c r="D109" s="32">
+        <v>7.1</v>
+      </c>
+      <c r="E109" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F109" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A110" s="32">
+        <v>102</v>
+      </c>
+      <c r="B110" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="C110" s="32">
+        <v>4.7</v>
+      </c>
+      <c r="D110" s="32">
+        <v>9</v>
+      </c>
+      <c r="E110" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F110" s="32">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB2800B6-9A9D-0540-829B-0E7333B4C1BF}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="32">
+        <v>1</v>
+      </c>
+      <c r="B2" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="32">
+        <v>2</v>
+      </c>
+      <c r="B3" s="32">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="32">
+        <v>3</v>
+      </c>
+      <c r="B4" s="32">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="32">
+        <v>4</v>
+      </c>
+      <c r="B5" s="32">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="32">
+        <v>5</v>
+      </c>
+      <c r="B6" s="32">
+        <v>1.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B9BE1A8-8916-494A-9C59-4C1D0AC1A125}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.1640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="32">
+        <v>1</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>215</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="32">
+        <v>2</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="C3" s="32" t="s">
+        <v>212</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEC29394-7904-DE41-AA7C-594860F085E7}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15" style="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="65.6640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="37" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="31" t="s">
+        <v>238</v>
+      </c>
+      <c r="B2" s="31">
+        <v>0.3</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="31" t="s">
+        <v>236</v>
+      </c>
+      <c r="B3" s="31">
+        <v>3.33</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="31" t="s">
+        <v>234</v>
+      </c>
+      <c r="B4" s="31">
+        <v>0.17</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="31" t="s">
+        <v>232</v>
+      </c>
+      <c r="B5" s="31">
+        <v>5.88</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="31" t="s">
+        <v>230</v>
+      </c>
+      <c r="B6" s="31">
+        <v>1.77</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="31" t="s">
+        <v>228</v>
+      </c>
+      <c r="B7" s="31">
+        <v>1</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="31" t="s">
+        <v>226</v>
+      </c>
+      <c r="B8" s="31">
+        <v>0.5091</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="31" t="s">
+        <v>224</v>
+      </c>
+      <c r="B9" s="31">
+        <v>161.58000000000001</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="31" t="s">
+        <v>222</v>
+      </c>
+      <c r="B10" s="31">
+        <v>1</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="31" t="s">
+        <v>220</v>
+      </c>
+      <c r="B11" s="31">
+        <v>484.2</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="31" t="s">
+        <v>218</v>
+      </c>
+      <c r="B12" s="31">
+        <v>16.14</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="B13" s="31">
+        <v>0</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="B14" s="31">
+        <v>1</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>175</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBC0FA2F-B4B4-EA47-9464-ADEF25FE852A}">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="7.33203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" style="31" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7" style="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.6640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" style="31" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>250</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>249</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>248</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>247</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>246</v>
+      </c>
+      <c r="H1" s="31" t="s">
+        <v>245</v>
+      </c>
+      <c r="I1" s="31" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="31" t="s">
+        <v>243</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" s="31">
+        <v>4.056</v>
+      </c>
+      <c r="D2" s="31">
+        <v>0.79300000000000004</v>
+      </c>
+      <c r="E2" s="31">
+        <v>3.05</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>239</v>
+      </c>
+      <c r="C3" s="31">
+        <v>0.8</v>
+      </c>
+      <c r="D3" s="31">
+        <v>1.298857E-2</v>
+      </c>
+      <c r="E3" s="31">
+        <v>-6.7000000000000004E-2</v>
+      </c>
+      <c r="F3" s="31">
+        <v>2.5700000000000001E-2</v>
+      </c>
+      <c r="G3" s="31">
+        <v>-5.3600000000000002E-3</v>
+      </c>
+      <c r="H3" s="31">
+        <v>5.4699999999999996E-4</v>
+      </c>
+      <c r="I3" s="31">
+        <v>-2.1100000000000001E-5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="31" t="s">
+        <v>240</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>239</v>
+      </c>
+      <c r="C4" s="31">
+        <v>1</v>
+      </c>
+      <c r="D4" s="31">
+        <v>-7.0199999999999999E-2</v>
+      </c>
+      <c r="E4" s="31">
+        <v>1.0500000000000001E-2</v>
+      </c>
+      <c r="F4" s="31">
+        <v>-6.8000000000000005E-4</v>
+      </c>
+      <c r="G4" s="31">
+        <v>-2.3900000000000002E-5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5C9FE61-D242-2C47-8FE8-E6503E877DAB}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.6640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="63.5" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="31" t="s">
+        <v>254</v>
+      </c>
+      <c r="B2" s="31">
+        <v>0.2</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="31" t="s">
+        <v>252</v>
+      </c>
+      <c r="B3" s="31">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="B4" s="31">
+        <v>0</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5" s="31">
+        <v>1</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>175</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3216,33 +6014,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H110"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
     <col min="3" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="8" max="8" width="22.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -3261,7 +6059,7 @@
       </c>
       <c r="H2" s="16"/>
     </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -3280,7 +6078,7 @@
       </c>
       <c r="H3" s="18"/>
     </row>
-    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -3298,7 +6096,7 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -3317,7 +6115,7 @@
       </c>
       <c r="H5" s="18"/>
     </row>
-    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -3336,7 +6134,7 @@
       </c>
       <c r="H6" s="18"/>
     </row>
-    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -3354,7 +6152,7 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -3372,12 +6170,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="31" t="s">
-        <v>190</v>
+      <c r="B9" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="C9" s="3">
         <v>19</v>
@@ -3390,12 +6188,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="31" t="s">
-        <v>191</v>
+      <c r="B10" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="C10" s="3">
         <v>20</v>
@@ -3409,12 +6207,12 @@
       </c>
       <c r="H10" s="15"/>
     </row>
-    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3">
         <v>19</v>
@@ -3428,12 +6226,12 @@
       </c>
       <c r="H11" s="18"/>
     </row>
-    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="31" t="s">
-        <v>196</v>
+      <c r="B12" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="C12" s="3">
         <v>19</v>
@@ -3447,12 +6245,12 @@
       </c>
       <c r="H12" s="25"/>
     </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C13" s="3">
         <v>19</v>
@@ -3466,12 +6264,12 @@
       </c>
       <c r="H13" s="18"/>
     </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C14" s="3">
         <v>19</v>
@@ -3484,12 +6282,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C15" s="3">
         <v>19</v>
@@ -3503,12 +6301,12 @@
       </c>
       <c r="H15" s="27"/>
     </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C16" s="3">
         <v>12</v>
@@ -3522,12 +6320,12 @@
       </c>
       <c r="H16" s="27"/>
     </row>
-    <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C17" s="3">
         <v>12</v>
@@ -3541,12 +6339,12 @@
       </c>
       <c r="H17" s="27"/>
     </row>
-    <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C18" s="3">
         <v>19</v>
@@ -3560,12 +6358,12 @@
       </c>
       <c r="H18" s="18"/>
     </row>
-    <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C19" s="3">
         <v>19</v>
@@ -3579,12 +6377,12 @@
       </c>
       <c r="H19" s="18"/>
     </row>
-    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C20" s="3">
         <v>19</v>
@@ -3598,12 +6396,12 @@
       </c>
       <c r="H20" s="15"/>
     </row>
-    <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C21" s="3">
         <v>19</v>
@@ -3616,12 +6414,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C22" s="3">
         <v>19</v>
@@ -3635,12 +6433,12 @@
       </c>
       <c r="H22" s="15"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C23" s="3">
         <v>19</v>
@@ -3653,12 +6451,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="23">
         <v>108</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C24" s="3">
         <v>19</v>
@@ -3672,12 +6470,12 @@
       </c>
       <c r="H24" s="17"/>
     </row>
-    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>23</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C25" s="3">
         <v>19</v>
@@ -3691,12 +6489,12 @@
       </c>
       <c r="H25" s="18"/>
     </row>
-    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>24</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C26" s="3">
         <v>19</v>
@@ -3710,12 +6508,12 @@
       </c>
       <c r="H26" s="18"/>
     </row>
-    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>25</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C27" s="3">
         <v>19</v>
@@ -3729,12 +6527,12 @@
       </c>
       <c r="H27" s="18"/>
     </row>
-    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>26</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C28" s="3">
         <v>19</v>
@@ -3748,12 +6546,12 @@
       </c>
       <c r="H28" s="19"/>
     </row>
-    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C29" s="3">
         <v>22</v>
@@ -3767,12 +6565,12 @@
       </c>
       <c r="H29" s="19"/>
     </row>
-    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C30" s="3">
         <v>19</v>
@@ -3786,12 +6584,12 @@
       </c>
       <c r="H30" s="15"/>
     </row>
-    <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>32</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C31" s="3">
         <v>19</v>
@@ -3805,12 +6603,12 @@
       </c>
       <c r="H31" s="25"/>
     </row>
-    <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C32" s="3">
         <v>19</v>
@@ -3824,12 +6622,12 @@
       </c>
       <c r="H32" s="25"/>
     </row>
-    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>30</v>
       </c>
-      <c r="B33" s="31" t="s">
-        <v>31</v>
+      <c r="B33" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="C33" s="3">
         <v>16</v>
@@ -3843,12 +6641,12 @@
       </c>
       <c r="H33" s="25"/>
     </row>
-    <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C34" s="3">
         <v>19</v>
@@ -3862,12 +6660,12 @@
       </c>
       <c r="H34" s="15"/>
     </row>
-    <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C35" s="3">
         <v>19</v>
@@ -3880,12 +6678,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C36" s="3">
         <v>19</v>
@@ -3899,12 +6697,12 @@
       </c>
       <c r="H36" s="18"/>
     </row>
-    <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C37" s="3">
         <v>19</v>
@@ -3917,12 +6715,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C38" s="3">
         <v>19</v>
@@ -3936,12 +6734,12 @@
       </c>
       <c r="H38" s="15"/>
     </row>
-    <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="23">
         <v>109</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C39" s="26">
         <v>19</v>
@@ -3954,12 +6752,12 @@
       </c>
       <c r="H39" s="18"/>
     </row>
-    <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>38</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C40" s="3">
         <v>19</v>
@@ -3973,12 +6771,12 @@
       </c>
       <c r="H40" s="15"/>
     </row>
-    <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>39</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C41" s="3">
         <v>12</v>
@@ -3992,12 +6790,12 @@
       </c>
       <c r="H41" s="25"/>
     </row>
-    <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>40</v>
       </c>
-      <c r="B42" s="31" t="s">
-        <v>192</v>
+      <c r="B42" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="C42" s="3">
         <v>19</v>
@@ -4011,12 +6809,12 @@
       </c>
       <c r="H42" s="15"/>
     </row>
-    <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>41</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C43" s="3">
         <v>19</v>
@@ -4030,12 +6828,12 @@
       </c>
       <c r="H43" s="18"/>
     </row>
-    <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>42</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C44" s="3">
         <v>19</v>
@@ -4049,12 +6847,12 @@
       </c>
       <c r="H44" s="15"/>
     </row>
-    <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>43</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C45" s="3">
         <v>19</v>
@@ -4067,12 +6865,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>44</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C46" s="3">
         <v>19</v>
@@ -4086,12 +6884,12 @@
       </c>
       <c r="H46" s="15"/>
     </row>
-    <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>45</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C47" s="3">
         <v>19</v>
@@ -4104,12 +6902,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>105</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C48" s="3">
         <v>19</v>
@@ -4123,12 +6921,12 @@
       </c>
       <c r="H48" s="18"/>
     </row>
-    <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>46</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C49" s="3">
         <v>19</v>
@@ -4142,12 +6940,12 @@
       </c>
       <c r="H49" s="18"/>
     </row>
-    <row r="50" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>47</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C50" s="3">
         <v>12</v>
@@ -4161,12 +6959,12 @@
       </c>
       <c r="H50" s="18"/>
     </row>
-    <row r="51" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>48</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C51" s="3">
         <v>19</v>
@@ -4180,12 +6978,12 @@
       </c>
       <c r="H51" s="27"/>
     </row>
-    <row r="52" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>49</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C52" s="3">
         <v>19</v>
@@ -4199,12 +6997,12 @@
       </c>
       <c r="H52" s="15"/>
     </row>
-    <row r="53" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>50</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C53" s="3">
         <v>19</v>
@@ -4217,12 +7015,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>51</v>
       </c>
-      <c r="B54" s="31" t="s">
-        <v>51</v>
+      <c r="B54" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="C54" s="3">
         <v>19</v>
@@ -4236,12 +7034,12 @@
       </c>
       <c r="H54" s="18"/>
     </row>
-    <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>52</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C55" s="3">
         <v>19</v>
@@ -4255,12 +7053,12 @@
       </c>
       <c r="H55" s="18"/>
     </row>
-    <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>53</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C56" s="3">
         <v>19</v>
@@ -4274,12 +7072,12 @@
       </c>
       <c r="H56" s="15"/>
     </row>
-    <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>54</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C57" s="3">
         <v>19</v>
@@ -4293,12 +7091,12 @@
       </c>
       <c r="H57" s="18"/>
     </row>
-    <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>104</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C58" s="3">
         <v>19</v>
@@ -4312,12 +7110,12 @@
       </c>
       <c r="H58" s="27"/>
     </row>
-    <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>106</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C59" s="3">
         <v>19</v>
@@ -4331,12 +7129,12 @@
       </c>
       <c r="H59" s="27"/>
     </row>
-    <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>55</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C60" s="3">
         <v>19</v>
@@ -4350,12 +7148,12 @@
       </c>
       <c r="H60" s="26"/>
     </row>
-    <row r="61" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>56</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C61" s="3">
         <v>19</v>
@@ -4369,12 +7167,12 @@
       </c>
       <c r="H61" s="29"/>
     </row>
-    <row r="62" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>57</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C62" s="3">
         <v>19</v>
@@ -4388,12 +7186,12 @@
       </c>
       <c r="H62" s="26"/>
     </row>
-    <row r="63" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>58</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C63" s="3">
         <v>19</v>
@@ -4407,12 +7205,12 @@
       </c>
       <c r="H63" s="26"/>
     </row>
-    <row r="64" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>59</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C64" s="3">
         <v>20</v>
@@ -4426,12 +7224,12 @@
       </c>
       <c r="H64" s="25"/>
     </row>
-    <row r="65" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>60</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C65" s="3">
         <v>19</v>
@@ -4444,12 +7242,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>61</v>
       </c>
-      <c r="B66" s="31" t="s">
-        <v>193</v>
+      <c r="B66" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="C66" s="3">
         <v>19</v>
@@ -4462,12 +7260,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>62</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C67" s="3">
         <v>19</v>
@@ -4480,12 +7278,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>63</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C68" s="3">
         <v>19</v>
@@ -4499,12 +7297,12 @@
       </c>
       <c r="H68" s="15"/>
     </row>
-    <row r="69" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>64</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C69" s="3">
         <v>19</v>
@@ -4518,12 +7316,12 @@
       </c>
       <c r="H69" s="18"/>
     </row>
-    <row r="70" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>65</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C70" s="3">
         <v>19</v>
@@ -4537,12 +7335,12 @@
       </c>
       <c r="H70" s="18"/>
     </row>
-    <row r="71" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>66</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C71" s="3">
         <v>19</v>
@@ -4556,12 +7354,12 @@
       </c>
       <c r="H71" s="15"/>
     </row>
-    <row r="72" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>67</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C72" s="3">
         <v>19</v>
@@ -4575,12 +7373,12 @@
       </c>
       <c r="H72" s="18"/>
     </row>
-    <row r="73" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>103</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C73" s="3">
         <v>19</v>
@@ -4594,12 +7392,12 @@
       </c>
       <c r="H73" s="18"/>
     </row>
-    <row r="74" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>68</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C74" s="3">
         <v>19</v>
@@ -4613,12 +7411,12 @@
       </c>
       <c r="H74" s="18"/>
     </row>
-    <row r="75" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>69</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C75" s="3">
         <v>19</v>
@@ -4632,12 +7430,12 @@
       </c>
       <c r="H75" s="15"/>
     </row>
-    <row r="76" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>70</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C76" s="3">
         <v>19</v>
@@ -4650,12 +7448,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>71</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C77" s="3">
         <v>19</v>
@@ -4669,12 +7467,12 @@
       </c>
       <c r="H77" s="18"/>
     </row>
-    <row r="78" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>72</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C78" s="3">
         <v>19</v>
@@ -4688,12 +7486,12 @@
       </c>
       <c r="H78" s="18"/>
     </row>
-    <row r="79" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>73</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C79" s="3">
         <v>19</v>
@@ -4706,12 +7504,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>74</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C80" s="3">
         <v>19</v>
@@ -4725,12 +7523,12 @@
       </c>
       <c r="H80" s="18"/>
     </row>
-    <row r="81" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>75</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C81" s="3">
         <v>19</v>
@@ -4744,12 +7542,12 @@
       </c>
       <c r="H81" s="18"/>
     </row>
-    <row r="82" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>76</v>
       </c>
-      <c r="B82" s="31" t="s">
-        <v>78</v>
+      <c r="B82" s="3" t="s">
+        <v>83</v>
       </c>
       <c r="C82" s="3">
         <v>19</v>
@@ -4762,12 +7560,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>77</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C83" s="3">
         <v>19</v>
@@ -4781,12 +7579,12 @@
       </c>
       <c r="H83" s="25"/>
     </row>
-    <row r="84" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>78</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C84" s="3">
         <v>19</v>
@@ -4800,12 +7598,12 @@
       </c>
       <c r="H84" s="25"/>
     </row>
-    <row r="85" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>79</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C85" s="3">
         <v>16</v>
@@ -4819,12 +7617,12 @@
       </c>
       <c r="H85" s="18"/>
     </row>
-    <row r="86" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>80</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C86" s="3">
         <v>20</v>
@@ -4838,12 +7636,12 @@
       </c>
       <c r="H86" s="18"/>
     </row>
-    <row r="87" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>81</v>
       </c>
-      <c r="B87" s="31" t="s">
-        <v>194</v>
+      <c r="B87" s="3" t="s">
+        <v>88</v>
       </c>
       <c r="C87" s="3">
         <v>19</v>
@@ -4856,12 +7654,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>82</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C88" s="3">
         <v>16</v>
@@ -4874,12 +7672,12 @@
         <v>170.02558720000002</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>83</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C89" s="3">
         <v>19</v>
@@ -4893,12 +7691,12 @@
       </c>
       <c r="H89" s="18"/>
     </row>
-    <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>84</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C90" s="3">
         <v>19</v>
@@ -4912,12 +7710,12 @@
       </c>
       <c r="H90" s="15"/>
     </row>
-    <row r="91" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>85</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C91" s="3">
         <v>19</v>
@@ -4930,12 +7728,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>86</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C92" s="3">
         <v>19</v>
@@ -4949,12 +7747,12 @@
       </c>
       <c r="H92" s="21"/>
     </row>
-    <row r="93" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>87</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C93" s="3">
         <v>19</v>
@@ -4968,12 +7766,12 @@
       </c>
       <c r="H93" s="18"/>
     </row>
-    <row r="94" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>88</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C94" s="3">
         <v>19</v>
@@ -4986,12 +7784,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>89</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C95" s="3">
         <v>19</v>
@@ -5005,12 +7803,12 @@
       </c>
       <c r="H95" s="15"/>
     </row>
-    <row r="96" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="23">
         <v>90</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C96" s="3">
         <v>19</v>
@@ -5023,12 +7821,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="23">
         <v>110</v>
       </c>
       <c r="B97" s="26" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C97" s="3">
         <v>19</v>
@@ -5042,12 +7840,12 @@
       </c>
       <c r="H97" s="22"/>
     </row>
-    <row r="98" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="23">
         <v>107</v>
       </c>
       <c r="B98" s="24" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C98" s="3">
         <v>21</v>
@@ -5061,12 +7859,12 @@
       </c>
       <c r="H98" s="18"/>
     </row>
-    <row r="99" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>91</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C99" s="3">
         <v>20</v>
@@ -5080,12 +7878,12 @@
       </c>
       <c r="H99" s="25"/>
     </row>
-    <row r="100" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>92</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C100" s="3">
         <v>19</v>
@@ -5098,12 +7896,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>93</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C101" s="3">
         <v>24</v>
@@ -5116,12 +7914,12 @@
         <v>590.04849120000006</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>94</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C102" s="3">
         <v>19</v>
@@ -5135,12 +7933,12 @@
       </c>
       <c r="H102" s="28"/>
     </row>
-    <row r="103" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>95</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C103" s="3">
         <v>19</v>
@@ -5154,12 +7952,12 @@
       </c>
       <c r="H103" s="18"/>
     </row>
-    <row r="104" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
         <v>96</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C104" s="3">
         <v>19</v>
@@ -5173,12 +7971,12 @@
       </c>
       <c r="H104" s="18"/>
     </row>
-    <row r="105" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
         <v>97</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C105" s="3">
         <v>19</v>
@@ -5192,12 +7990,12 @@
       </c>
       <c r="H105" s="15"/>
     </row>
-    <row r="106" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
         <v>98</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C106" s="3">
         <v>19</v>
@@ -5211,12 +8009,12 @@
       </c>
       <c r="H106" s="15"/>
     </row>
-    <row r="107" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
         <v>99</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C107" s="3">
         <v>19</v>
@@ -5229,12 +8027,12 @@
         <v>293.00340819999997</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
         <v>100</v>
       </c>
       <c r="B108" s="25" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C108" s="3">
         <v>21</v>
@@ -5247,12 +8045,12 @@
         <v>398.00913420000006</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
         <v>101</v>
       </c>
-      <c r="B109" t="s">
-        <v>195</v>
+      <c r="B109" s="25" t="s">
+        <v>110</v>
       </c>
       <c r="C109" s="25">
         <v>21</v>
@@ -5265,12 +8063,12 @@
         <v>398.00913420000006</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="30">
         <v>102</v>
       </c>
       <c r="B110" s="25" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C110" s="3">
         <v>19</v>
@@ -5290,79 +8088,630 @@
       <sortCondition ref="B1:B110"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="B111 B1:B108 B221:B1048576 H2:H109">
-    <cfRule type="duplicateValues" dxfId="23" priority="2"/>
+  <conditionalFormatting sqref="B111 B1:B109 B221:B1048576 H2:H109">
+    <cfRule type="duplicateValues" dxfId="22" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B111 B1:B108 B221:B1048576">
-    <cfRule type="duplicateValues" dxfId="22" priority="21"/>
+  <conditionalFormatting sqref="B111 B1:B109 B221:B1048576">
+    <cfRule type="duplicateValues" dxfId="21" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B221:B1048576 I12 B1:B108">
-    <cfRule type="duplicateValues" dxfId="21" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="56"/>
+  <conditionalFormatting sqref="B221:B1048576 I12 B1:B109">
+    <cfRule type="duplicateValues" dxfId="20" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H17">
-    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H51">
-    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H58">
-    <cfRule type="duplicateValues" dxfId="15" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H59">
-    <cfRule type="duplicateValues" dxfId="12" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H60">
-    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H61">
-    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H62:H63">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B109">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80E82622-3A88-1F49-AF68-ACF99F08B025}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9" style="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="31">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31">
+        <v>1.2211053932890721</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="31">
+        <v>2</v>
+      </c>
+      <c r="B3" s="31">
+        <v>1.071538695091609</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="31">
+        <v>3</v>
+      </c>
+      <c r="B4" s="31">
+        <v>1.0199111676417569</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="31">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31">
+        <v>0.89993807834392991</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{166D6D86-0BDA-FD46-9BB9-94583C9F87C6}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="31">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="31">
+        <v>2</v>
+      </c>
+      <c r="B3" s="31">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="31">
+        <v>3</v>
+      </c>
+      <c r="B4" s="31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="31">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31">
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="31">
+        <v>5</v>
+      </c>
+      <c r="B6" s="31">
+        <v>1.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{029A5F8F-540F-E94B-9527-3EDB7663841A}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>259</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>258</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="31">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="31">
+        <v>2</v>
+      </c>
+      <c r="B3" s="31">
+        <v>1</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>256</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{875DC3DE-2C15-3443-97EB-5AABBFF7996B}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.5" style="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.83203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="B2" s="31">
+        <v>-0.8</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="31">
+        <v>1.7992999999999999</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="31" t="s">
+        <v>248</v>
+      </c>
+      <c r="B4" s="31">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="31" t="s">
+        <v>265</v>
+      </c>
+      <c r="B5" s="31">
+        <v>50</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="31" t="s">
+        <v>263</v>
+      </c>
+      <c r="B6" s="31">
+        <v>1</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="B7" s="31">
+        <v>0</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="B8" s="31">
+        <v>1</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>260</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1519B359-C8FB-1343-8A59-305FA9F6C139}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="31">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="31">
+        <v>2</v>
+      </c>
+      <c r="B3" s="31">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="31">
+        <v>3</v>
+      </c>
+      <c r="B4" s="31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="31">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8111133-DD08-734B-987A-5A530EA1088A}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="31">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="31">
+        <v>2</v>
+      </c>
+      <c r="B3" s="31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="31">
+        <v>3</v>
+      </c>
+      <c r="B4" s="31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="31">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="31">
+        <v>5</v>
+      </c>
+      <c r="B6" s="31">
+        <v>0.85</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2699350C-1394-CE43-A292-F6F4D0638F13}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.33203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>276</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="31">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31">
+        <v>0.9</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="31">
+        <v>2</v>
+      </c>
+      <c r="B3" s="31">
+        <v>0.95</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="31">
+        <v>3</v>
+      </c>
+      <c r="B4" s="31">
+        <v>1</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="31">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31">
+        <v>1.05</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9718C2D7-90BE-1C44-A7E5-A36AAAADA09D}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.6640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.6640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="B2" s="31">
+        <v>1</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="31">
+        <v>161.32</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="B4" s="31">
+        <v>1.1531499999999999</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="31" t="s">
+        <v>281</v>
+      </c>
+      <c r="B5" s="31">
+        <v>-3.993E-2</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="31" t="s">
+        <v>279</v>
+      </c>
+      <c r="B6" s="31">
+        <v>4.438E-4</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="B7" s="31">
+        <v>0</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="B8" s="31">
+        <v>1</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>260</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -5373,7 +8722,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -5384,7 +8733,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -5395,7 +8744,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -5406,7 +8755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>2</v>
       </c>
@@ -5417,7 +8766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>2</v>
       </c>
@@ -5428,7 +8777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>3</v>
       </c>
@@ -5439,7 +8788,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>3</v>
       </c>
@@ -5450,7 +8799,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>3</v>
       </c>
@@ -5461,7 +8810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>4</v>
       </c>
@@ -5472,7 +8821,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>4</v>
       </c>
@@ -5483,7 +8832,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>4</v>
       </c>
@@ -5494,7 +8843,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>5</v>
       </c>
@@ -5505,7 +8854,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>5</v>
       </c>
@@ -5516,7 +8865,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>5</v>
       </c>
@@ -5527,7 +8876,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>6</v>
       </c>
@@ -5538,7 +8887,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>6</v>
       </c>
@@ -5549,7 +8898,7 @@
         <v>3.66</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>6</v>
       </c>
@@ -5560,10 +8909,10 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
     </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
     </row>
   </sheetData>
@@ -5575,58 +8924,58 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4"/>
     </row>
   </sheetData>
@@ -5638,32 +8987,32 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C2" s="3">
         <v>0.125</v>
@@ -5672,12 +9021,12 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C3" s="3">
         <v>2.5000000000000001E-2</v>
@@ -5686,12 +9035,12 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C4" s="3">
         <v>1.7500000000000002E-2</v>
@@ -5700,12 +9049,12 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C5" s="3">
         <v>0.01</v>
@@ -5714,10 +9063,10 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
     </row>
   </sheetData>
@@ -5729,33 +9078,33 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="70" customWidth="1"/>
     <col min="3" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C2" s="3">
         <v>0.98</v>
@@ -5764,12 +9113,12 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C3" s="3">
         <v>0.99</v>
@@ -5778,12 +9127,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C4" s="3">
         <v>1</v>
@@ -5792,12 +9141,12 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C5" s="3">
         <v>1.01</v>
@@ -5806,12 +9155,12 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C6" s="3">
         <v>1.03</v>
@@ -5820,7 +9169,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
     </row>
   </sheetData>
@@ -5832,33 +9181,33 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C2" s="3">
         <v>160</v>
@@ -5867,12 +9216,12 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C3" s="3">
         <v>140</v>
@@ -5881,12 +9230,12 @@
         <v>90000</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C4" s="3">
         <v>115</v>
@@ -5895,12 +9244,12 @@
         <v>70000</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="C5" s="3">
         <v>85</v>
@@ -5909,12 +9258,12 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C6" s="3">
         <v>60</v>
@@ -5923,10 +9272,10 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
     </row>
   </sheetData>
@@ -5938,167 +9287,167 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="B2" s="3">
         <v>9.2499999999999995E-6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B3" s="3">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B4" s="3">
         <v>3.06</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="B6" s="3">
         <v>4.5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B7" s="3">
         <v>-2</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B8" s="3">
         <v>213.96744000000001</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B9" s="3">
         <v>-39.579185000000003</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B10" s="3">
         <v>2.3020512000000002</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B11" s="3">
         <v>0</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B12" s="3">
         <v>1</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6"/>
     </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4"/>
     </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4"/>
     </row>
-    <row r="17" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
     </row>
-    <row r="18" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4"/>
     </row>
-    <row r="19" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4"/>
     </row>
-    <row r="20" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
     </row>
-    <row r="21" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
     </row>
   </sheetData>
@@ -6110,7 +9459,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
@@ -6118,27 +9467,27 @@
     <col min="5" max="6" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -6158,7 +9507,7 @@
         <v>-12.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>2</v>
       </c>
@@ -6178,7 +9527,7 @@
         <v>-12.061</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
         <v>3</v>
       </c>
@@ -6198,7 +9547,7 @@
         <v>-11.297000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>4</v>
       </c>
@@ -6218,7 +9567,7 @@
         <v>-10.79</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
         <v>5</v>
       </c>
@@ -6238,13 +9587,13 @@
         <v>-10.1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
     </row>
-    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
     </row>
-    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
     </row>
   </sheetData>

--- a/SMAF_lookup.xlsx
+++ b/SMAF_lookup.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uflorida-my.sharepoint.com/personal/mohkam_singh_ufl_edu/Documents/Mohkam Singh - WORDLY/Research Projects/PhD Research/gSHAPE/Github Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="164" documentId="11_95635A838F67E66DF7088085E56DEBB51F12BD57" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EB48831-8FE0-1D46-AC60-A5C02F33EEE0}"/>
+  <xr:revisionPtr revIDLastSave="166" documentId="11_95635A838F67E66DF7088085E56DEBB51F12BD57" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A69C7750-BE9E-0249-823D-3CFFF60840F1}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="500" firstSheet="12" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="500" firstSheet="27" activeTab="35" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ph_factors" sheetId="14" r:id="rId1"/>
@@ -40,6 +40,22 @@
     <sheet name="pmn_texture_factors" sheetId="26" r:id="rId25"/>
     <sheet name="pmn_climate_factors" sheetId="27" r:id="rId26"/>
     <sheet name="pmn_constants" sheetId="28" r:id="rId27"/>
+    <sheet name="awc_texture_params" sheetId="29" r:id="rId28"/>
+    <sheet name="awc_om_factors" sheetId="30" r:id="rId29"/>
+    <sheet name="awc_region_codes" sheetId="31" r:id="rId30"/>
+    <sheet name="awc_constants" sheetId="32" r:id="rId31"/>
+    <sheet name="wfps_texture_params" sheetId="33" r:id="rId32"/>
+    <sheet name="wfps_env_constants" sheetId="34" r:id="rId33"/>
+    <sheet name="wfps_weighting" sheetId="35" r:id="rId34"/>
+    <sheet name="wfps_constants" sheetId="36" r:id="rId35"/>
+    <sheet name="mbc_om_factors" sheetId="37" r:id="rId36"/>
+    <sheet name="mbc_texture_factors" sheetId="38" r:id="rId37"/>
+    <sheet name="mbc_season_climate_factors" sheetId="39" r:id="rId38"/>
+    <sheet name="mbc_constants" sheetId="40" r:id="rId39"/>
+    <sheet name="soc_om_factors" sheetId="41" r:id="rId40"/>
+    <sheet name="soc_texture_factors" sheetId="42" r:id="rId41"/>
+    <sheet name="soc_climate_factors" sheetId="43" r:id="rId42"/>
+    <sheet name="soc_constants" sheetId="44" r:id="rId43"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">crop_factors!$A$1:$E$109</definedName>
@@ -69,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="335">
   <si>
     <t>Clean crop name</t>
   </si>
@@ -927,6 +943,153 @@
   </si>
   <si>
     <t>logistic asymptote: y = a / (1 + b*exp(-c*x))</t>
+  </si>
+  <si>
+    <t>d_humid</t>
+  </si>
+  <si>
+    <t>b1_arid</t>
+  </si>
+  <si>
+    <t>b2_arid</t>
+  </si>
+  <si>
+    <t>humid Land Resource Regions A and K-V -&gt; sinusoidal curve</t>
+  </si>
+  <si>
+    <t>humid</t>
+  </si>
+  <si>
+    <t>arid Land Resource Regions B-J -&gt; MMF curve</t>
+  </si>
+  <si>
+    <t>arid</t>
+  </si>
+  <si>
+    <t>region_code</t>
+  </si>
+  <si>
+    <t>upper clamp; both raw curves exceed 1.0 (arid asymptote 1.088)</t>
+  </si>
+  <si>
+    <t>humid sinusoidal frequency (x in g H2O / g soil)</t>
+  </si>
+  <si>
+    <t>sin_c</t>
+  </si>
+  <si>
+    <t>humid sinusoidal amplitude</t>
+  </si>
+  <si>
+    <t>sin_b</t>
+  </si>
+  <si>
+    <t>humid sinusoidal offset: y = a + b*cos(c*x + d_humid)</t>
+  </si>
+  <si>
+    <t>sin_a</t>
+  </si>
+  <si>
+    <t>arid MMF shape exponent</t>
+  </si>
+  <si>
+    <t>arid MMF upper asymptote</t>
+  </si>
+  <si>
+    <t>arid MMF: y = (a*b + c*x^d)/(b + x^d); b = b1_arid * b2_arid</t>
+  </si>
+  <si>
+    <t>Harris model exponent</t>
+  </si>
+  <si>
+    <t>Harris model scale term</t>
+  </si>
+  <si>
+    <t>Harris model: y = 1 / (a + b * x^c)</t>
+  </si>
+  <si>
+    <t>weights to be supplied from the DB</t>
+  </si>
+  <si>
+    <t>balanced</t>
+  </si>
+  <si>
+    <t>environmental_protection</t>
+  </si>
+  <si>
+    <t>biological_activity</t>
+  </si>
+  <si>
+    <t>w_env</t>
+  </si>
+  <si>
+    <t>w_bio</t>
+  </si>
+  <si>
+    <t>goal_name</t>
+  </si>
+  <si>
+    <t>goal_code</t>
+  </si>
+  <si>
+    <t>assumed particle density (g/cm3) in WFPS = (w * BD)/(1 - BD/2.65)</t>
+  </si>
+  <si>
+    <t>particle_density</t>
+  </si>
+  <si>
+    <t>c1 from the quadratic</t>
+  </si>
+  <si>
+    <t>c1 is overridden in the source; the quadratic returns a negative value at max_range 25</t>
+  </si>
+  <si>
+    <t>c1_override</t>
+  </si>
+  <si>
+    <t>winter, lo/lo</t>
+  </si>
+  <si>
+    <t>winter, lo/hi</t>
+  </si>
+  <si>
+    <t>winter, hi/lo</t>
+  </si>
+  <si>
+    <t>winter, hi/hi</t>
+  </si>
+  <si>
+    <t>fall, lo/lo</t>
+  </si>
+  <si>
+    <t>fall, lo/hi</t>
+  </si>
+  <si>
+    <t>fall, hi/lo</t>
+  </si>
+  <si>
+    <t>fall, hi/hi</t>
+  </si>
+  <si>
+    <t>summer, lo/lo</t>
+  </si>
+  <si>
+    <t>summer, lo/hi</t>
+  </si>
+  <si>
+    <t>summer, hi/lo</t>
+  </si>
+  <si>
+    <t>summer, hi/hi</t>
+  </si>
+  <si>
+    <t>spring - no change with climate</t>
+  </si>
+  <si>
+    <t>season</t>
+  </si>
+  <si>
+    <t>season_climate_code</t>
   </si>
 </sst>
 </file>
@@ -8690,6 +8853,138 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD58950-62EC-9C46-B27C-96CB7FD7303C}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>287</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="31">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31">
+        <v>2.7539999000000012E-3</v>
+      </c>
+      <c r="C2" s="31">
+        <v>-1.89288002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="31">
+        <v>2</v>
+      </c>
+      <c r="B3" s="31">
+        <v>7.4039996812500014E-3</v>
+      </c>
+      <c r="C3" s="31">
+        <v>-2.3483424981250001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="31">
+        <v>3</v>
+      </c>
+      <c r="B4" s="31">
+        <v>8.6929996249999995E-3</v>
+      </c>
+      <c r="C4" s="31">
+        <v>-2.4717799925000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="31">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31">
+        <v>6.2346664E-3</v>
+      </c>
+      <c r="C5" s="31">
+        <v>-2.2356866700000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="31">
+        <v>5</v>
+      </c>
+      <c r="B6" s="31">
+        <v>4.2549998250000004E-3</v>
+      </c>
+      <c r="C6" s="31">
+        <v>-2.0427200124999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A227F20-0344-1A48-B9EC-D2E2D4271877}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="31">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="31">
+        <v>2</v>
+      </c>
+      <c r="B3" s="31">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="31">
+        <v>3</v>
+      </c>
+      <c r="B4" s="31">
+        <v>1.0349999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="31">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C22"/>
@@ -8918,6 +9213,944 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA2CD5F3-6B90-6348-B17C-9292EE4809CB}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>293</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="31">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>292</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="31">
+        <v>2</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>290</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>289</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0005926D-A2EE-EC4A-BC1D-C6AD6201B1FC}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="B2" s="31">
+        <v>1.14E-2</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="B3" s="31">
+        <v>1.08786</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="31" t="s">
+        <v>158</v>
+      </c>
+      <c r="B4" s="31">
+        <v>2.1819999999999999</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="31" t="s">
+        <v>300</v>
+      </c>
+      <c r="B5" s="31">
+        <v>0.47720000000000001</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="B6" s="31">
+        <v>0.52675000000000005</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="31" t="s">
+        <v>296</v>
+      </c>
+      <c r="B7" s="31">
+        <v>6.87765</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="B8" s="31">
+        <v>0</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="B9" s="31">
+        <v>1</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>294</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{841E16A5-9CFF-6448-A42D-B30EF6D49653}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="31">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31">
+        <v>-0.49199999999999999</v>
+      </c>
+      <c r="C2" s="31">
+        <v>5.44</v>
+      </c>
+      <c r="D2" s="31">
+        <v>-5.03</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="31">
+        <v>2</v>
+      </c>
+      <c r="B3" s="31">
+        <v>-0.49199999999999999</v>
+      </c>
+      <c r="C3" s="31">
+        <v>5.44</v>
+      </c>
+      <c r="D3" s="31">
+        <v>-5.03</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="31">
+        <v>3</v>
+      </c>
+      <c r="B4" s="31">
+        <v>-0.745</v>
+      </c>
+      <c r="C4" s="31">
+        <v>5.63</v>
+      </c>
+      <c r="D4" s="31">
+        <v>-4.6399999999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="31">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31">
+        <v>-0.745</v>
+      </c>
+      <c r="C5" s="31">
+        <v>5.63</v>
+      </c>
+      <c r="D5" s="31">
+        <v>-4.6399999999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="31">
+        <v>5</v>
+      </c>
+      <c r="B6" s="31">
+        <v>-0.745</v>
+      </c>
+      <c r="C6" s="31">
+        <v>5.63</v>
+      </c>
+      <c r="D6" s="31">
+        <v>-4.6399999999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F54F3AD-ACFC-2146-B5DC-4B721BCC6471}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.6640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.83203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="B2" s="31">
+        <v>1.0213000000000001</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="31">
+        <v>19.776900000000001</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="31" t="s">
+        <v>248</v>
+      </c>
+      <c r="B4" s="31">
+        <v>11.010899999999999</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>304</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC0BDFFA-7C16-3C4D-A967-7AABEBE7A748}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10" style="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.1640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.33203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.83203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>314</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>313</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>312</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>311</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="31">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>310</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="31">
+        <v>2</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>309</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="31">
+        <v>3</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>308</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>307</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD82F6C1-DA71-954D-8D21-EE7F8E355BE0}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15" style="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.83203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="31" t="s">
+        <v>316</v>
+      </c>
+      <c r="B2" s="31">
+        <v>2.65</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="B3" s="31">
+        <v>0</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="B4" s="31">
+        <v>1</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>260</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19C4C3C3-BBAD-CD4F-B71D-23F195C39C50}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9.5" style="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="77.33203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>269</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>319</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="31">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31">
+        <v>25</v>
+      </c>
+      <c r="C2" s="31">
+        <v>6.2097000000000003E-3</v>
+      </c>
+      <c r="D2" s="31" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="31">
+        <v>2</v>
+      </c>
+      <c r="B3" s="31">
+        <v>5</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="31">
+        <v>3</v>
+      </c>
+      <c r="B4" s="31">
+        <v>3.5</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="31">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31">
+        <v>2</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>317</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{203ACF31-4035-8F4B-9BDC-2415406AA6A8}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="31">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="31">
+        <v>2</v>
+      </c>
+      <c r="B3" s="31">
+        <v>1.0249999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="31">
+        <v>3</v>
+      </c>
+      <c r="B4" s="31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="31">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="31">
+        <v>5</v>
+      </c>
+      <c r="B6" s="31">
+        <v>0.95</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3151E920-5D90-2D48-9B33-583546C7DD85}">
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="20.33203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29" style="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>334</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>333</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>276</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="31">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31">
+        <v>1</v>
+      </c>
+      <c r="C2" s="31">
+        <v>1</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="31">
+        <v>2.1</v>
+      </c>
+      <c r="B3" s="31">
+        <v>0.92</v>
+      </c>
+      <c r="C3" s="31">
+        <v>2</v>
+      </c>
+      <c r="D3" s="31">
+        <v>1</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="31">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4" s="31">
+        <v>0.93</v>
+      </c>
+      <c r="C4" s="31">
+        <v>2</v>
+      </c>
+      <c r="D4" s="31">
+        <v>2</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="31">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="B5" s="31">
+        <v>0.94</v>
+      </c>
+      <c r="C5" s="31">
+        <v>2</v>
+      </c>
+      <c r="D5" s="31">
+        <v>3</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="31">
+        <v>2.4</v>
+      </c>
+      <c r="B6" s="31">
+        <v>0.95</v>
+      </c>
+      <c r="C6" s="31">
+        <v>2</v>
+      </c>
+      <c r="D6" s="31">
+        <v>4</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="31">
+        <v>3.1</v>
+      </c>
+      <c r="B7" s="31">
+        <v>0.98</v>
+      </c>
+      <c r="C7" s="31">
+        <v>3</v>
+      </c>
+      <c r="D7" s="31">
+        <v>1</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="31">
+        <v>3.2</v>
+      </c>
+      <c r="B8" s="31">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="C8" s="31">
+        <v>3</v>
+      </c>
+      <c r="D8" s="31">
+        <v>2</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="31">
+        <v>3.3</v>
+      </c>
+      <c r="B9" s="31">
+        <v>0.97</v>
+      </c>
+      <c r="C9" s="31">
+        <v>3</v>
+      </c>
+      <c r="D9" s="31">
+        <v>3</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="31">
+        <v>3.4</v>
+      </c>
+      <c r="B10" s="31">
+        <v>0.96499999999999997</v>
+      </c>
+      <c r="C10" s="31">
+        <v>3</v>
+      </c>
+      <c r="D10" s="31">
+        <v>4</v>
+      </c>
+      <c r="E10" s="31" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="31">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B11" s="31">
+        <v>0.88</v>
+      </c>
+      <c r="C11" s="31">
+        <v>4</v>
+      </c>
+      <c r="D11" s="31">
+        <v>1</v>
+      </c>
+      <c r="E11" s="31" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="31">
+        <v>4.2</v>
+      </c>
+      <c r="B12" s="31">
+        <v>0.9</v>
+      </c>
+      <c r="C12" s="31">
+        <v>4</v>
+      </c>
+      <c r="D12" s="31">
+        <v>2</v>
+      </c>
+      <c r="E12" s="31" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="31">
+        <v>4.3</v>
+      </c>
+      <c r="B13" s="31">
+        <v>0.92</v>
+      </c>
+      <c r="C13" s="31">
+        <v>4</v>
+      </c>
+      <c r="D13" s="31">
+        <v>3</v>
+      </c>
+      <c r="E13" s="31" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="31">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="B14" s="31">
+        <v>0.94</v>
+      </c>
+      <c r="C14" s="31">
+        <v>4</v>
+      </c>
+      <c r="D14" s="31">
+        <v>4</v>
+      </c>
+      <c r="E14" s="31" t="s">
+        <v>320</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB8A6745-3164-FF46-8400-AADAD672391F}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="12.6640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.6640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="B2" s="31">
+        <v>1</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="31">
+        <v>40.747999999999998</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="B4" s="31">
+        <v>1.9316867000000001E-2</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="31" t="s">
+        <v>281</v>
+      </c>
+      <c r="B5" s="31">
+        <v>2.5638000000000002E-3</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="31" t="s">
+        <v>279</v>
+      </c>
+      <c r="B6" s="31">
+        <v>-7.8866666999999997E-4</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="B7" s="31">
+        <v>0</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="B8" s="31">
+        <v>1</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>260</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -8981,6 +10214,256 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D161720-D2F9-DC4B-9DF0-81E96E1ADED1}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="31">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="31">
+        <v>2</v>
+      </c>
+      <c r="B3" s="31">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="31">
+        <v>3</v>
+      </c>
+      <c r="B4" s="31">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="31">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31">
+        <v>3.81</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC782FC9-60A3-1B4A-B85A-5F72C3611880}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="31">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="31">
+        <v>2</v>
+      </c>
+      <c r="B3" s="31">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="31">
+        <v>3</v>
+      </c>
+      <c r="B4" s="31">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="31">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="31">
+        <v>5</v>
+      </c>
+      <c r="B6" s="31">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9DE095B-2486-1949-99EB-5E8EDEF7A1B2}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>276</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="31">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31">
+        <v>0.15</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="31">
+        <v>2</v>
+      </c>
+      <c r="B3" s="31">
+        <v>0.05</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="31">
+        <v>3</v>
+      </c>
+      <c r="B4" s="31">
+        <v>-0.05</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="31">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31">
+        <v>-0.1</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D8575D4-D14E-844D-BCFC-285ABD0F9841}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="B2" s="31">
+        <v>1</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="31">
+        <v>50.1</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="B4" s="31">
+        <v>0</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5" s="31">
+        <v>1</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>260</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 

--- a/SMAF_lookup.xlsx
+++ b/SMAF_lookup.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uflorida-my.sharepoint.com/personal/mohkam_singh_ufl_edu/Documents/Mohkam Singh - WORDLY/Research Projects/PhD Research/gSHAPE/Github Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="166" documentId="11_95635A838F67E66DF7088085E56DEBB51F12BD57" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A69C7750-BE9E-0249-823D-3CFFF60840F1}"/>
+  <xr:revisionPtr revIDLastSave="167" documentId="11_95635A838F67E66DF7088085E56DEBB51F12BD57" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AA96D3B-BABB-DE4C-ACE8-988665EF197C}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="500" firstSheet="27" activeTab="35" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="16920" tabRatio="500" firstSheet="35" activeTab="43" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ph_factors" sheetId="14" r:id="rId1"/>
@@ -56,6 +56,10 @@
     <sheet name="soc_texture_factors" sheetId="42" r:id="rId41"/>
     <sheet name="soc_climate_factors" sheetId="43" r:id="rId42"/>
     <sheet name="soc_constants" sheetId="44" r:id="rId43"/>
+    <sheet name="bg_om_factors" sheetId="45" r:id="rId44"/>
+    <sheet name="bg_texture_factors" sheetId="46" r:id="rId45"/>
+    <sheet name="bg_climate_factors" sheetId="47" r:id="rId46"/>
+    <sheet name="bg_constants" sheetId="48" r:id="rId47"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">crop_factors!$A$1:$E$109</definedName>
@@ -85,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="340">
   <si>
     <t>Clean crop name</t>
   </si>
@@ -1090,6 +1094,21 @@
   </si>
   <si>
     <t>season_climate_code</t>
+  </si>
+  <si>
+    <t>hi degree days / hi ppt (&gt;=170 deg-days and &gt;=550 mm)</t>
+  </si>
+  <si>
+    <t>upper clamp; the raw curve approaches a = 1.01</t>
+  </si>
+  <si>
+    <t>BG is divided by this before entering the exponent</t>
+  </si>
+  <si>
+    <t>x_scale</t>
+  </si>
+  <si>
+    <t>logistic asymptote: y = a / (1 + b*exp(-c * x/x_scale))</t>
   </si>
 </sst>
 </file>
@@ -10467,6 +10486,275 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FD0FC9B-152C-4148-A837-4A5BA684F170}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="31">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="31">
+        <v>2</v>
+      </c>
+      <c r="B3" s="31">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="31">
+        <v>3</v>
+      </c>
+      <c r="B4" s="31">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="31">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31">
+        <v>5.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56303983-9DF5-594C-944D-C3E84432531C}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12" style="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="31">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="31">
+        <v>2</v>
+      </c>
+      <c r="B3" s="31">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="31">
+        <v>3</v>
+      </c>
+      <c r="B4" s="31">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="31">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="31">
+        <v>5</v>
+      </c>
+      <c r="B6" s="31">
+        <v>1.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6826A34E-17FD-1B48-9942-3AFED748CD17}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.33203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.83203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>276</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="31">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31">
+        <v>2.1</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="31">
+        <v>2</v>
+      </c>
+      <c r="B3" s="31">
+        <v>0.85</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="31">
+        <v>3</v>
+      </c>
+      <c r="B4" s="31">
+        <v>0.7</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="31">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31">
+        <v>0.45</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBF5E631-3E46-DF4F-9CE1-87D4B4C71C48}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.6640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.1640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.83203125" style="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="B2" s="31">
+        <v>1.01</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="31">
+        <v>48.4</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="31" t="s">
+        <v>338</v>
+      </c>
+      <c r="B4" s="31">
+        <v>1000</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="B5" s="31">
+        <v>0</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="B6" s="31">
+        <v>1</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>336</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D8"/>

--- a/SMAF_lookup.xlsx
+++ b/SMAF_lookup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uflorida-my.sharepoint.com/personal/mohkam_singh_ufl_edu/Documents/Mohkam Singh - WORDLY/Research Projects/PhD Research/gSHAPE/Github Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="172" documentId="11_95635A838F67E66DF7088085E56DEBB51F12BD57" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E5D7388-9032-8C4A-9944-357AE0865863}"/>
+  <xr:revisionPtr revIDLastSave="176" documentId="11_95635A838F67E66DF7088085E56DEBB51F12BD57" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B96471B1-C2A3-BC40-B7E7-1A664942FCA4}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="16920" tabRatio="500" firstSheet="33" activeTab="39" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ph_crop_factors" sheetId="49" r:id="rId1"/>
@@ -9940,6 +9940,9 @@
       <c r="B3" s="31">
         <v>5</v>
       </c>
+      <c r="C3">
+        <v>1.24192E-2</v>
+      </c>
       <c r="D3" s="31" t="s">
         <v>317</v>
       </c>
@@ -9951,6 +9954,9 @@
       <c r="B4" s="31">
         <v>3.5</v>
       </c>
+      <c r="C4">
+        <v>1.8629E-2</v>
+      </c>
       <c r="D4" s="31" t="s">
         <v>317</v>
       </c>
@@ -9961,6 +9967,9 @@
       </c>
       <c r="B5" s="31">
         <v>2</v>
+      </c>
+      <c r="C5">
+        <v>2.1289800000000001E-2</v>
       </c>
       <c r="D5" s="31" t="s">
         <v>317</v>
